--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -703,7 +703,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>692.788</t>
+          <t>1601.894</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>11.79</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>234.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -748,97 +748,97 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>227.65</t>
+          <t>228.125</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>220.82</t>
+          <t>221.11</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-42.80</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>1.51515151515151</t>
+          <t>33.33333333333333</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>-111.39</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -848,22 +848,22 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-81506985.4</t>
+          <t>-50218326.2</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-95974335.1</t>
+          <t>-23756113.8</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-26489198.03</t>
+          <t>9737328.62</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>38.96</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>64.08</t>
+          <t>63.92</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>71126</t>
+          <t>74302</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>560.0</t>
+          <t>1179.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -995,17 +995,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>23.18</t>
+          <t>48.80</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>575.0</t>
+          <t>608.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1015,97 +1015,97 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>-7.04</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>91</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>588.55</t>
+          <t>589.65</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>579.8</t>
+          <t>580.56</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-57.59</t>
+          <t>-22.63</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>7.575757575757557</t>
+          <t>33.33333333333331</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>-102.61</t>
+          <t>54.71</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1115,22 +1115,22 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-195170.8</t>
+          <t>-32574.6</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-96328.9</t>
+          <t>-71922.2</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>-54</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-54648.05</t>
+          <t>15546.47</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>72.15</t>
+          <t>72.77</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>46033</t>
+          <t>48675</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1247,64 +1247,64 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-1.82</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>價-量-</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1322,37 +1322,37 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>14.375</t>
+          <t>14.345</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>15.231</t>
+          <t>15.156</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1362,17 +1362,17 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.99999999999993</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.666666666666631</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>-104.07</t>
+          <t>-150.64</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1382,22 +1382,22 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-461.2</t>
+          <t>-293.0</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-226.0</t>
+          <t>-116.9</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-78.22</t>
+          <t>-7.63</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>24.39</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>56.55</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2339.257</t>
+          <t>3661.681</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1529,17 +1529,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1549,27 +1549,27 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1579,67 +1579,67 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.48999999999999</t>
+          <t>41.5025</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>41.088</t>
+          <t>41.087</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-68.92</t>
+          <t>-36.57</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.77777777777789</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14.81481481481475</t>
+          <t>40.74074074074071</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>-224.89</t>
+          <t>-144.91</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1649,22 +1649,22 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-68213705.6</t>
+          <t>-20024818.6</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>54617828.9</t>
+          <t>44593017.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-224</t>
+          <t>-144</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-17877337.83</t>
+          <t>-3368604.63</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1694,17 +1694,17 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>14.84</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>84789</t>
+          <t>86963</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>建材營造右下</t>
+          <t>建材營造平</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5132.916</t>
+          <t>3922.257</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1796,17 +1796,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>277.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1816,97 +1816,97 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>52</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>281.45</t>
+          <t>281.65</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>279.9</t>
+          <t>280.28</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-77.28</t>
+          <t>-95.21</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>29.54545454545455</t>
+          <t>38.63636363636363</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17.7849927849928</t>
+          <t>22.72727272727273</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-371.38</t>
+          <t>-158.02</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1916,22 +1916,22 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-435474087.6</t>
+          <t>-64708550.6</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>160464575.6</t>
+          <t>111530375.5</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-371</t>
+          <t>-158</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-96797262.14</t>
+          <t>-2770738.22</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>17.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>184219</t>
+          <t>185559</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1838.17</t>
+          <t>1653.784</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2063,17 +2063,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2113,22 +2113,22 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -2138,42 +2138,42 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10.411</t>
+          <t>10.4085</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.2164</t>
+          <t>10.2144</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-110.29</t>
+          <t>-140.15</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>24.99999999999989</t>
+          <t>60.00000000000014</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>31.19047619047624</t>
+          <t>41.66666666666673</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>-31.87</t>
+          <t>-33.79</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -2183,22 +2183,22 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-10329971.4</t>
+          <t>-4665489.4</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-7833453.4</t>
+          <t>-3487109.1</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5253842.77</t>
+          <t>-2929687.08</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>155.68</t>
+          <t>159.44</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2315,12 +2315,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>38023.651</t>
+          <t>21101.469</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2330,17 +2330,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>75.32</t>
+          <t>41.80</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2350,52 +2350,52 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>151</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>119</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>38024</t>
+          <t>21101</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -2405,42 +2405,42 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>117.525</t>
+          <t>117.925</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>111.05</t>
+          <t>111.43</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>36.36363636363637</t>
+          <t>59.09090909090909</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>78.78787878787878</t>
+          <t>65.15151515151514</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>182.06</t>
+          <t>340.35</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -2450,22 +2450,22 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>71978566.8</t>
+          <t>430903410.2</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-87717764.0</t>
+          <t>97855180.5</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-182</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-243248585.96</t>
+          <t>8947440.01</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2495,47 +2495,47 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>17.81</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>21.13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>22.58%</t>
+          <t>22.12%</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>10.09%</t>
+          <t>9.22%</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>278600</t>
+          <t>284453</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>39.07</t>
+          <t>35.46</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>281.847</t>
+          <t>302.811</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2647,42 +2647,42 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>303</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>24.52</t>
+          <t>24.4725</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.741</t>
+          <t>24.717</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2692,22 +2692,22 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>31.81818181818169</t>
+          <t>54.54545454545445</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>53.03030303030302</t>
+          <t>49.99999999999994</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>-92.99</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2717,22 +2717,22 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>-5446898.0</t>
+          <t>-3364902.2</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-2822412.2</t>
+          <t>-2629494.1</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-905049.83</t>
+          <t>41196.6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -2762,17 +2762,17 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>11.14</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -2834,12 +2834,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>弱勢突破股;建議關注股;多頭排列股</t>
+          <t>建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2864,17 +2864,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>44.00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2894,87 +2894,87 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>68</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-16.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>99</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>31.8425</t>
+          <t>31.9825</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>30.268</t>
+          <t>30.347</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>58.33333333333344</t>
+          <t>66.66666666666627</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>74.9999999999999</t>
+          <t>63.88888888888867</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>53.04</t>
+          <t>119.64</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -2984,32 +2984,32 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>573.6</t>
+          <t>876.6</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>374.8</t>
+          <t>399.1</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>119</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-165.68</t>
+          <t>76.21</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16961.942</t>
+          <t>11575.724</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>42</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -3181,67 +3181,67 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>105</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>16962</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>23.9875</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>25.852</t>
+          <t>25.735</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>34.51</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>60.71428571428572</t>
+          <t>36.36363636363619</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>74.20634920634924</t>
+          <t>65.69264069264062</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>-120.38</t>
+          <t>-126.02</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -3251,22 +3251,22 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-10157410.2</t>
+          <t>-17209167.8</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>49828508.7</t>
+          <t>66141831.8</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-126</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>32051467.68</t>
+          <t>8438238.5</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>183494</t>
+          <t>182361</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -703,7 +703,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1601.894</t>
+          <t>1276.399</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11.79</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>232.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -758,87 +758,87 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>228.125</t>
+          <t>228.75</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>221.11</t>
+          <t>221.37</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-14.08</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>33.33333333333333</t>
+          <t>61.66666666666666</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-111.39</t>
+          <t>-104.84</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -848,22 +848,22 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-50218326.2</t>
+          <t>-82194101.0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-23756113.8</t>
+          <t>-40126431.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>9737328.62</t>
+          <t>-15229190.41</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>63.92</t>
+          <t>63.68</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>74302</t>
+          <t>73825</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -965,12 +965,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>強勢股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1179.0</t>
+          <t>1970.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -995,17 +995,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>48.80</t>
+          <t>81.54</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>608.0</t>
+          <t>642.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-7.04</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>153</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1045,52 +1045,52 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>78</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>589.65</t>
+          <t>593.0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>580.56</t>
+          <t>581.76</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-22.63</t>
+          <t>46.01</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>33.33333333333331</t>
+          <t>66.66666666666664</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>54.71</t>
+          <t>244.32</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1115,32 +1115,32 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-32574.6</t>
+          <t>241877.2</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-71922.2</t>
+          <t>70247.7</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-54</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>15546.47</t>
+          <t>105157.58</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>72.77</t>
+          <t>73.75</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>48675</t>
+          <t>51397</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>反彈型股</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1262,17 +1262,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1317,62 +1317,62 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>41</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>14.345</t>
+          <t>14.315</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>15.156</t>
+          <t>15.079</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>8.91</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>19.99999999999993</t>
+          <t>59.99999999999979</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>6.666666666666631</t>
+          <t>26.66666666666656</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>-150.64</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1382,22 +1382,22 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-293.0</t>
+          <t>-135.2</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-116.9</t>
+          <t>-139.1</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-7.63</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>56.55</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1499,12 +1499,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>強勢股;多頭排列股</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3661.681</t>
+          <t>6893.882</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1529,17 +1529,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1549,97 +1549,97 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>78</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.5025</t>
+          <t>41.57250000000001</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>41.087</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-36.57</t>
+          <t>32.24</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>77.77777777777789</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>40.74074074074071</t>
+          <t>59.25925925925932</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>-144.91</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1649,32 +1649,32 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-20024818.6</t>
+          <t>64851566.0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>44593017.0</t>
+          <t>50648764.4</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-144</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3368604.63</t>
+          <t>17504154.91</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1694,17 +1694,17 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>15.18</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>86963</t>
+          <t>88930</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3922.257</t>
+          <t>2140.681</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1796,17 +1796,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>277.0</t>
+          <t>273.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1816,97 +1816,97 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-18.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>281.65</t>
+          <t>281.7</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>280.28</t>
+          <t>280.63</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-95.21</t>
+          <t>-140.47</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>38.63636363636363</t>
+          <t>22.72727272727273</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22.72727272727273</t>
+          <t>30.30303030303031</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-158.02</t>
+          <t>-234.47</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1916,22 +1916,22 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-64708550.6</t>
+          <t>-331458510.2</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>111530375.5</t>
+          <t>-99099403.9</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-158</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2770738.22</t>
+          <t>-62000115.82</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>17.06</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>44.08</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>185559</t>
+          <t>183214</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1653.784</t>
+          <t>4403.419</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2063,17 +2063,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2083,29 +2083,29 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>價-量-</t>
@@ -2113,67 +2113,67 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1654</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10.4085</t>
+          <t>10.431</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.2144</t>
+          <t>10.2204</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-140.15</t>
+          <t>-53.43</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>60.00000000000014</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>41.66666666666673</t>
+          <t>61.66666666666666</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>-33.79</t>
+          <t>-73.07</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -2183,22 +2183,22 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-4665489.4</t>
+          <t>686177.0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-3487109.1</t>
+          <t>2548069.3</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-73</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2929687.08</t>
+          <t>954866.68</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>159.44</t>
+          <t>160.39</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2315,12 +2315,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21101.469</t>
+          <t>14053.659</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>41.80</t>
+          <t>36.70</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2350,97 +2350,97 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>-9.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>79</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>117.925</t>
+          <t>118.3</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>111.43</t>
+          <t>111.84</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>59.09090909090909</t>
+          <t>52.63157894736842</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>65.15151515151514</t>
+          <t>49.36204146730463</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>340.35</t>
+          <t>-5379.34</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -2450,22 +2450,22 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>430903410.2</t>
+          <t>-688076246.8</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>97855180.5</t>
+          <t>13033371.6</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>-5379</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>8947440.01</t>
+          <t>-132735718.89</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>44.08</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2567,12 +2567,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>反彈型股</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>302.811</t>
+          <t>444.655</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2647,67 +2647,67 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>445</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>24.4725</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.717</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>59.45</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>-0.08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>54.54545454545445</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>49.99999999999994</t>
+          <t>62.12121212121205</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2717,32 +2717,32 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>-3364902.2</t>
+          <t>-459408.0</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-2629494.1</t>
+          <t>-723152.9</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-36</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>41196.6</t>
+          <t>978134.86</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2762,17 +2762,17 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>11.14</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>居家生活右下</t>
+          <t>居家生活平</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2864,17 +2864,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>44.00</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2884,97 +2884,97 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>58</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>-10.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>24</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>31.9825</t>
+          <t>32.1625</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>30.347</t>
+          <t>30.427</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>66.66666666666627</t>
+          <t>83.33333333333314</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>63.88888888888867</t>
+          <t>69.44444444444429</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>119.64</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -2984,22 +2984,22 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>876.6</t>
+          <t>731.6</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>399.1</t>
+          <t>581.3</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>76.21</t>
+          <t>60.25</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3116,62 +3116,62 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>14124.654</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>11.89</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>24.15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>-0.62</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>11575.724</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>9.75</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>24.15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>35</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -3181,67 +3181,67 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>102</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>11576</t>
+          <t>14125</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>23.9875</t>
+          <t>23.9525</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>25.735</t>
+          <t>25.623</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>34.51</t>
+          <t>33.27</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>36.36363636363619</t>
+          <t>6.666666666666288</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>65.69264069264062</t>
+          <t>34.58152958152938</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>-126.02</t>
+          <t>-332.78</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -3251,22 +3251,22 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-17209167.8</t>
+          <t>-165009539.0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>66141831.8</t>
+          <t>70885608.9</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-126</t>
+          <t>-332</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>8438238.5</t>
+          <t>-12663163.76</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA11"/>
+  <dimension ref="A1:BA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -698,12 +698,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1276.399</t>
+          <t>830.697</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -768,62 +768,62 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>831</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>228.75</t>
+          <t>229.2</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>221.37</t>
+          <t>221.68</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-14.08</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>61.66666666666666</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-104.84</t>
+          <t>-180.51</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -848,22 +848,22 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-82194101.0</t>
+          <t>-81145022.6</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-40126431.0</t>
+          <t>-28927323.3</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-15229190.41</t>
+          <t>-24482261.45</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>63.68</t>
+          <t>64.58</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -970,177 +970,177 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4.26</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3325.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-1.21</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>670.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3325</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>8.94</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>598.4</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>583.72</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>92.78</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>12.21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>6.34</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>115.96</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>722306.6</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>334459.1</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>240728.16</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>4966</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>5.65</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1970.0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>81.54</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>5.89</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>642.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-6.64</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>7.25</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>593.0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>581.76</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>46.01</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>7.10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4.87</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>66.66666666666664</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>244.32</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>241877.2</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>70247.7</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>105157.58</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>73.75</t>
+          <t>74.13</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51397</t>
+          <t>53639</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1262,184 +1262,184 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-1.05</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-1.52</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-4.72</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>14.2975</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>15.006</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>16.90</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>-0.28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>59.99999999999989</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3346.15</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>126.6</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-3.9</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>-3346</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>90.11</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>李洲</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>-2.06</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>-5.07</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>14.315</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>15.079</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>8.91</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>59.99999999999979</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>26.66666666666656</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>-135.2</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-139.1</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>48.95</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>李洲</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AQ4" t="inlineStr">
         <is>
           <t>0.66</t>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1504,177 +1504,177 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-2.22</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4813.708</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8.18</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4814</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>41.615</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>41.125</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>26.39</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>52.49999999999986</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>76.75925925925927</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>600.45</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>47753274.6</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>-9542050.8</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>-600</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>-5583324.29</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>6893.882</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>11.72</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>42.95</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-2.75</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>6894</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>41.57250000000001</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>41.11</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>32.24</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>59.25925925925932</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>28.04</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>64851566.0</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>50648764.4</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>17504154.91</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1694,17 +1694,17 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>14.84</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>88930</t>
+          <t>86963</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2140.681</t>
+          <t>3175.818</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1796,17 +1796,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>273.5</t>
+          <t>278.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1826,87 +1826,87 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-18.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>56</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>281.7</t>
+          <t>281.9</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>280.63</t>
+          <t>281.02</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-140.47</t>
+          <t>-168.65</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>22.72727272727273</t>
+          <t>43.18181818181818</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>30.30303030303031</t>
+          <t>34.84848484848485</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-234.47</t>
+          <t>-25.23</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1916,22 +1916,22 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-331458510.2</t>
+          <t>92066746.4</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-99099403.9</t>
+          <t>123136157.2</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-62000115.82</t>
+          <t>8025286.29</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>44.94</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>183214</t>
+          <t>186229</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2033,132 +2033,132 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>強勢股;建議關注股;多頭排列股</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>60756.283</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2349</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.43</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4403.419</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8.98</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10.6</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>157</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>805</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>60756</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>7.40</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10.431</t>
+          <t>119.25</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.2204</t>
+          <t>112.48</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-53.43</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>61.66666666666666</t>
+          <t>70.57416267942584</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>-73.07</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -2183,42 +2183,42 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>686177.0</t>
+          <t>1279167601.8</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2548069.3</t>
+          <t>925401898.2</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-73</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>954866.68</t>
+          <t>487516629.05</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>錸德</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2228,264 +2228,264 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>17.81</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>23.22</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>13.42%</t>
+          <t>22.12%</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>9.22%</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>160.39</t>
+          <t>44.94</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>312547</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>光學產品84.42%、其他15.58% (2024年)</t>
+          <t>資訊及消費性電子43.00%、雲端及物聯網37.00%、光電通訊20.00% (2024年)</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>錸德-光電業-上市</t>
+          <t>光寶科-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>光電業平</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>35.46</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 光碟片</t>
+          <t>** 汽車 - 銷售、進出口業務、車燈、其他** 電腦及週邊設備 - 機殼、電源供應器、伺服器、其他電腦及週邊設備、安全監控系統** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 其他 - 其他電子產品及電子服務產業** 雲端運算 - 電力設備、冷卻設備、雲端應用服務、系統整合、顧問諮詢、設備安裝服務、IaaS、PaaS、SaaS** 體驗科技 - 環境感知、深度感測、視覺、手勢/動作** LED照明產業 - 封裝/模組、燈具/應用** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 智慧電網 - 配電管理設施** 醫療器材 - 醫療耗材、生物檢測</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>強勢股;建議關注股;多頭排列股</t>
+          <t>反彈型股</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>266.335</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.41</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>24.85</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>24.475</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>24.685</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>89.16</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>82.35294117647078</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>78.96613190730841</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>-159.34</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>-298022.8</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>502255.4</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>-159</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>283945.74</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>14053.659</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>36.70</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>121.5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>-9.0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>14054</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>5.78</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>118.3</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>111.84</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>52.63157894736842</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>49.36204146730463</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>-5379.34</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>-688076246.8</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>13033371.6</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>-5379</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>-132735718.89</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>橋椿</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2495,99 +2495,99 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>17.81</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>21.13</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>22.12%</t>
+          <t>12.06%</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>9.22%</t>
+          <t>3.02%</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>11.23</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>284453</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>資訊及消費性電子43.00%、雲端及物聯網37.00%、光電通訊20.00% (2024年)</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>光寶科-電腦及週邊設備業-上市</t>
+          <t>橋椿-居家生活-上市</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>居家生活平</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>35.46</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>** 汽車 - 銷售、進出口業務、車燈、其他** 電腦及週邊設備 - 機殼、電源供應器、伺服器、其他電腦及週邊設備、安全監控系統** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 其他 - 其他電子產品及電子服務產業** 雲端運算 - 電力設備、冷卻設備、雲端應用服務、系統整合、顧問諮詢、設備安裝服務、IaaS、PaaS、SaaS** 體驗科技 - 環境感知、深度感測、視覺、手勢/動作** LED照明產業 - 封裝/模組、燈具/應用** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 智慧電網 - 配電管理設施** 醫療器材 - 醫療耗材、生物檢測</t>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>反彈型股</t>
+          <t>弱勢突破股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>444.655</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>32.82</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2617,82 +2617,82 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>95</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>64</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>32.3325</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>30.517</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>59.45</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>62.12121212121205</t>
+          <t>83.33333333333314</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>50.30</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2717,144 +2717,144 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>-459408.0</t>
+          <t>875.2</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-723152.9</t>
+          <t>582.3</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>-36</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>978134.86</t>
+          <t>147.78</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>橋椿</t>
+          <t>宏佳騰</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>19.62</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>12.06%</t>
+          <t>21.60%</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>-2.75%</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
+          <t>ATV/ UTV64.10%、摩托車14.76%、電動車輛13.19%、零組件及其他7.95% (2024年)</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>橋椿-居家生活-上市</t>
+          <t>宏佳騰-電機機械-上櫃</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>居家生活平</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>** 其他 - 其他</t>
+          <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>建議關注股;多頭排列股</t>
+          <t>反彈型股</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>12711.519</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2864,17 +2864,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10.70</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2894,17 +2894,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>32</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2914,67 +2914,67 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>90</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>32.1625</t>
+          <t>23.9575</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>30.427</t>
+          <t>25.515</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>83.33333333333314</t>
+          <t>46.66666666666639</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>69.44444444444429</t>
+          <t>29.8989898989896</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>-2847.91</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -2984,382 +2984,115 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>731.6</t>
+          <t>-33611834.0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>581.3</t>
+          <t>1223176.8</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-2847</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>60.25</t>
+          <t>21507517.72</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>宏佳騰</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>水泥工業</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>21.60%</t>
+          <t>16.86%</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>6.58%</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>184626</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>ATV/ UTV64.10%、摩托車14.76%、電動車輛13.19%、零組件及其他7.95% (2024年)</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>宏佳騰-電機機械-上櫃</t>
+          <t>台泥-水泥工業-上市</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>水泥工業右下</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>33.02</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
-        <is>
-          <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>反彈型股</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>14124.654</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>11.89</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>24.15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>-0.62</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>-7.0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>14125</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>-6.52</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>23.9525</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>25.623</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>33.27</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>-0.36</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>-0.54</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>6.666666666666288</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>34.58152958152938</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>-332.78</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>-165009539.0</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>70885608.9</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>-332</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-12663163.76</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>4.14</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>4.52</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>19.02</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>16.86%</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>6.58%</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>16.69</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>182361</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>台泥-水泥工業-上市</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>水泥工業右下</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>33.02</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
         <is>
           <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA10"/>
+  <dimension ref="A1:BA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -703,7 +703,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>830.697</t>
+          <t>923.694</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>232.5</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -748,57 +748,57 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>924</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -808,37 +808,37 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>221.68</t>
+          <t>221.96</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-23.12</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>63.33333333333334</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-180.51</t>
+          <t>-57.39</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -848,22 +848,22 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-81145022.6</t>
+          <t>-98282376.8</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-28927323.3</t>
+          <t>-62444937.2</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-24482261.45</t>
+          <t>-31421002.59</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>64.58</t>
+          <t>51.66</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>73825</t>
+          <t>71761</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3325.0</t>
+          <t>1535.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -995,17 +995,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>46.17</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1015,97 +1015,97 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>205</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>44</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>598.4</t>
+          <t>602.6</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>583.72</t>
+          <t>585.58</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>92.78</t>
+          <t>92.89</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.89473684210527</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.29824561403507</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>115.96</t>
+          <t>176.82</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1115,22 +1115,22 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>722306.6</t>
+          <t>571420.4</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>334459.1</t>
+          <t>206423.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>176</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>240728.16</t>
+          <t>83874.56</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>74.13</t>
+          <t>75.59</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>53639</t>
+          <t>53479</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>251.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1262,17 +1262,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1282,164 +1282,164 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>9.27</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-4.06</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>14.3575</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>14.965</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>54.97</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>86.66666666666659</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>194.17</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>1035.2</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>351.9</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>366.94</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>李洲</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>-1.52</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>-4.72</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>14.2975</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>15.006</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>16.90</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>59.99999999999989</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3346.15</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>126.6</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-3.9</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>-3346</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>90.11</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>李洲</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AQ4" t="inlineStr">
         <is>
           <t>0.66</t>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>57.65</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4813.708</t>
+          <t>2795.173</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1529,17 +1529,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1549,97 +1549,97 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>32</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.615</t>
+          <t>41.6975</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>41.125</t>
+          <t>41.15900000000001</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>52.49999999999986</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>76.75925925925927</t>
+          <t>71.66666666666664</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>600.45</t>
+          <t>720.74</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1649,22 +1649,22 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>47753274.6</t>
+          <t>53252682.6</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-9542050.8</t>
+          <t>-8578904.1</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-600</t>
+          <t>-720</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-5583324.29</t>
+          <t>2444729.25</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1694,17 +1694,17 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>21.09</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>86963</t>
+          <t>87377</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3175.818</t>
+          <t>2372.716</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1816,27 +1816,27 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1846,67 +1846,67 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>281.9</t>
+          <t>281.875</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>281.02</t>
+          <t>281.45</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-168.65</t>
+          <t>-218.38</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>43.18181818181818</t>
+          <t>46.34146341463415</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>34.84848484848485</t>
+          <t>37.4168514412417</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-25.23</t>
+          <t>2864.45</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1916,22 +1916,22 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>92066746.4</t>
+          <t>424168056.2</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>123136157.2</t>
+          <t>-15343643.6</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>-2864</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>8025286.29</t>
+          <t>-58691857.63</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>44.94</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2033,27 +2033,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>強勢股;建議關注股;多頭排列股</t>
+          <t>強勢股;多頭排列股</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60756.283</t>
+          <t>3406.686</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2063,17 +2063,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2083,82 +2083,82 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>60756</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>119.25</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>112.48</t>
+          <t>10.2534</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>112.24</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -2168,57 +2168,57 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>70.57416267942584</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>38.23</t>
+          <t>112.75</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1279167601.8</t>
+          <t>25412174.4</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>925401898.2</t>
+          <t>11944577.5</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>487516629.05</t>
+          <t>4779477.86</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>錸德</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2228,99 +2228,99 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>17.81</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>23.22</t>
+          <t>219.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>22.12%</t>
+          <t>13.42%</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>9.22%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>44.94</t>
+          <t>163.82</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>312547</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>資訊及消費性電子43.00%、雲端及物聯網37.00%、光電通訊20.00% (2024年)</t>
+          <t>光學產品84.42%、其他15.58% (2024年)</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>光寶科-電腦及週邊設備業-上市</t>
+          <t>錸德-光電業-上市</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>光電業平</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>35.46</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>** 汽車 - 銷售、進出口業務、車燈、其他** 電腦及週邊設備 - 機殼、電源供應器、伺服器、其他電腦及週邊設備、安全監控系統** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 其他 - 其他電子產品及電子服務產業** 雲端運算 - 電力設備、冷卻設備、雲端應用服務、系統整合、顧問諮詢、設備安裝服務、IaaS、PaaS、SaaS** 體驗科技 - 環境感知、深度感測、視覺、手勢/動作** LED照明產業 - 封裝/模組、燈具/應用** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 智慧電網 - 配電管理設施** 醫療器材 - 醫療耗材、生物檢測</t>
+          <t>** 電腦及週邊設備 - 光碟片</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>反彈型股</t>
+          <t>強勢股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>266.335</t>
+          <t>128300.961</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2330,17 +2330,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2350,97 +2350,97 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>940</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>128301</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>24.475</t>
+          <t>120.075</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>24.685</t>
+          <t>113.11</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>30.97</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>82.35294117647078</t>
+          <t>96.875</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>78.96613190730841</t>
+          <t>83.1688596491228</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>-159.34</t>
+          <t>-187.36</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -2450,42 +2450,42 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-298022.8</t>
+          <t>-2659166418.2</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>502255.4</t>
+          <t>-925377316.6</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-159</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>283945.74</t>
+          <t>-991216135.21</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>橋椿</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2495,99 +2495,99 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>17.81</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>12.06%</t>
+          <t>22.12%</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>9.22%</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>311377</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
+          <t>資訊及消費性電子43.00%、雲端及物聯網37.00%、光電通訊20.00% (2024年)</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>橋椿-居家生活-上市</t>
+          <t>光寶科-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>居家生活平</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>35.46</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>** 其他 - 其他</t>
+          <t>** 汽車 - 銷售、進出口業務、車燈、其他** 電腦及週邊設備 - 機殼、電源供應器、伺服器、其他電腦及週邊設備、安全監控系統** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 其他 - 其他電子產品及電子服務產業** 雲端運算 - 電力設備、冷卻設備、雲端應用服務、系統整合、顧問諮詢、設備安裝服務、IaaS、PaaS、SaaS** 體驗科技 - 環境感知、深度感測、視覺、手勢/動作** LED照明產業 - 封裝/模組、燈具/應用** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 智慧電網 - 配電管理設施** 醫療器材 - 醫療耗材、生物檢測</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>弱勢突破股;建議關注股;多頭排列股</t>
+          <t>反彈型股</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>214.451</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>32.82</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2617,97 +2617,97 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>32.3325</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>30.517</t>
+          <t>24.655</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>134.22</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.23529411764692</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>83.33333333333314</t>
+          <t>90.19607843137256</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>50.30</t>
+          <t>8886.86</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2717,382 +2717,649 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>875.2</t>
+          <t>2042695.6</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>582.3</t>
+          <t>22729.8</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>147.78</t>
+          <t>691592.79</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>宏佳騰</t>
+          <t>橋椿</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>21.60%</t>
+          <t>12.06%</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>3.02%</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>ATV/ UTV64.10%、摩托車14.76%、電動車輛13.19%、零組件及其他7.95% (2024年)</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>宏佳騰-電機機械-上櫃</t>
+          <t>橋椿-居家生活-上市</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>居家生活平</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>建議關注股;多頭排列股</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1599</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>10.77</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>6.18</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>32.495</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>30.605</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>-4.72</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>76.92307692307709</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>86.75213675213674</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>26.96</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>1038.4</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>817.9</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>-6.9</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>宏佳騰</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>6.95</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>19.53</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>21.60%</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-2.75%</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>40.18</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>2474</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>ATV/ UTV64.10%、摩托車14.76%、電動車輛13.19%、零組件及其他7.95% (2024年)</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>宏佳騰-電機機械-上櫃</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>電機機械平</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>26.82</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>反彈型股</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>1101</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>12711.519</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>6790.212</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>10.70</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>5.72</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>24.35</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>12712</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>6790</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>0.29</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>-6.10</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>23.9575</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>25.515</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>36.42</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>-0.50</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>46.66666666666639</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>29.8989898989896</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>-2847.91</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>-5.69</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>23.97</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>25.415</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>37.42</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>33.33333333333333</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>28.88888888888865</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>-88.53</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>-33611834.0</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>1223176.8</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>-2847</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>21507517.72</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>-177483720.2</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>-94140549.7</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>9213745.12</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
         <is>
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
         <is>
           <t>台泥</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>水泥工業</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>4.09</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>4.52</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>19.17</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
         <is>
           <t>16.86%</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AT11" t="inlineStr">
         <is>
           <t>6.58%</t>
         </is>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>184626</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>16.73</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>183871</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
         <is>
           <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>台泥-水泥工業-上市</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>水泥工業右下</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>33.02</t>
         </is>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -698,12 +698,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>建議關注股;多頭排列股</t>
+          <t>強勢股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>923.694</t>
+          <t>2626.905</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>238.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -748,97 +748,97 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>229.2</t>
+          <t>229.8</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>221.96</t>
+          <t>222.43</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-23.12</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>63.33333333333334</t>
+          <t>68.33333333333333</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-57.39</t>
+          <t>579.55</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -848,32 +848,32 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-98282376.8</t>
+          <t>57518307.0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-62444937.2</t>
+          <t>-11994339.2</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-579</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-31421002.59</t>
+          <t>27012910.9</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>51.66</t>
+          <t>53.88</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>71761</t>
+          <t>75572</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>半導體業右下</t>
+          <t>半導體業平</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1535.0</t>
+          <t>2675.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -995,17 +995,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>80.45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>669.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>226</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1045,67 +1045,67 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>602.6</t>
+          <t>606.65</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>585.58</t>
+          <t>587.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>92.89</t>
+          <t>80.93</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>97.89473684210527</t>
+          <t>98.94736842105263</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>99.29824561403507</t>
+          <t>98.94736842105262</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>176.82</t>
+          <t>148.60</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1115,22 +1115,22 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>571420.4</t>
+          <t>998342.6</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>206423.0</t>
+          <t>401585.9</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>83874.56</t>
+          <t>184553.73</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>75.59</t>
+          <t>76.05</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>53479</t>
+          <t>53559</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1237,209 +1237,209 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3066</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8.93</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>866.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>17.35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>14.52</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4.41</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-3.12</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>14.51</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>14.977</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>149.71</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>125.07</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>4139.8</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>1839.3</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>1381.95</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3066</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>8.86</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>251.0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>李洲</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15.8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>9.27</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>-4.06</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>14.3575</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>14.965</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>54.97</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>86.66666666666659</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>194.17</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>1035.2</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>351.9</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>366.94</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>李洲</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AQ4" t="inlineStr">
         <is>
           <t>0.66</t>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>57.65</t>
+          <t>61.42</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2795.173</t>
+          <t>1425.421</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1529,17 +1529,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-13.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1584,62 +1584,62 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.6975</t>
+          <t>41.7775</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>41.15900000000001</t>
+          <t>41.192</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>71.66666666666664</t>
+          <t>54.99999999999997</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>720.74</t>
+          <t>1669.17</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1649,22 +1649,22 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>53252682.6</t>
+          <t>60502346.0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-8578904.1</t>
+          <t>-3855679.8</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-720</t>
+          <t>-1669</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2444729.25</t>
+          <t>-5354128.57</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1694,17 +1694,17 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>21.08</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>87377</t>
+          <t>86860</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2372.716</t>
+          <t>5023.864</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1796,17 +1796,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>278.0</t>
+          <t>284.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1816,134 +1816,134 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>5024</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>282.2</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>281.74</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-149.67</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>78.04878048780488</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>55.85735402808574</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>10677.47</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>427392893.0</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>-4040597.3</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>-10677</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>52325749.4</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2373</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>-1.98</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>281.875</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>281.45</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-218.38</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>46.34146341463415</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>37.4168514412417</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2864.45</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>424168056.2</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>-15343643.6</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>-2864</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>-58691857.63</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK6" t="inlineStr">
         <is>
           <t>技嘉</t>
@@ -1961,17 +1961,17 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>186229</t>
+          <t>190583</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3406.686</t>
+          <t>2941.673</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2063,17 +2063,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2083,27 +2083,27 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -2113,52 +2113,52 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.5775</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.2534</t>
+          <t>10.2764</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>112.24</t>
+          <t>120.43</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>112.75</t>
+          <t>181.65</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -2183,22 +2183,22 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>25412174.4</t>
+          <t>35633600.2</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>11944577.5</t>
+          <t>12651814.4</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>181</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4779477.86</t>
+          <t>5090826.13</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>219.0</t>
+          <t>223.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>163.82</t>
+          <t>168.56</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -2300,12 +2300,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>強勢股;建議關注股;多頭排列股</t>
+          <t>強勢股;多頭排列股</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2315,12 +2315,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>128300.961</t>
+          <t>69822.23</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2330,17 +2330,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>54.42</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2350,97 +2350,97 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>201</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>470</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>128301</t>
+          <t>69822</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>120.075</t>
+          <t>121.075</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>113.11</t>
+          <t>113.8</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>30.97</t>
+          <t>38.68</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>96.875</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>83.1688596491228</t>
+          <t>98.95833333333333</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>-187.36</t>
+          <t>39.04</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -2450,22 +2450,22 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-2659166418.2</t>
+          <t>164176828.2</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-925377316.6</t>
+          <t>118077697.5</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-991216135.21</t>
+          <t>31521060.78</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>311377</t>
+          <t>321912</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>214.451</t>
+          <t>389.873</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2632,14 +2632,14 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>價-量-</t>
@@ -2647,57 +2647,57 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>390</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.555</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.655</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>134.22</t>
+          <t>275.71</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>88.23529411764692</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>8886.86</t>
+          <t>13260.98</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2717,22 +2717,22 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2042695.6</t>
+          <t>5365363.6</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>22729.8</t>
+          <t>-40767.2</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>-13260</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>691592.79</t>
+          <t>1291242.23</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2762,17 +2762,17 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2864,17 +2864,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2889,27 +2889,27 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>65</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -2919,62 +2919,62 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>43</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>32.495</t>
+          <t>32.6425</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>30.605</t>
+          <t>30.686</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-7.43</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>76.92307692307709</t>
+          <t>53.84615384615309</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>86.75213675213674</t>
+          <t>76.92307692307672</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>26.96</t>
+          <t>17.03</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -2984,22 +2984,22 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1038.4</t>
+          <t>809.0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>817.9</t>
+          <t>691.3</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-6.9</t>
+          <t>-169.22</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2463</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6790.212</t>
+          <t>7354.77</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -3181,67 +3181,67 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>67</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>23.985</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>25.415</t>
+          <t>25.319</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>33.33333333333333</t>
+          <t>26.66666666666657</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>28.88888888888865</t>
+          <t>35.55555555555541</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>-88.53</t>
+          <t>-85.57</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -3251,22 +3251,22 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-177483720.2</t>
+          <t>-130643469.6</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-94140549.7</t>
+          <t>-70400439.9</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9213745.12</t>
+          <t>-658017.46</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>19.13</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>183871</t>
+          <t>183494</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA11"/>
+  <dimension ref="A1:BB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,160 +536,165 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>MA_short</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>VPC_MA_%</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>VPC_break</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change_sum</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>highlight_date</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
@@ -703,260 +708,265 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6789</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2014.787</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>14.83</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-2.34</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>234.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>232.6</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>230.075</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>222.83</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>5.48</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>71.42857142857143</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>63.8095238095238</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>-37.65</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>-110864984.4</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>-80541655.3</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>-15095374.03</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>6789</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5.24</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2626.905</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>238.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-3.93</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2627</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>229.8</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>222.43</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>68.33333333333333</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>579.55</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>57518307.0</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-11994339.2</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>-579</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>27012910.9</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
           <t>采鈺</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>半導體業</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>24.47%</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>13.31%</t>
+          <t>22.79%</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>53.88</t>
+          <t>12.35%</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75572</t>
+          <t>57.87</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>74302</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
           <t>影像感測器67.42%、微光學元件30.36%、其他2.22% (2024年)</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>采鈺-半導體業-上市</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>半導體業平</t>
-        </is>
-      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>57.75</t>
+          <t>半導體業右下</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
+        <is>
+          <t>55.59</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>** 半導體 - 生產製程及檢測設備</t>
         </is>
@@ -970,7 +980,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -980,12 +990,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2675.0</t>
+          <t>3459.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -995,17 +1005,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>80.45</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>669.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1015,215 +1025,220 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>221</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>80</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>8.90</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>606.65</t>
+          <t>665.2</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>587.5</t>
+          <t>610.85</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>80.93</t>
+          <t>589.5</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>70.10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>21.34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>98.94736842105263</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>98.94736842105262</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>148.60</t>
-        </is>
-      </c>
       <c r="AD3" t="inlineStr">
         <is>
+          <t>105.06</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>998342.6</t>
-        </is>
-      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>401585.9</t>
+          <t>1320522.6</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>643974.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>184553.73</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
+          <t>288058.71</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
           <t>譜瑞-KY</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>半導體業</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>53.52</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>42.56%</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>15.83%</t>
+          <t>43.11%</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>76.05</t>
+          <t>17.22%</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>53559</t>
+          <t>77.36</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>54199</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>高速訊號傳輸介面晶片44.78%、DisplayPort系列(DP)38.99%、Source Drivers12.74%、TrueTouch系列3.49% (2024年)</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>譜瑞-KY-半導體業-上櫃</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>285.42</t>
-        </is>
-      </c>
       <c r="BA3" t="inlineStr">
+        <is>
+          <t>252.85</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>** 半導體 - 平面顯示器驅動IC</t>
         </is>
@@ -1237,7 +1252,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1247,12 +1262,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>866.0</t>
+          <t>1571.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1262,17 +1277,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-6.73</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1287,210 +1302,215 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>14.51</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>14.977</t>
+          <t>14.605</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>149.71</t>
+          <t>14.982</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>265.35</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.01449275362319</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>125.07</t>
+          <t>90.33816425120771</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
+          <t>-62.71</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>4139.8</t>
-        </is>
-      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>1839.3</t>
+          <t>-1278.6</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>-785.8</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1381.95</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
+          <t>-1064.42</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
           <t>李洲</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>30.44</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
+          <t>28.68</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
           <t>32.58%</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>-34.62%</t>
         </is>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>61.42</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>LED 光電產品93.51%、磊晶片6.32%、其他0.17% (2024年)</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>李洲-光電業-上櫃</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>13.27</t>
         </is>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>** LED照明產業 - 封裝/模組、燈具/應用</t>
         </is>
@@ -1504,7 +1524,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1514,12 +1534,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1425.421</t>
+          <t>1194.184</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1529,17 +1549,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1549,215 +1569,220 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.7775</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>41.192</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>41.233</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>12.83</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>54.99999999999997</t>
+          <t>54.99999999999972</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1669.17</t>
+          <t>55.83333333333326</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
+          <t>300.10</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>60502346.0</t>
-        </is>
-      </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-3855679.8</t>
+          <t>40039858.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-1669</t>
+          <t>10007519.7</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-5354128.57</t>
+          <t>300</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
+          <t>-2416861.81</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
           <t>興富發</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>建材營造</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>5.96</t>
-        </is>
-      </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>0.55</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>14.82</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
+          <t>14.86</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
           <t>39.21%</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
         <is>
           <t>-5.55%</t>
         </is>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>21.08</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>86860</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>87067</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>建設業務99.44%、百貨0.38%、營造0.18% (2024年)</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>興富發-建材營造-上市</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>建材營造平</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>26.04</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>** 建材營造 - 建設業</t>
         </is>
@@ -1771,7 +1796,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1781,12 +1806,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5023.864</t>
+          <t>2430.169</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1796,17 +1821,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>284.5</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1816,215 +1841,220 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>73</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>282.2</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>281.74</t>
+          <t>282.475</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-149.67</t>
+          <t>281.94</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-27.23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>78.04878048780488</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>55.85735402808574</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>10677.47</t>
+          <t>74.79674796747967</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
+          <t>145.38</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>427392893.0</t>
-        </is>
-      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-4040597.3</t>
+          <t>349901474.2</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-10677</t>
+          <t>142596461.8</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>52325749.4</t>
+          <t>145</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
+          <t>74133879.71</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>技嘉</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>98.15</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>17.52</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
+          <t>17.61</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
           <t>12.90%</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AU6" t="inlineStr">
         <is>
           <t>6.45%</t>
         </is>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>190583</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>191588</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>網路通訊產品64.27%、電腦配件31.22%、其他4.51% (2024年)</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>技嘉-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>85.03</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、主機板、機殼、電源供應器、散熱片、風扇馬達、散熱模組、顯示卡、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
@@ -2033,12 +2063,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>強勢股;多頭排列股</t>
+          <t>多頭排列股</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2048,12 +2078,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2941.673</t>
+          <t>4200.948</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2063,17 +2093,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2083,12 +2113,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -2098,200 +2128,205 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10.5775</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.2764</t>
+          <t>10.5825</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>120.43</t>
+          <t>10.2988</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>100.47</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.73684210526308</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>181.65</t>
+          <t>98.24561403508767</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>151.42</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>35633600.2</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>12651814.4</t>
+          <t>22810963.4</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>9072737.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5090826.13</t>
+          <t>151</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
+          <t>-784916.11</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>錸德</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>2.42</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>223.0</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
+          <t>222.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
           <t>13.42%</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AU7" t="inlineStr">
         <is>
           <t>0.33%</t>
         </is>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>168.56</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>166.48</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>7700</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>光學產品84.42%、其他15.58% (2024年)</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>錸德-光電業-上市</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>光電業平</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>8.25</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 光碟片</t>
         </is>
@@ -2305,7 +2340,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2315,12 +2350,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>69822.23</t>
+          <t>38130.566</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2330,17 +2365,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>54.42</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2350,215 +2385,220 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>184</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>-10.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>-17.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>69822</t>
+          <t>38131</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>121.075</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>113.8</t>
+          <t>122.025</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>114.51</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>98.95833333333333</t>
+          <t>97.2972972972973</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>98.05743243243244</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
+          <t>-188.99</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>164176828.2</t>
-        </is>
-      </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>118077697.5</t>
+          <t>-1399362894.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-484229741.9</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>31521060.78</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
+          <t>-370142034.99</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
           <t>光寶科</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>17.81</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>23.91</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
+          <t>23.83</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
           <t>22.12%</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AU8" t="inlineStr">
         <is>
           <t>9.22%</t>
         </is>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>321912</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>320741</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
           <t>資訊及消費性電子43.00%、雲端及物聯網37.00%、光電通訊20.00% (2024年)</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>光寶科-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右上</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>35.46</t>
         </is>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>** 汽車 - 銷售、進出口業務、車燈、其他** 電腦及週邊設備 - 機殼、電源供應器、伺服器、其他電腦及週邊設備、安全監控系統** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 其他 - 其他電子產品及電子服務產業** 雲端運算 - 電力設備、冷卻設備、雲端應用服務、系統整合、顧問諮詢、設備安裝服務、IaaS、PaaS、SaaS** 體驗科技 - 環境感知、深度感測、視覺、手勢/動作** LED照明產業 - 封裝/模組、燈具/應用** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 智慧電網 - 配電管理設施** 醫療器材 - 醫療耗材、生物檢測</t>
         </is>
@@ -2572,7 +2612,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2582,12 +2622,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>389.873</t>
+          <t>353.723</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2597,17 +2637,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2617,12 +2657,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2632,7 +2672,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2647,185 +2687,190 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>354</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>24.555</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>24.5975</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>275.71</t>
+          <t>24.637</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1742.12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>90.19607843137256</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>13260.98</t>
+          <t>96.07843137254896</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
+          <t>389.45</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>5365363.6</t>
-        </is>
-      </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-40767.2</t>
+          <t>5689948.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>-13260</t>
+          <t>1162522.9</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1291242.23</t>
+          <t>389</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
+          <t>1618167.38</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
           <t>橋椿</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>居家生活</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>12.06%</t>
+          <t>20.36</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>5050</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
           <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>橋椿-居家生活-上市</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>居家生活平</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>38.74</t>
-        </is>
-      </c>
       <c r="BA9" t="inlineStr">
+        <is>
+          <t>35.8</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
         <is>
           <t>** 其他 - 其他</t>
         </is>
@@ -2839,7 +2884,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2849,12 +2894,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2864,17 +2909,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>34.36</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2884,7 +2929,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2894,205 +2939,210 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>67</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>67</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>32.6425</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>30.686</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-7.43</t>
+          <t>30.772</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-7.71</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>53.84615384615309</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>76.92307692307672</t>
+          <t>92.30769230769164</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t>74.35897435897394</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
+          <t>-18.40</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>809.0</t>
-        </is>
-      </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>691.3</t>
+          <t>604.2</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>740.4</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-169.22</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
+          <t>-5.77</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>宏佳騰</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>6.95</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>19.44</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
+          <t>33.98</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
           <t>21.60%</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AU10" t="inlineStr">
         <is>
           <t>-2.75%</t>
         </is>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>40.6</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>2482</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
           <t>ATV/ UTV64.10%、摩托車14.76%、電動車輛13.19%、零組件及其他7.95% (2024年)</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>宏佳騰-電機機械-上櫃</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>電機機械平</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>26.82</t>
         </is>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
         </is>
@@ -3106,7 +3156,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3116,12 +3166,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7354.77</t>
+          <t>9677.836</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3131,17 +3181,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3151,7 +3201,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -3161,205 +3211,210 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>9678</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>-4.75</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>24.02</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>25.219</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>38.15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>33.33333333333333</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>31.11111111111106</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>-22.91</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>-27440071.4</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>-22324619.6</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>-6.0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>7355</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>-5.27</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>23.985</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>25.319</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>37.35</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>26.66666666666657</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>35.55555555555541</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>-85.57</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>-130643469.6</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>-70400439.9</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-658017.46</t>
-        </is>
-      </c>
       <c r="AI11" t="inlineStr">
         <is>
+          <t>23596915.23</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
           <t>台泥</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>水泥工業</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>4.12</t>
-        </is>
-      </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>4.52</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>19.13</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
+          <t>19.17</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
           <t>16.86%</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AU11" t="inlineStr">
         <is>
           <t>6.58%</t>
         </is>
       </c>
-      <c r="AU11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>16.75</t>
         </is>
       </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>183494</t>
-        </is>
-      </c>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>183871</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
           <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>台泥-水泥工業-上市</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>水泥工業右下</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>33.02</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -703,12 +703,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>強勢股;建議關注股;多頭排列股</t>
+          <t>弱勢突破股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2014.787</t>
+          <t>1365.734</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -733,17 +733,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>231.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -758,22 +758,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -783,72 +783,72 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>37</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>232.6</t>
+          <t>232.4</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>230.075</t>
+          <t>230.6</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>222.83</t>
+          <t>223.4</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>71.42857142857143</t>
+          <t>53.57142857142857</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>63.8095238095238</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-37.65</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -858,22 +858,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-110864984.4</t>
+          <t>-113615983.2</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-80541655.3</t>
+          <t>-97905042.1</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-15095374.03</t>
+          <t>-32163333.88</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>43.84</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>57.87</t>
+          <t>58.31</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>74302</t>
+          <t>73508</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3459.0</t>
+          <t>2768.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1005,17 +1005,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1030,82 +1030,82 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>257</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>8.90</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>665.2</t>
+          <t>679.8</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>610.85</t>
+          <t>617.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>589.5</t>
+          <t>592.86</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>70.10</t>
+          <t>71.42</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21.34</t>
+          <t>26.18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1115,12 +1115,12 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>98.94736842105262</t>
+          <t>99.64912280701753</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>105.06</t>
+          <t>71.54</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1130,22 +1130,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1320522.6</t>
+          <t>1458162.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>643974.0</t>
+          <t>850019.6</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>288058.71</t>
+          <t>324971.6</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>77.36</t>
+          <t>73.14</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>54199</t>
+          <t>57241</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1571.0</t>
+          <t>481.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-6.73</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1302,97 +1302,97 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-10.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>481</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>16.02</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>14.605</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>14.982</t>
+          <t>14.992</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>265.35</t>
+          <t>704.77</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>71.01449275362319</t>
+          <t>66.66666666666661</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>90.33816425120771</t>
+          <t>79.22705314009659</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-62.71</t>
+          <t>-91.27</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1402,22 +1402,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-1278.6</t>
+          <t>-2962.2</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-785.8</t>
+          <t>-1548.7</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1064.42</t>
+          <t>-1342.74</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>60.23</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>強勢股;多頭排列股</t>
+          <t>強勢股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1194.184</t>
+          <t>2408.565</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1579,17 +1579,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1599,47 +1599,47 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>41</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.825</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.233</t>
+          <t>41.277</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>12.83</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1654,17 +1654,17 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>54.99999999999972</t>
+          <t>57.49999999999993</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>55.83333333333326</t>
+          <t>54.16666666666657</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>300.10</t>
+          <t>-95.89</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1674,22 +1674,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>40039858.0</t>
+          <t>1360548.8</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>10007519.7</t>
+          <t>33106057.4</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>-95</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2416861.81</t>
+          <t>3500769.69</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>16.83</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>87067</t>
+          <t>87170</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1791,54 +1791,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>強勢股;多頭排列股</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4468.186</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2430.169</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>289.5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>6.83</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>286.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1846,82 +1846,82 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>112</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>283.2</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>282.475</t>
+          <t>283.125</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>281.94</t>
+          <t>282.41</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-27.23</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>74.79674796747967</t>
+          <t>92.6829268292683</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>145.38</t>
+          <t>268.67</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1946,32 +1946,32 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>349901474.2</t>
+          <t>724485900.2</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>142596461.8</t>
+          <t>196513695.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>74133879.71</t>
+          <t>131957452.94</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>191588</t>
+          <t>193933</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2063,12 +2063,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>多頭排列股</t>
+          <t>強勢股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4200.948</t>
+          <t>10034.236</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2118,47 +2118,47 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>58</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -2168,37 +2168,37 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.5825</t>
+          <t>10.6325</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>10.2988</t>
+          <t>10.3484</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>100.47</t>
+          <t>128.31</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>94.73684210526308</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>151.42</t>
+          <t>96.44</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2218,64 +2218,64 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>22810963.4</t>
+          <t>37833804.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>9072737.0</t>
+          <t>19259990.5</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-784916.11</t>
+          <t>7748143.85</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>錸德</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>錸德</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR7" t="inlineStr">
         <is>
           <t>2.42</t>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>222.0</t>
+          <t>244.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>166.48</t>
+          <t>142.99</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>光電業平</t>
+          <t>光電業右上</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2335,12 +2335,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>強勢股;多頭排列股</t>
+          <t>強勢股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>38130.566</t>
+          <t>39908.762</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2365,17 +2365,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>31.11</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2390,97 +2390,97 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>115</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-17.0</t>
+          <t>-69.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>38131</t>
+          <t>39909</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>122.025</t>
+          <t>123.275</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>114.51</t>
+          <t>115.3</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>37.88</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>97.2972972972973</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>98.05743243243244</t>
+          <t>99.09909909909909</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-188.99</t>
+          <t>113.84</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-1399362894.0</t>
+          <t>44538309.4</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-484229741.9</t>
+          <t>-321768968.7</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>-113</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-370142034.99</t>
+          <t>167741004.87</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>320741</t>
+          <t>328936</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2607,12 +2607,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>反彈型股</t>
+          <t>強勢股</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>353.723</t>
+          <t>247.395</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2637,17 +2637,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2662,72 +2662,72 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>247</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.5975</t>
+          <t>24.6125</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>24.637</t>
+          <t>24.643</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1742.12</t>
+          <t>558.00</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2737,22 +2737,22 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>68.1818181818181</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>96.07843137254896</t>
+          <t>89.39393939393938</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>389.45</t>
+          <t>151.31</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2762,22 +2762,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>5689948.0</t>
+          <t>2250111.2</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>1162522.9</t>
+          <t>895351.6</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>151</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1618167.38</t>
+          <t>670498.53</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>20.36</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2909,17 +2909,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>34.36</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2934,134 +2934,134 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>6.37</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>33.03</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>30.836</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>-17.75</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>48.71794871794824</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>-56.09</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>205.8</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>468.7</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>-56</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>-147.19</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>6.46</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>33.18</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>32.76</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>30.772</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>-7.71</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>92.30769230769164</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>74.35897435897394</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>-18.40</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>604.2</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>740.4</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-18</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-5.77</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AL10" t="inlineStr">
         <is>
           <t>宏佳騰</t>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -3089,37 +3089,37 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>32.91</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>21.60%</t>
+          <t>20.81%</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>-4.48%</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9677.836</t>
+          <t>15471.976</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>13.03</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3206,97 +3206,97 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>127</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>15472</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>24.08</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>25.219</t>
+          <t>25.157</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>43.87</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>33.33333333333333</t>
+          <t>64.28571428571443</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>31.11111111111106</t>
+          <t>41.42857142857142</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-22.91</t>
+          <t>578.39</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-27440071.4</t>
+          <t>116362112.8</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-22324619.6</t>
+          <t>-24323713.1</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-578</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>23596915.23</t>
+          <t>50848804.1</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>19.37</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.76</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>183871</t>
+          <t>185759</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -703,12 +703,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>弱勢突破股;建議關注股;多頭排列股</t>
+          <t>強勢股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1365.734</t>
+          <t>2298.438</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -733,17 +733,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>231.5</t>
+          <t>240.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -763,92 +763,92 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>54</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>74</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>232.4</t>
+          <t>237.7</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>230.6</t>
+          <t>231.95</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>223.4</t>
+          <t>224.83</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>31.77</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>53.57142857142857</t>
+          <t>78.37837837837837</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.3166023166023</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>222.65</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -858,32 +858,32 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-113615983.2</t>
+          <t>37359743.4</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-97905042.1</t>
+          <t>-30461316.7</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-222</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-32163333.88</t>
+          <t>-6468564.87</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>43.84</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>61.83</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>73508</t>
+          <t>76365</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>半導體業右下</t>
+          <t>半導體業平</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2768.0</t>
+          <t>5905.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1005,17 +1005,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1030,17 +1030,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>229</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1050,62 +1050,62 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>148</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>679.8</t>
+          <t>720.8</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>617.7</t>
+          <t>636.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>592.86</t>
+          <t>601.78</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>71.42</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>26.18</t>
+          <t>40.26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1115,12 +1115,12 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>99.64912280701753</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>69.20</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1130,22 +1130,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1458162.0</t>
+          <t>3138685.4</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>850019.6</t>
+          <t>1855052.9</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>324971.6</t>
+          <t>704181.58</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>73.14</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>57241</t>
+          <t>62685</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>半導體業右下</t>
+          <t>半導體業平</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1247,12 +1247,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>反彈型股</t>
+          <t>強勢股</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>481.0</t>
+          <t>2834.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1302,122 +1302,122 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>15.0575</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>14.992</t>
+          <t>15.096</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>704.77</t>
+          <t>271.70</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>66.66666666666661</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>79.22705314009659</t>
+          <t>88.88888888888886</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-91.27</t>
+          <t>80.10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-2962.2</t>
+          <t>9366.4</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-1548.7</t>
+          <t>5200.8</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1342.74</t>
+          <t>4069.49</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1462,32 +1462,32 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>32.58%</t>
+          <t>15.96%</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>-34.62%</t>
+          <t>-47.47%</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>60.23</t>
+          <t>74.33</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>強勢股;建議關注股;多頭排列股</t>
+          <t>弱勢突破股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2408.565</t>
+          <t>2566.11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1589,62 +1589,62 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>57</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>41.825</t>
+          <t>41.88</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.277</t>
+          <t>41.356</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1654,17 +1654,17 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>57.49999999999993</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>54.16666666666657</t>
+          <t>39.16666666666659</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-95.89</t>
+          <t>-51.55</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1674,22 +1674,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>1360548.8</t>
+          <t>17022899.4</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>33106057.4</t>
+          <t>35137791.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-95</t>
+          <t>-51</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3500769.69</t>
+          <t>-5395604.48</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>16.83</t>
+          <t>16.23</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>87170</t>
+          <t>86446</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1796,182 +1796,182 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6484.95</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>18.22</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.39</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>287.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>6485</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>286.5</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>283.35</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>282.47</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>77.91</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>84.375</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>86.45833333333333</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>35.15</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>883895078.8</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>654031567.5</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>126387583.78</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4468.186</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>289.5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>4468</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>283.2</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>283.125</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>282.41</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>88.48</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>92.6829268292683</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>268.67</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>724485900.2</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>196513695.0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>131957452.94</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>17.83</t>
+          <t>17.67</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>193933</t>
+          <t>192258</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2068,182 +2068,182 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2349</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-2.47</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>9821.082</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-4.20</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11.85</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>9821</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>8.64</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>11.69</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>10.76</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>10.4372</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>83.67</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>82.05128205128206</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>93.1837606837607</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>-346.58</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>-46023957.2</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>-10305891.4</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-17893076.25</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2349</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>9.69</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>10034.236</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>7.49</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>10034</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>8.35</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>5.90</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>11.26</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>10.6325</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>10.3484</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>128.31</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>98.24561403508767</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>96.44</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>37833804.0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>19259990.5</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>7748143.85</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>142.99</t>
+          <t>198.55</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>光電業右上</t>
+          <t>光電業平</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>39908.762</t>
+          <t>35544.365</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2365,17 +2365,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2390,97 +2390,97 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>79</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-69.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>407</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>39909</t>
+          <t>35544</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>137.9</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>123.275</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>115.3</t>
+          <t>116.61</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.57894736842105</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>99.09909909909909</t>
+          <t>89.20848633210933</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>113.84</t>
+          <t>119.82</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>44538309.4</t>
+          <t>239726345.2</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-321768968.7</t>
+          <t>-1209720036.5</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-113</t>
+          <t>-119</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>167741004.87</t>
+          <t>-464869121.38</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>23.83</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>328936</t>
+          <t>320741</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2607,12 +2607,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>強勢股</t>
+          <t>強勢股;多頭排列股</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>247.395</t>
+          <t>385.129</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2637,122 +2637,122 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>24.75</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-0.60</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.6125</t>
+          <t>24.6475</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>24.643</t>
+          <t>24.642</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>558.00</t>
+          <t>84.47</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>68.1818181818181</t>
+          <t>41.17647058823539</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>89.39393939393938</t>
+          <t>47.0588235294118</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>151.31</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2762,22 +2762,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2250111.2</t>
+          <t>2557331.6</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>895351.6</t>
+          <t>2300013.6</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>670498.53</t>
+          <t>534734.21</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2879,12 +2879,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>建議關注股;多頭排列股</t>
+          <t>建議關注股</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2909,17 +2909,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>64</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2949,67 +2949,67 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>-27.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>32.805</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>30.836</t>
+          <t>30.969</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-17.75</t>
+          <t>-30.39</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>48.71794871794824</t>
+          <t>10.60606060606064</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-56.09</t>
+          <t>-52.80</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3034,22 +3034,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>205.8</t>
+          <t>320.8</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>468.7</t>
+          <t>679.6</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-56</t>
+          <t>-52</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-147.19</t>
+          <t>-61.24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>34.51</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15471.976</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3206,97 +3206,97 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>-34.0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>127</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>15472</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>24.2375</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>25.157</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>43.87</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>64.28571428571443</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>41.42857142857142</t>
+          <t>88.09523809523813</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>578.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>116362112.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-24323713.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-578</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>50848804.1</t>
+          <t>69390494.11</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>17.58</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>185759</t>
+          <t>186892</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2298.438</t>
+          <t>1442.82</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -733,17 +733,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>240.5</t>
+          <t>241.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -768,14 +768,14 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>價-量-</t>
@@ -783,72 +783,72 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>237.7</t>
+          <t>238.4</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>231.95</t>
+          <t>232.2</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>224.83</t>
+          <t>225.5</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>31.77</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>78.37837837837837</t>
+          <t>83.78378378378379</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>77.3166023166023</t>
+          <t>87.38738738738738</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>222.65</t>
+          <t>-190.58</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -858,22 +858,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>37359743.4</t>
+          <t>-17930057.2</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-30461316.7</t>
+          <t>19794124.9</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-222</t>
+          <t>-190</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6468564.87</t>
+          <t>23209164.41</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>61.83</t>
+          <t>64.44</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>76365</t>
+          <t>76683</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5905.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1005,17 +1005,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>88.61</t>
+          <t>48.08</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>794.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1030,82 +1030,82 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>236</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>69</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>720.8</t>
+          <t>745.8</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>636.2</t>
+          <t>645.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>601.78</t>
+          <t>606.42</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>66.37</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.26</t>
+          <t>46.17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>69.20</t>
+          <t>53.38</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1130,22 +1130,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3138685.4</t>
+          <t>3284213.6</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1855052.9</t>
+          <t>2141278.1</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>704181.58</t>
+          <t>621498.63</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.56</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>62685</t>
+          <t>63566</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1247,12 +1247,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>強勢股</t>
+          <t>強勢股;多頭排列股</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2834.0</t>
+          <t>577.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1302,82 +1302,82 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>577</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>14.23</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>15.0575</t>
+          <t>15.2525</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>15.096</t>
+          <t>15.154</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>271.70</t>
+          <t>167.83</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1387,37 +1387,37 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>88.88888888888886</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>80.10</t>
+          <t>34.31</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>9366.4</t>
+          <t>8464.8</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5200.8</t>
+          <t>6302.3</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4069.49</t>
+          <t>3559.2</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>74.33</t>
+          <t>87.44</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>弱勢突破股;建議關注股;多頭排列股</t>
+          <t>強勢股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2566.11</t>
+          <t>3251.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1589,62 +1589,62 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>48</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>41.88</t>
+          <t>41.9075</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.356</t>
+          <t>41.398</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1654,17 +1654,17 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>45.83333333333299</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>39.16666666666659</t>
+          <t>35.27777777777761</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-51.55</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1674,32 +1674,32 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>17022899.4</t>
+          <t>56501052.6</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>35137791.0</t>
+          <t>58501699.3</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-51</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5395604.48</t>
+          <t>4013805.82</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1719,47 +1719,47 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>39.21%</t>
+          <t>20.37%</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>-5.55%</t>
+          <t>7.22%</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>16.23</t>
+          <t>17.06</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>86446</t>
+          <t>87584</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6484.95</t>
+          <t>4356.952</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1821,17 +1821,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>287.0</t>
+          <t>282.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1846,97 +1846,97 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>98</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>286.5</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>283.35</t>
+          <t>283.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>282.47</t>
+          <t>282.36</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>77.91</t>
+          <t>36.52</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>84.375</t>
+          <t>53.125</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>86.45833333333333</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1946,22 +1946,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>883895078.8</t>
+          <t>352723405.2</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>654031567.5</t>
+          <t>390058149.1</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>126387583.78</t>
+          <t>-27135058.26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>192258</t>
+          <t>188908</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9821.082</t>
+          <t>9249.063</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -2128,42 +2128,42 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-14.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -2173,42 +2173,42 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>10.7775</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>10.4372</t>
+          <t>10.463</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>83.67</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>82.05128205128206</t>
+          <t>34.37500000000005</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>93.1837606837607</t>
+          <t>71.30876068376071</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-346.58</t>
+          <t>-289.92</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2218,22 +2218,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-46023957.2</t>
+          <t>-73157831.8</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-10305891.4</t>
+          <t>-18762115.8</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-17893076.25</t>
+          <t>-20511985.02</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>198.55</t>
+          <t>197.81</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35544.365</t>
+          <t>32354.032</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2365,17 +2365,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2390,97 +2390,97 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>73</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>551</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>35544</t>
+          <t>32354</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>137.9</t>
+          <t>136.9</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>126.175</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>116.61</t>
+          <t>117.14</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>81.57894736842105</t>
+          <t>57.89473684210527</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>89.20848633210933</t>
+          <t>75.1733986128111</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>119.82</t>
+          <t>-113.80</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>239726345.2</t>
+          <t>-2542698055.6</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-1209720036.5</t>
+          <t>-1189260613.7</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-119</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-464869121.38</t>
+          <t>-623655612.91</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>320741</t>
+          <t>310206</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2607,12 +2607,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>強勢股;多頭排列股</t>
+          <t>強勢股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>385.129</t>
+          <t>294.808</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2637,17 +2637,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2662,12 +2662,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2687,72 +2687,72 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>295</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.89</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.6475</t>
+          <t>24.6825</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>24.642</t>
+          <t>24.647</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>84.47</t>
+          <t>91.66</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>41.17647058823539</t>
+          <t>73.33333333333343</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>47.0588235294118</t>
+          <t>48.77599524658357</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>-44.07</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2762,22 +2762,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2557331.6</t>
+          <t>2082672.2</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2300013.6</t>
+          <t>3724017.9</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-44</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>534734.21</t>
+          <t>906637.06</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2909,17 +2909,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>28.72</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2934,27 +2934,27 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>73</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-27.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -2964,52 +2964,52 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>56</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>32.45</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>32.805</t>
+          <t>32.76000000000001</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>30.969</t>
+          <t>31.028</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-30.39</t>
+          <t>-38.31</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-52.80</t>
+          <t>-52.79</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>320.8</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>679.6</t>
+          <t>529.5</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-61.24</t>
+          <t>-224.95</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>32.76</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34.51</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73515.862</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.91</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3216,82 +3216,82 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-34.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>641</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73516</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>24.2375</t>
+          <t>24.245</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>24.996</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>37.88</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>88.09523809523813</t>
+          <t>66.66666666666664</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>69390494.11</t>
+          <t>-120717316.31</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -3356,42 +3356,42 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>23.11</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>16.86%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>6.58%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>31.51</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>186892</t>
+          <t>179718</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1442.82</t>
+          <t>1275.17</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -733,17 +733,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>241.5</t>
+          <t>239.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -758,97 +758,97 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>36</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-18.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>238.4</t>
+          <t>239.4</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>232.2</t>
+          <t>232.5</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>225.5</t>
+          <t>226.04</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>24.16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>83.78378378378379</t>
+          <t>70.27027027027027</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>87.38738738738738</t>
+          <t>77.47747747747748</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-190.58</t>
+          <t>133.06</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -858,22 +858,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-17930057.2</t>
+          <t>15724902.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>19794124.9</t>
+          <t>-47570041.2</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-190</t>
+          <t>-133</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>23209164.41</t>
+          <t>-5579070.89</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>45.27</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>64.44</t>
+          <t>64.13</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>76683</t>
+          <t>75889</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>4484.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1005,17 +1005,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>48.08</t>
+          <t>67.29</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>794.0</t>
+          <t>836.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1030,82 +1030,82 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>203</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>-33.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>166</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>18.29</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>745.8</t>
+          <t>777.6</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>645.8</t>
+          <t>657.35</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>606.42</t>
+          <t>611.78</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>66.37</t>
+          <t>62.86</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>53.62</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>32.93</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>45.93</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1130,22 +1130,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3284213.6</t>
+          <t>3563842.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2141278.1</t>
+          <t>2442182.3</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>621498.63</t>
+          <t>636014.07</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>22.56</t>
+          <t>23.76</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.62</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>63566</t>
+          <t>66928</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>577.0</t>
+          <t>341.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1302,97 +1302,97 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>341</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.82</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>15.2525</t>
+          <t>15.445</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>15.154</t>
+          <t>15.202</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>167.83</t>
+          <t>112.13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.47619047619044</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.8253968253968</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>34.31</t>
+          <t>122.69</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1402,22 +1402,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>8464.8</t>
+          <t>12549.6</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6302.3</t>
+          <t>5635.5</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3559.2</t>
+          <t>1860.6</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>87.44</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1524,182 +1524,182 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2918.529</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7.01</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>42.35</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2919</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>42.13</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>41.9325</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>41.425</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>7.73</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>48.61111111111101</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>27.97</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>71130112.6</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>55584985.3</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>9444251.96</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3251.12</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>7.81</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>3251</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>42.07</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>41.9075</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>41.398</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>45.83333333333299</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>35.27777777777761</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>-3.42</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>56501052.6</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>58501699.3</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>4013805.82</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>15.44</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>17.06</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>87584</t>
+          <t>87688</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>強勢股;多頭排列股</t>
+          <t>弱勢突破股;多頭排列股</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4356.952</t>
+          <t>6045.39</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1821,17 +1821,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>282.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1851,92 +1851,92 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>47</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>111</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>284.6</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>283.1</t>
+          <t>282.575</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>282.36</t>
+          <t>282.18</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.52</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>53.125</t>
+          <t>8.695652173913043</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>48.73188405797102</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-212.20</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1946,22 +1946,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>352723405.2</t>
+          <t>-125748347.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>390058149.1</t>
+          <t>112076563.6</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-212</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-27135058.26</t>
+          <t>-168756111.58</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1991,47 +1991,47 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>152.65</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>12.90%</t>
+          <t>9.42%</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>6.45%</t>
+          <t>5.18%</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>188908</t>
+          <t>186899</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>85.03</t>
+          <t>77.62</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9249.063</t>
+          <t>3959.401</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2123,92 +2123,92 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-14.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-4.70</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.7775</t>
+          <t>10.805</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>10.463</t>
+          <t>10.4886</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>25.50</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>34.37500000000005</t>
+          <t>19.23076923076924</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>71.30876068376071</t>
+          <t>45.2190170940171</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-289.92</t>
+          <t>-191.81</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2218,22 +2218,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-73157831.8</t>
+          <t>-72500299.6</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-18762115.8</t>
+          <t>-24844668.1</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>191</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-20511985.02</t>
+          <t>-17377059.36</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -2288,17 +2288,17 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>13.42%</t>
+          <t>14.57%</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>197.81</t>
+          <t>151.46</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32354.032</t>
+          <t>24024.659</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2365,17 +2365,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2390,97 +2390,97 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>71</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>382</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>32354</t>
+          <t>24025</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>136.9</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>126.175</t>
+          <t>127.075</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>117.14</t>
+          <t>117.7</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>57.89473684210527</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>75.1733986128111</t>
+          <t>52.74122807017543</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-113.80</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-2542698055.6</t>
+          <t>-845843449.4</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-1189260613.7</t>
+          <t>-1122603171.7</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-623655612.91</t>
+          <t>-156276245.48</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>310206</t>
+          <t>313718</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>294.808</t>
+          <t>770.414</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2637,17 +2637,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2672,112 +2672,112 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>770</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>24.98</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>24.7475</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>24.664</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>138.42</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>24.89</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>24.6825</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>24.647</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>91.66</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>73.33333333333343</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>48.77599524658357</t>
+          <t>71.50326797385627</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-44.07</t>
+          <t>-14.67</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2082672.2</t>
+          <t>4234068.4</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3724017.9</t>
+          <t>4962008.2</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-44</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>906637.06</t>
+          <t>2068525.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2894,174 +2894,174 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>13.33</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>-0.31</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>28.72</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-0.92</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>32.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-25.0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-1.59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>-1.77</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>5.18</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>32.11</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>32.69</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>31.081</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>-50.26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>-395.65</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>-360.4</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>121.9</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>-395</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>-263.42</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>-1.39</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>5.58</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>32.45</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>32.76000000000001</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>31.028</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>-38.31</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>10.60606060606064</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>-52.79</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>250.0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>529.5</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-52</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-224.95</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AL10" t="inlineStr">
         <is>
           <t>宏佳騰</t>
@@ -3079,17 +3079,17 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.24</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3166,162 +3166,162 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>35558.069</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>29.94</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>73515.862</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>61.91</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>35558</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>-2.65</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>24.2575</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>24.919</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>17.52</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>33.33333333333331</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>73516</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-2.66</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>-3.00</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>24.245</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>24.996</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>37.88</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>66.66666666666664</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-120717316.31</t>
+          <t>-144770357.77</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -3351,47 +3351,47 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>23.11</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>31.51</t>
+          <t>31.57</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>179718</t>
+          <t>178963</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1275.17</t>
+          <t>2333.325</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -733,17 +733,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>239.0</t>
+          <t>247.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -758,97 +758,97 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-18.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>57</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>239.4</t>
+          <t>242.6</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>232.5</t>
+          <t>233.225</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>226.04</t>
+          <t>226.76</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>24.16</t>
+          <t>32.91</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>70.27027027027027</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>77.47747747747748</t>
+          <t>84.68468468468468</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>133.06</t>
+          <t>387.34</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -858,22 +858,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15724902.0</t>
+          <t>192697164.2</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-47570041.2</t>
+          <t>39540590.5</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-133</t>
+          <t>387</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5579070.89</t>
+          <t>40183085.05</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>45.27</t>
+          <t>46.88</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>64.13</t>
+          <t>63.71</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>75889</t>
+          <t>78588</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4484.0</t>
+          <t>3575.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1005,17 +1005,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>67.29</t>
+          <t>53.65</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>836.0</t>
+          <t>810.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1030,122 +1030,122 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>169</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-33.0</t>
+          <t>-34.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>104</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>18.29</t>
+          <t>19.30</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>777.6</t>
+          <t>796.6</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>657.35</t>
+          <t>667.75</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>611.78</t>
+          <t>616.68</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>62.86</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>56.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>37.70</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.52380952380952</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.84126984126982</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>45.93</t>
+          <t>27.94</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3563842.0</t>
+          <t>2588930.8</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2442182.3</t>
+          <t>2023546.4</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>636014.07</t>
+          <t>131483.05</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>23.76</t>
+          <t>23.02</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>66928</t>
+          <t>64847</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>341.0</t>
+          <t>316.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1302,97 +1302,97 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-15.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>316</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>17.82</t>
+          <t>18.12</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>15.445</t>
+          <t>15.61</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>15.202</t>
+          <t>15.238</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>112.13</t>
+          <t>74.87</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>90.47619047619044</t>
+          <t>67.85714285714279</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>96.8253968253968</t>
+          <t>86.11111111111107</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>122.69</t>
+          <t>159.07</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1402,22 +1402,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>12549.6</t>
+          <t>12991.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5635.5</t>
+          <t>5014.4</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>159</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1860.6</t>
+          <t>666.31</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2918.529</t>
+          <t>6619.606</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1574,84 +1574,84 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>57</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.13</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>41.9325</t>
+          <t>41.9675</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.425</t>
+          <t>41.473</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
       <c r="AB5" t="inlineStr">
         <is>
           <t>100.0</t>
@@ -1659,37 +1659,37 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>48.61111111111101</t>
+          <t>81.94444444444434</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>27.97</t>
+          <t>97.51</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>71130112.6</t>
+          <t>107776567.6</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>55584985.3</t>
+          <t>54568558.2</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>9444251.96</t>
+          <t>25067104.31</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>87688</t>
+          <t>88413</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>弱勢突破股;多頭排列股</t>
+          <t>建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6045.39</t>
+          <t>1997.583</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1821,17 +1821,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>282.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1846,97 +1846,97 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>34</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>-13.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>51</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>284.6</t>
+          <t>283.1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>282.575</t>
+          <t>282.15</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>282.18</t>
+          <t>282.03</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-18.65</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>8.695652173913043</t>
+          <t>34.78260869565217</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>48.73188405797102</t>
+          <t>32.20108695652175</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-212.20</t>
+          <t>-218.87</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1946,32 +1946,32 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-125748347.0</t>
+          <t>-270072931.6</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>112076563.6</t>
+          <t>227206484.3</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-212</t>
+          <t>-218</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-168756111.58</t>
+          <t>-93955529.27</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>186899</t>
+          <t>188908</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2078,214 +2078,214 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3447.072</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>3959.401</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3447</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>-2.61</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>10.84</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>10.5138</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>12.39</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>24.53525641025641</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>-247.89</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>-89000160.4</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>-25583178.2</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-8555750.67</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>錸德</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>11.15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>-6.0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>3959</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>-4.70</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>8.28</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>3.02</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>10.805</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>10.4886</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>25.50</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>19.23076923076924</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>45.2190170940171</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>-191.81</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-72500299.6</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>-24844668.1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-17377059.36</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>錸德</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr">
         <is>
           <t>14.57%</t>
@@ -2298,12 +2298,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>151.46</t>
+          <t>156.93</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24024.659</t>
+          <t>21679.166</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>16.90</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2395,72 +2395,72 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>60</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>324</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>24025</t>
+          <t>21679</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>127.075</t>
+          <t>127.975</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>117.7</t>
+          <t>118.27</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>52.74122807017543</t>
+          <t>31.79824561403509</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>-103.58</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-845843449.4</t>
+          <t>-2533824327.6</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-1122603171.7</t>
+          <t>-1244643009.1</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-156276245.48</t>
+          <t>-284723432.77</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>770.414</t>
+          <t>587.312</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2637,17 +2637,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2662,122 +2662,122 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>25.11</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>24.805</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>24.668</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>115.80</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>87.50000000000011</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>86.94444444444451</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>4.26</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>2450335.6</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2350223.4</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>770</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>24.98</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>24.7475</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>24.664</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>138.42</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>71.50326797385627</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>-14.67</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>4234068.4</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>4962008.2</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-14</t>
-        </is>
-      </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2068525.57</t>
+          <t>218398.75</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2909,17 +2909,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2934,97 +2934,97 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>63</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-25.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>41</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>32.06</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>32.655</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>31.081</t>
+          <t>31.136</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-50.26</t>
+          <t>-54.76</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.52941176470586</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.843137254901952</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-395.65</t>
+          <t>-19.79</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3034,22 +3034,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-360.4</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>171.8</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-395</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-263.42</t>
+          <t>-124.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35558.069</t>
+          <t>38172.033</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3211,117 +3211,117 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>38172</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-1.16</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>-2.31</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>24.18</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>24.28</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>24.853</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>9.45</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>19.04761904761897</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>6.349206349206303</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>35558</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-2.55</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>-2.65</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>24.2575</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>24.919</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>17.52</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>33.33333333333331</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-144770357.77</t>
+          <t>-27245617.25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>31.57</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>178963</t>
+          <t>180473</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2333.325</t>
+          <t>8367.933</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -733,17 +733,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>61.58</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>247.5</t>
+          <t>262.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -758,82 +758,82 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>88</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>163</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>242.6</t>
+          <t>246.1</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>233.225</t>
+          <t>235.05</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>226.76</t>
+          <t>227.55</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>55.59</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -843,37 +843,37 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>84.68468468468468</t>
+          <t>90.09009009009009</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>387.34</t>
+          <t>61.91</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>192697164.2</t>
+          <t>453611186.2</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>39540590.5</t>
+          <t>280154807.2</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>40183085.05</t>
+          <t>194182468.36</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>49.62</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>78588</t>
+          <t>83192</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3575.0</t>
+          <t>3811.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1005,17 +1005,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>53.65</t>
+          <t>57.19</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>810.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1030,97 +1030,97 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>178</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-34.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>140</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>19.30</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>796.6</t>
+          <t>800.6</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>667.75</t>
+          <t>677.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>616.68</t>
+          <t>620.76</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>56.78</t>
+          <t>56.21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>37.70</t>
+          <t>41.40</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>84.52380952380952</t>
+          <t>66.46706586826348</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>94.84126984126982</t>
+          <t>83.66362513069097</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1130,22 +1130,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2588930.8</t>
+          <t>990582.6</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2023546.4</t>
+          <t>1498258.7</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>131483.05</t>
+          <t>-229492.84</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>64847</t>
+          <t>62445</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>316.0</t>
+          <t>331.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1302,97 +1302,97 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-15.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>331</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>13.86</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>18.12</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>15.61</t>
+          <t>15.7475</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>15.238</t>
+          <t>15.263</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>74.87</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>67.85714285714279</t>
+          <t>27.0833333333334</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>86.11111111111107</t>
+          <t>61.80555555555552</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>159.07</t>
+          <t>113.88</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1402,22 +1402,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>12991.0</t>
+          <t>9372.6</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5014.4</t>
+          <t>4382.2</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>666.31</t>
+          <t>-191.9</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>88.16</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6619.606</t>
+          <t>4271.229</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1574,22 +1574,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1599,52 +1599,52 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>38</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>42.27</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>41.9675</t>
+          <t>41.975</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.473</t>
+          <t>41.506</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1654,42 +1654,42 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.63157894736826</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>81.94444444444434</t>
+          <t>84.21052631578944</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>97.51</t>
+          <t>-9.62</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>107776567.6</t>
+          <t>51235886.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>54568558.2</t>
+          <t>56687386.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>25067104.31</t>
+          <t>467057.52</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>15.42</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.06</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>88413</t>
+          <t>87481</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1997.583</t>
+          <t>5301.801</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1821,17 +1821,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>14.90</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>282.0</t>
+          <t>284.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1861,82 +1861,82 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>465</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>283.1</t>
+          <t>282.8</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>282.15</t>
+          <t>282.35</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>282.03</t>
+          <t>281.97</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-18.65</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>34.78260869565217</t>
+          <t>47.61904761904761</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>32.20108695652175</t>
+          <t>30.36576949620429</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-218.87</t>
+          <t>-29.58</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1946,22 +1946,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-270072931.6</t>
+          <t>204871069.4</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>227206484.3</t>
+          <t>290911917.3</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-218</t>
+          <t>-29</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-93955529.27</t>
+          <t>32121364.34</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.74</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>188908</t>
+          <t>190248</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2063,12 +2063,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>強勢股;建議關注股;多頭排列股</t>
+          <t>弱勢突破股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3447.072</t>
+          <t>3147.139</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2093,199 +2093,199 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.82</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3147</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>-2.40</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>11.27</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>10.885</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>10.5278</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>-1.86</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>13.07692307692306</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>-55.82</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>-52378617.6</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>-33614879.9</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-7662162.32</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>錸德</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
           <t>1.44</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>3447</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>-2.61</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>6.09</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>10.84</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>10.5138</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>12.39</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>24.53525641025641</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>-247.89</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-89000160.4</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>-25583178.2</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-8555750.67</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>錸德</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr">
         <is>
           <t>14.57%</t>
@@ -2298,12 +2298,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>156.93</t>
+          <t>154.47</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2335,12 +2335,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>強勢股;建議關注股;多頭排列股</t>
+          <t>弱勢突破股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21679.166</t>
+          <t>32576.457</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2365,17 +2365,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>16.90</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2390,97 +2390,97 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>32576</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-4.14</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>8.36</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>128.6</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>118.68</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>-12.00</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>21679</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>-0.74</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>5.49</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>8.21</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>135.0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>127.975</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>118.27</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>31.79824561403509</t>
+          <t>12.49999999999999</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-103.58</t>
+          <t>-7.03</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-2533824327.6</t>
+          <t>-2621300414.4</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-1244643009.1</t>
+          <t>-2449112264.4</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-284723432.77</t>
+          <t>-463228275.28</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.74</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>313718</t>
+          <t>298500</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>587.312</t>
+          <t>503.213</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2637,17 +2637,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2662,97 +2662,97 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>503</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.805</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>24.668</t>
+          <t>24.673</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>115.80</t>
+          <t>98.94</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>87.50000000000011</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>86.94444444444451</t>
+          <t>95.83333333333337</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>60.03</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2762,22 +2762,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2450335.6</t>
+          <t>6905268.2</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2350223.4</t>
+          <t>4314915.3</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>218398.75</t>
+          <t>1024615.0</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>14.42</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2909,17 +2909,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2934,134 +2934,134 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-16.0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>-2.26</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>31.86</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>32.5975</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>31.187</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>-66.22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>7.843137254901952</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>-319.67</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>-503.6</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>-120.0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>-179.4</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>-1.82</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>4.88</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>32.06</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>32.655</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>31.136</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>-54.76</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>23.52941176470586</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>7.843137254901952</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>-19.79</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>137.8</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>171.8</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-19</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-124.01</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AL10" t="inlineStr">
         <is>
           <t>宏佳騰</t>
@@ -3079,17 +3079,17 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.24</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>反彈型股</t>
+          <t>弱勢突破股</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38172.033</t>
+          <t>38577.907</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.49</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3206,122 +3206,122 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>-30.0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>38578</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-2.47</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>23.89</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>24.2575</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>24.776</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>-12.05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>6.349206349206303</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>124.0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>38172</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-1.16</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>-2.31</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>24.18</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>24.28</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>24.853</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>9.45</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>19.04761904761897</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>6.349206349206303</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-27245617.25</t>
+          <t>-80056021.51</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>180473</t>
+          <t>175943</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>-8.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8367.933</t>
+          <t>4228.272</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -733,17 +733,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>61.58</t>
+          <t>31.12</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-7.93</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>262.0</t>
+          <t>239.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -758,47 +758,47 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>109</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>144</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -808,47 +808,47 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>245.9</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>235.05</t>
+          <t>235.6</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>227.55</t>
+          <t>228.08</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>26.22950819672131</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>90.09009009009009</t>
+          <t>75.40983606557377</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>61.91</t>
+          <t>81.01</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -858,22 +858,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>453611186.2</t>
+          <t>356183145.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>280154807.2</t>
+          <t>196771444.2</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>194182468.36</t>
+          <t>53055642.24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>49.62</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>61.81</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>83192</t>
+          <t>76048</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3811.0</t>
+          <t>2560.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1005,17 +1005,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>57.19</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>775.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1030,97 +1030,97 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>149</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>-29.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>82</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>800.6</t>
+          <t>799.0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>677.6</t>
+          <t>686.15</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>620.76</t>
+          <t>624.68</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>56.21</t>
+          <t>54.72</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>41.40</t>
+          <t>44.06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>66.46706586826348</t>
+          <t>61.63522012578616</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>83.66362513069097</t>
+          <t>70.87536517261971</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-123.91</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1130,22 +1130,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>990582.6</t>
+          <t>-335203.6</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1498258.7</t>
+          <t>1401740.9</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-33</t>
+          <t>-123</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-229492.84</t>
+          <t>-400596.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.04</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>62445</t>
+          <t>62045</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1247,12 +1247,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>強勢股;多頭排列股</t>
+          <t>強勢股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>331.0</t>
+          <t>848.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1302,27 +1302,27 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1332,67 +1332,67 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>848</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>13.86</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>15.7475</t>
+          <t>15.955</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>15.263</t>
+          <t>15.327</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>27.0833333333334</t>
+          <t>95.83333333333329</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>61.80555555555552</t>
+          <t>63.59126984126982</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>113.88</t>
+          <t>-69.00</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1402,22 +1402,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>9372.6</t>
+          <t>1717.8</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>4382.2</t>
+          <t>5542.1</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>-69</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-191.9</t>
+          <t>806.5</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>88.16</t>
+          <t>87.95</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>強勢股;建議關注股;多頭排列股</t>
+          <t>弱勢突破股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4271.229</t>
+          <t>4947.036</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1579,17 +1579,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1604,47 +1604,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>42.32000000000001</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>41.975</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.506</t>
+          <t>41.532</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1654,17 +1654,17 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>52.63157894736826</t>
+          <t>26.31578947368413</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>84.21052631578944</t>
+          <t>59.64912280701748</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>29.42</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1674,22 +1674,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>51235886.0</t>
+          <t>31213835.2</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>56687386.0</t>
+          <t>24118367.3</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>467057.52</t>
+          <t>-18730830.67</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>15.42</t>
+          <t>15.33</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>17.06</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>87481</t>
+          <t>86963</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>建議關注股;多頭排列股</t>
+          <t>建議關注股</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5301.801</t>
+          <t>6942.012</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1821,17 +1821,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14.90</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>284.0</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1846,17 +1846,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1871,72 +1871,72 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>201</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>282.8</t>
+          <t>279.4</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>282.35</t>
+          <t>281.45</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>281.97</t>
+          <t>281.69</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-161.42</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>47.61904761904761</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>30.36576949620429</t>
+          <t>27.4672187715666</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-29.58</t>
+          <t>-432.09</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1946,22 +1946,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>204871069.4</t>
+          <t>-551658006.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>290911917.3</t>
+          <t>166118536.4</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-29</t>
+          <t>-432</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>32121364.34</t>
+          <t>-137336247.9</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>16.49</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>190248</t>
+          <t>180870</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2063,12 +2063,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>弱勢突破股;建議關注股;多頭排列股</t>
+          <t>建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3147.139</t>
+          <t>3080.063</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -2128,72 +2128,72 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>52</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.885</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>10.5278</t>
+          <t>10.5348</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>13.07692307692306</t>
+          <t>6.666666666666647</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-55.82</t>
+          <t>13.20</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2218,32 +2218,32 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-52378617.6</t>
+          <t>-35288976.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-33614879.9</t>
+          <t>-40656466.6</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7662162.32</t>
+          <t>-6726257.49</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>154.47</t>
+          <t>149.78</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2335,12 +2335,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>弱勢突破股;建議關注股;多頭排列股</t>
+          <t>建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2350,137 +2350,137 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>-3.57</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>18330.799</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>14.29</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-2.03</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>32576.457</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>25.39</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-3.92</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>127.5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>-5.0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>18331</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-5.53</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>8.30</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>130.2</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>128.9</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>119.02</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>-26.93</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>451</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>32576</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>-4.14</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>3.42</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>8.36</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>128.6</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>118.68</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>-12.00</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4.70</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>12.49999999999999</t>
+          <t>6.249999999999996</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-7.03</t>
+          <t>-125.86</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2490,32 +2490,32 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-2621300414.4</t>
+          <t>-2093695520.4</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-2449112264.4</t>
+          <t>-926984587.6</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-463228275.28</t>
+          <t>-432374751.18</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>298500</t>
+          <t>287965</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>503.213</t>
+          <t>445.246</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2637,17 +2637,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2662,24 +2662,24 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>價-量-</t>
@@ -2692,67 +2692,67 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>445</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.945</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>24.673</t>
+          <t>24.674</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>98.94</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33333333333339</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>95.83333333333337</t>
+          <t>90.27777777777783</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>60.03</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2762,22 +2762,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>6905268.2</t>
+          <t>2731175.4</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4314915.3</t>
+          <t>2644253.5</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1024615.0</t>
+          <t>-262486.2</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2909,17 +2909,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2934,97 +2934,97 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-16.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>114</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>31.86</t>
+          <t>32.02</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>32.5975</t>
+          <t>32.615</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>31.187</t>
+          <t>31.251</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-66.22</t>
+          <t>-49.84</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>76.47058823529414</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>7.843137254901952</t>
+          <t>33.33333333333334</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-319.67</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3034,22 +3034,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-503.6</t>
+          <t>321.2</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>-120.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-179.4</t>
+          <t>123.66</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>33.57</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38577.907</t>
+          <t>30283.028</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>32.49</t>
+          <t>25.50</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3206,92 +3206,92 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>90</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-30.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>189</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>30283</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>24.2575</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>24.776</t>
+          <t>24.697</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-21.24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.448275862069016</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>6.349206349206303</t>
+          <t>7.498631636562642</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-369680958.4</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-80056021.51</t>
+          <t>5534747.03</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>31.13</t>
+          <t>30.97</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>175943</t>
+          <t>176320</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-8.79</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4228.272</t>
+          <t>2418.121</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -733,17 +733,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>17.79</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>239.5</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -758,122 +758,122 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2418</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>245.6</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>236.025</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>228.65</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>13.77</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4.96</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>27.86885245901639</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>51.36612021857923</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>109.32</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>402610166.2</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>192340054.5</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-8.0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>4228</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-2.60</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>4.37</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>245.9</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>235.6</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>228.08</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>29.65</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>5.46</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>4.21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>26.22950819672131</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>75.40983606557377</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>81.01</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>356183145.0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>196771444.2</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>53055642.24</t>
+          <t>74659960.1</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>61.81</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>76048</t>
+          <t>76207</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2560.0</t>
+          <t>3762.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1005,17 +1005,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>56.45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>775.0</t>
+          <t>817.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1030,97 +1030,97 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-29.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>104</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>15.33</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>799.0</t>
+          <t>803.6</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>686.15</t>
+          <t>696.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>624.68</t>
+          <t>629.52</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>21.02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>54.72</t>
+          <t>56.29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>44.06</t>
+          <t>46.51</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>61.63522012578616</t>
+          <t>84.29752066115702</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>70.87536517261971</t>
+          <t>70.79993555173553</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-123.91</t>
+          <t>-115.64</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1130,22 +1130,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-335203.6</t>
+          <t>-238130.6</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1401740.9</t>
+          <t>1523041.5</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-123</t>
+          <t>-115</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-400596.01</t>
+          <t>-134415.99</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>23.22</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>62045</t>
+          <t>65407</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>848.0</t>
+          <t>2125.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1302,97 +1302,97 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>12.63</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>15.955</t>
+          <t>16.1025</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>15.327</t>
+          <t>15.37</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>95.83333333333329</t>
+          <t>47.91666666666671</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>63.59126984126982</t>
+          <t>56.94444444444446</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-69.00</t>
+          <t>-7165.92</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1402,22 +1402,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>1717.8</t>
+          <t>-8231.8</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5542.1</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-69</t>
+          <t>-7165</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>806.5</t>
+          <t>-2623.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>87.95</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>弱勢突破股;建議關注股;多頭排列股</t>
+          <t>建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4947.036</t>
+          <t>1953.849</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1549,12 +1549,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1574,84 +1574,84 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.32000000000001</t>
+          <t>42.26000000000001</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>41.9625</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.532</t>
+          <t>41.56399999999999</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
       <c r="AB5" t="inlineStr">
         <is>
           <t>26.31578947368413</t>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>59.64912280701748</t>
+          <t>35.08771929824552</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>-158.07</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1674,32 +1674,32 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>31213835.2</t>
+          <t>-12714020.8</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>24118367.3</t>
+          <t>21893515.9</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-158</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-18730830.67</t>
+          <t>-22300333.24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6942.012</t>
+          <t>2917.429</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1821,17 +1821,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>272.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1851,92 +1851,92 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>42</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>48</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>279.4</t>
+          <t>277.5</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>281.45</t>
+          <t>280.55</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>281.69</t>
+          <t>281.48</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-161.42</t>
+          <t>-487.69</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.82051282051282</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>27.4672187715666</t>
+          <t>20.14652014652015</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-432.09</t>
+          <t>-240.82</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1946,22 +1946,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-551658006.0</t>
+          <t>-145739858.6</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>166118536.4</t>
+          <t>103491773.3</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-432</t>
+          <t>-240</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-137336247.9</t>
+          <t>-49645895.59</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>16.49</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>180870</t>
+          <t>182544</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3080.063</t>
+          <t>3130.961</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2118,97 +2118,97 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>10.5348</t>
+          <t>10.5518</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-28.30</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.87499999999998</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>6.666666666666647</t>
+          <t>7.291666666666642</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13.20</t>
+          <t>80.87</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2218,22 +2218,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-35288976.0</t>
+          <t>-7736165.8</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-40656466.6</t>
+          <t>-40446998.8</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-80</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6726257.49</t>
+          <t>-842077.69</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>149.78</t>
+          <t>158.11</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2335,12 +2335,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>建議關注股;多頭排列股</t>
+          <t>建議關注股</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18330.799</t>
+          <t>17660.711</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2365,17 +2365,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>13.77</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2390,97 +2390,97 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>53</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>187</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>18331</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>128.9</t>
+          <t>129.325</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>119.02</t>
+          <t>119.37</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-26.93</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.42857142857143</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>6.249999999999996</t>
+          <t>3.809523809523805</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-125.86</t>
+          <t>52.58</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-2093695520.4</t>
+          <t>-790167255.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-926984587.6</t>
+          <t>-1666432655.3</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>-52</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-432374751.18</t>
+          <t>-63079996.3</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>287965</t>
+          <t>292647</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>445.246</t>
+          <t>1015.484</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2637,17 +2637,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2662,22 +2662,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2687,72 +2687,72 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.66</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.945</t>
+          <t>24.9925</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>24.674</t>
+          <t>24.686</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>66.11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>83.33333333333339</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>90.27777777777783</t>
+          <t>94.44444444444446</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>51.65</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2762,22 +2762,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2731175.4</t>
+          <t>6532251.2</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2644253.5</t>
+          <t>4307461.7</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-262486.2</t>
+          <t>1675093.94</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>14.36</t>
+          <t>14.33</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2879,12 +2879,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>弱勢突破股;建議關注股</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2909,17 +2909,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>78.97</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2934,97 +2934,97 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>150</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>154</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>32.02</t>
+          <t>32.24</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>32.615</t>
+          <t>32.67</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>31.251</t>
+          <t>31.322</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-49.84</t>
+          <t>-31.37</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>76.47058823529414</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>33.33333333333334</t>
+          <t>58.82352941176472</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>73.99</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3034,22 +3034,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>321.2</t>
+          <t>1672.2</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>961.1</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>123.66</t>
+          <t>427.81</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>33.57</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30283.028</t>
+          <t>29698.001</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25.50</t>
+          <t>25.01</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3206,22 +3206,22 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>83</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -3231,67 +3231,67 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>172</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>30283</t>
+          <t>29698</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>24.697</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-21.24</t>
+          <t>-27.28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>3.448275862069016</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>7.498631636562642</t>
+          <t>1.14942528735632</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-369680958.4</t>
+          <t>-163606509.8</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>5534747.03</t>
+          <t>-39256229.67</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30.97</t>
+          <t>31.16</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>176320</t>
+          <t>175187</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB11"/>
+  <dimension ref="A1:BE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,65 +636,80 @@
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
+          <t>營業收入-上月比較增減(%)</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>營業收入-去年同月增減(%)</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>累計營業收入-前期比較增減(%)</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
@@ -708,7 +723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -718,67 +733,67 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1377.499</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>10.14</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>239.5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2418.121</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>17.79</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>240.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>59</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-51.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -793,62 +808,62 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>245.6</t>
+          <t>245.7</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>236.025</t>
+          <t>236.4</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>228.65</t>
+          <t>229.37</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>13.77</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>27.86885245901639</t>
+          <t>2.173913043478261</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>51.36612021857923</t>
+          <t>18.75742456640532</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>109.32</t>
+          <t>92.40</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -858,22 +873,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>402610166.2</t>
+          <t>398236514.6</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>192340054.5</t>
+          <t>206980708.3</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>74659960.1</t>
+          <t>19883814.62</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -883,7 +898,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -903,70 +918,85 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>-0.644811051273512</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>-20.18542484584181</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-6.47127141471608</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>4.31</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>6.99</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>45.45</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>22.79%</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>12.35%</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>62.96</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>76207</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>影像感測器67.42%、微光學元件30.36%、其他2.22% (2024年)</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>采鈺-半導體業-上市</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>半導體業平</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>55.59</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>** 半導體 - 生產製程及檢測設備</t>
         </is>
@@ -980,7 +1010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -990,12 +1020,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3762.0</t>
+          <t>2546.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1005,17 +1035,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>56.45</t>
+          <t>38.21</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>817.0</t>
+          <t>778.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1025,32 +1055,32 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>133</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>-19.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1065,62 +1095,62 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>803.6</t>
+          <t>792.0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>696.8</t>
+          <t>705.85</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>629.52</t>
+          <t>633.68</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>21.02</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>56.29</t>
+          <t>53.76</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>46.51</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>84.29752066115702</t>
+          <t>23.68421052631579</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>70.79993555173553</t>
+          <t>56.5389837710863</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-115.64</t>
+          <t>-227.09</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1130,22 +1160,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-238130.6</t>
+          <t>-1384740.8</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1523041.5</t>
+          <t>1089550.6</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-115</t>
+          <t>-227</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-134415.99</t>
+          <t>-323179.79</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1155,7 +1185,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1175,70 +1205,85 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-5.062816287608069</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>-3.412094994647266</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>5.211217380242647</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
           <t>2.02</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>52.71</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>23.22</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>43.11%</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>17.22%</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>40.9</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>65407</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>高速訊號傳輸介面晶片44.78%、DisplayPort系列(DP)38.99%、Source Drivers12.74%、TrueTouch系列3.49% (2024年)</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>譜瑞-KY-半導體業-上櫃</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>半導體業平</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>252.85</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>** 半導體 - 平面顯示器驅動IC</t>
         </is>
@@ -1252,7 +1297,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1262,12 +1307,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2125.0</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1277,17 +1322,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1297,32 +1342,32 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1337,62 +1382,62 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>7.83</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>16.1025</t>
+          <t>16.2475</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>15.37</t>
+          <t>15.415</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>47.91666666666671</t>
+          <t>19.99999999999988</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>56.94444444444446</t>
+          <t>54.58333333333329</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-7165.92</t>
+          <t>-446.01</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1402,22 +1447,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-8231.8</t>
+          <t>-7952.8</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>2298.4</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-7165</t>
+          <t>-446</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2623.51</t>
+          <t>-2375.62</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1427,7 +1472,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1452,65 +1497,80 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>200.283758971791</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125.7025761124122</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
+          <t>20.94933089328606</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>0.60</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
         <is>
           <t>15.96%</t>
         </is>
       </c>
-      <c r="AU4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>-47.47%</t>
         </is>
       </c>
-      <c r="AV4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>88.83</t>
         </is>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>1441</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>LED 光電產品93.51%、磊晶片6.32%、其他0.17% (2024年)</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>李洲-光電業-上櫃</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>12.69</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>** LED照明產業 - 封裝/模組、燈具/應用</t>
         </is>
@@ -1524,7 +1584,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1539,7 +1599,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1953.849</t>
+          <t>2591.268</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1549,12 +1609,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1574,27 +1634,27 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1609,47 +1669,47 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.26000000000001</t>
+          <t>42.19</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>41.9625</t>
+          <t>41.9725</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.56399999999999</t>
+          <t>41.599</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>-19.42</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1659,12 +1719,12 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>35.08771929824552</t>
+          <t>26.31578947368413</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-158.07</t>
+          <t>-1080.97</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1674,22 +1734,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-12714020.8</t>
+          <t>-59084107.6</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>21893515.9</t>
+          <t>6023002.5</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-158</t>
+          <t>-1080</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-22300333.24</t>
+          <t>-26213109.18</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1719,70 +1779,85 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
+          <t>-63.40863348097227</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-44.53237722684639</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-58.46140979330202</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
           <t>1.73</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>5.95</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
         <is>
           <t>2.28</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>15.33</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>20.37%</t>
         </is>
       </c>
-      <c r="AU5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>7.22%</t>
         </is>
       </c>
-      <c r="AV5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>16.98</t>
         </is>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>86963</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>建設業務99.44%、百貨0.38%、營造0.18% (2024年)</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>興富發-建材營造-上市</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>建材營造平</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>24.27</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>** 建材營造 - 建設業</t>
         </is>
@@ -1796,7 +1871,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1806,12 +1881,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2917.429</t>
+          <t>3731.391</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1821,17 +1896,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>272.5</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1841,27 +1916,27 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>38</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1881,62 +1956,62 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>277.5</t>
+          <t>275.9</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>280.55</t>
+          <t>279.725</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>281.48</t>
+          <t>281.16</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-487.69</t>
+          <t>-1278.08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12.82051282051282</t>
+          <t>5.88235294117647</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>20.14652014652015</t>
+          <t>6.234288587229773</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-240.82</t>
+          <t>86.97</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1946,22 +2021,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-145739858.6</t>
+          <t>-8760516.4</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>103491773.3</t>
+          <t>-67254431.7</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-240</t>
+          <t>-86</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-49645895.59</t>
+          <t>-122707133.89</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1991,70 +2066,85 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>8.811722960289302</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>45.46314217201299</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>32.12491672435991</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
           <t>3.67</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AU6" t="inlineStr">
         <is>
           <t>152.65</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>16.65</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>9.42%</t>
         </is>
       </c>
-      <c r="AU6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>5.18%</t>
         </is>
       </c>
-      <c r="AV6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>28.24</t>
         </is>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>182544</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>網路通訊產品64.27%、電腦配件31.22%、其他4.51% (2024年)</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>技嘉-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>77.62</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、主機板、機殼、電源供應器、散熱片、風扇馬達、散熱模組、顯示卡、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
@@ -2063,12 +2153,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>建議關注股;多頭排列股</t>
+          <t>建議關注股</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2078,12 +2168,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3130.961</t>
+          <t>1462.653</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2093,17 +2183,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2113,32 +2203,32 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -2158,57 +2248,57 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>10.9625</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>10.5518</t>
+          <t>10.5698</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-28.30</t>
+          <t>-34.24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>21.87499999999998</t>
+          <t>19.35483870967746</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>7.291666666666642</t>
+          <t>13.74327956989246</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>80.87</t>
+          <t>94.25</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2218,22 +2308,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-7736165.8</t>
+          <t>-2146786.2</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-40446998.8</t>
+          <t>-37323542.9</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-80</t>
+          <t>-94</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-842077.69</t>
+          <t>-483024.2</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2263,70 +2353,85 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>7.266079007508978</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.43204577292231</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
+          <t>8.178446379053689</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>3.29</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
         <is>
           <t>14.57%</t>
         </is>
       </c>
-      <c r="AU7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>0.16%</t>
         </is>
       </c>
-      <c r="AV7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>158.11</t>
         </is>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>7596</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>光學產品84.42%、其他15.58% (2024年)</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>錸德-光電業-上市</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>光電業平</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>7.63</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 光碟片</t>
         </is>
@@ -2340,7 +2445,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2350,12 +2455,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17660.711</t>
+          <t>13900.638</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2365,17 +2470,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13.77</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2385,32 +2490,32 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>38</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-15.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -2425,62 +2530,62 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>129.325</t>
+          <t>129.65</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>119.37</t>
+          <t>119.68</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-44.49</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11.42857142857143</t>
+          <t>6.896551724137931</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>3.809523809523805</t>
+          <t>6.108374384236448</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>52.58</t>
+          <t>-35.59</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2490,22 +2595,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-790167255.0</t>
+          <t>-1780567088.4</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-1666432655.3</t>
+          <t>-1313205268.9</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-63079996.3</t>
+          <t>-100281183.86</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2535,70 +2640,85 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>1.409424233691332</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>7.352888368225501</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>20.99056536095143</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
           <t>3.61</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AU8" t="inlineStr">
         <is>
           <t>17.81</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>21.74</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>22.12%</t>
         </is>
       </c>
-      <c r="AU8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>9.22%</t>
         </is>
       </c>
-      <c r="AV8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>28.24</t>
         </is>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>292647</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>資訊及消費性電子43.00%、雲端及物聯網37.00%、光電通訊20.00% (2024年)</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>光寶科-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右上</t>
         </is>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>35.46</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>** 汽車 - 銷售、進出口業務、車燈、其他** 電腦及週邊設備 - 機殼、電源供應器、伺服器、其他電腦及週邊設備、安全監控系統** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 其他 - 其他電子產品及電子服務產業** 雲端運算 - 電力設備、冷卻設備、雲端應用服務、系統整合、顧問諮詢、設備安裝服務、IaaS、PaaS、SaaS** 體驗科技 - 環境感知、深度感測、視覺、手勢/動作** LED照明產業 - 封裝/模組、燈具/應用** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 智慧電網 - 配電管理設施** 醫療器材 - 醫療耗材、生物檢測</t>
         </is>
@@ -2612,7 +2732,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2622,12 +2742,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1015.484</t>
+          <t>484.681</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2637,17 +2757,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2657,29 +2777,29 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>價-量-</t>
@@ -2697,17 +2817,17 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -2717,42 +2837,42 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.9925</t>
+          <t>25.0325</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>24.686</t>
+          <t>24.707</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>66.11</t>
+          <t>51.60</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.88888888888874</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>94.44444444444446</t>
+          <t>90.7407407407407</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>51.65</t>
+          <t>-95.72</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2762,22 +2882,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>6532251.2</t>
+          <t>92604.2</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4307461.7</t>
+          <t>2163336.3</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-95</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1675093.94</t>
+          <t>73474.09</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2787,7 +2907,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2807,70 +2927,85 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
+          <t>7.751419501579042</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-10.38604692305599</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-22.74807474555465</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
+      <c r="AT9" t="inlineStr">
         <is>
           <t>6.96</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AU9" t="inlineStr">
         <is>
           <t>7.59</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>20.85</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>8.32%</t>
         </is>
       </c>
-      <c r="AU9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>-1.03%</t>
         </is>
       </c>
-      <c r="AV9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>14.33</t>
         </is>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>5170</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>橋椿-居家生活-上市</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>居家生活平</t>
         </is>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>35.8</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>** 其他 - 其他</t>
         </is>
@@ -2879,12 +3014,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>弱勢突破股;建議關注股</t>
+          <t>建議關注股</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2894,12 +3029,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2909,17 +3044,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>78.97</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2929,27 +3064,27 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>154</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2969,62 +3104,62 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>32.32000000000001</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>32.67</t>
+          <t>32.63500000000001</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>31.322</t>
+          <t>31.382</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-31.37</t>
+          <t>-42.00</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>26.66666666666657</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>58.82352941176472</t>
+          <t>67.71241830065357</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>73.99</t>
+          <t>156.89</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3034,22 +3169,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>1672.2</t>
+          <t>1627.4</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>961.1</t>
+          <t>633.5</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>427.81</t>
+          <t>177.09</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3079,70 +3214,85 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.5502992040917953</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>-62.96013378851607</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-7.737807792515493</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
           <t>1.51</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AU10" t="inlineStr">
         <is>
           <t>6.79</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>33.78</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>20.81%</t>
         </is>
       </c>
-      <c r="AU10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>-4.48%</t>
         </is>
       </c>
-      <c r="AV10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>34.99</t>
         </is>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>2467</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>ATV/ UTV64.10%、摩托車14.76%、電動車輛13.19%、零組件及其他7.95% (2024年)</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>宏佳騰-電機機械-上櫃</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>電機機械平</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>電機機械右下</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
         <is>
           <t>26.0</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
         </is>
@@ -3156,7 +3306,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3166,12 +3316,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29698.001</t>
+          <t>39143.289</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3181,17 +3331,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>32.96</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3201,29 +3351,29 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>-7.0</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>價-量-</t>
@@ -3241,47 +3391,47 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.37</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.095</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>24.544</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-27.28</t>
+          <t>-29.67</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -3306,7 +3456,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-163606509.8</t>
+          <t>-175194490.4</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -3321,7 +3471,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-39256229.67</t>
+          <t>-84948252.87</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3356,65 +3506,80 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
+          <t>33.91465883488689</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-6.193883484790765</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>5.87318368368304</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
           <t>0.81</t>
         </is>
       </c>
-      <c r="AQ11" t="inlineStr">
+      <c r="AT11" t="inlineStr">
         <is>
           <t>4.31</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AU11" t="inlineStr">
         <is>
           <t>4.57</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>22.52</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>15.12%</t>
         </is>
       </c>
-      <c r="AU11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>3.15%</t>
         </is>
       </c>
-      <c r="AV11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>31.16</t>
         </is>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>175187</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>台泥-水泥工業-上市</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>水泥工業右下</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>28.5</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1377.499</t>
+          <t>2152.934</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -748,17 +748,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>239.5</t>
+          <t>244.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -768,102 +768,102 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>43</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-51.0</t>
+          <t>-16.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>49</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>245.7</t>
+          <t>245.0</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>236.4</t>
+          <t>237.025</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>229.37</t>
+          <t>230.16</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2.173913043478261</t>
+          <t>21.73913043478261</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>18.75742456640532</t>
+          <t>17.26063197909242</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>92.40</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -873,22 +873,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>398236514.6</t>
+          <t>390099758.6</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>206980708.3</t>
+          <t>291398461.4</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>19883814.62</t>
+          <t>45406697.15</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.21</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>64.08</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>76207</t>
+          <t>77477</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2546.0</t>
+          <t>1597.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>38.21</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-19.0</t>
+          <t>-15.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1085,72 +1085,72 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>58</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>792.0</t>
+          <t>785.6</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>705.85</t>
+          <t>715.15</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>633.68</t>
+          <t>637.78</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>53.76</t>
+          <t>51.16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>48.60</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23.68421052631579</t>
+          <t>4.918032786885246</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>56.5389837710863</t>
+          <t>37.63325465811933</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-227.09</t>
+          <t>-235.94</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-1384740.8</t>
+          <t>-1047620.4</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1089550.6</t>
+          <t>770655.2</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-227</t>
+          <t>-235</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-323179.79</t>
+          <t>-389627.46</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>23.22</t>
+          <t>22.11</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>65407</t>
+          <t>62285</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1307,12 +1307,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1342,87 +1342,87 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>-9.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>195</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.42</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>16.2475</t>
+          <t>16.395</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>15.415</t>
+          <t>15.453</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>54.58333333333329</t>
+          <t>29.30555555555548</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-446.01</t>
+          <t>-373.67</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1447,22 +1447,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-7952.8</t>
+          <t>-7505.8</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2298.4</t>
+          <t>2742.6</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-446</t>
+          <t>-373</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2375.62</t>
+          <t>-2038.46</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>89.35</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1594,62 +1594,62 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1933.464</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>42.05</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2591.268</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>6.22</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1659,22 +1659,22 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1684,47 +1684,47 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>41.9725</t>
+          <t>42.0125</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.599</t>
+          <t>41.637</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.42</t>
+          <t>-23.24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>26.31578947368413</t>
+          <t>31.57894736842066</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>26.31578947368413</t>
+          <t>28.07017543859632</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-1080.97</t>
+          <t>-2555.28</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1734,22 +1734,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-59084107.6</t>
+          <t>-99658667.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>6023002.5</t>
+          <t>4058950.3</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1080</t>
+          <t>-2555</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-26213109.18</t>
+          <t>-14065755.48</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>86963</t>
+          <t>87067</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3731.391</t>
+          <t>4190.214</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1896,17 +1896,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>277.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1916,102 +1916,102 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>30</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>54</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>275.9</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>279.725</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>281.16</t>
+          <t>281.05</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-1278.08</t>
+          <t>-283.92</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>5.88235294117647</t>
+          <t>44.11764705882353</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>6.234288587229773</t>
+          <t>20.94017094017095</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>86.97</t>
+          <t>235.37</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2021,22 +2021,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-8760516.4</t>
+          <t>109013797.8</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-67254431.7</t>
+          <t>-80529566.9</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-86</t>
+          <t>-235</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-122707133.89</t>
+          <t>-8267791.0</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28.84</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>182544</t>
+          <t>185894</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2168,29 +2168,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2047.513</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>-0.45</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1462.653</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-1.37</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>10.9</t>
@@ -2203,17 +2203,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -2233,72 +2233,72 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.9625</t>
+          <t>10.99</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>10.5698</t>
+          <t>10.5868</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-34.24</t>
+          <t>-39.04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19.35483870967746</t>
+          <t>24.00000000000006</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>13.74327956989246</t>
+          <t>21.74327956989248</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>94.25</t>
+          <t>72.26</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2308,22 +2308,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-2146786.2</t>
+          <t>-14333875.6</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-37323542.9</t>
+          <t>-51667018.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-94</t>
+          <t>-72</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-483024.2</t>
+          <t>-693352.77</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>158.11</t>
+          <t>154.07</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13900.638</t>
+          <t>10329.127</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2490,102 +2490,102 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-15.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>127</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>124.9</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>129.65</t>
+          <t>129.675</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>119.68</t>
+          <t>120.01</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-44.49</t>
+          <t>-50.18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>6.896551724137931</t>
+          <t>14.28571428571428</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>6.108374384236448</t>
+          <t>10.87027914614121</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-35.59</t>
+          <t>45.98</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2595,22 +2595,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-1780567088.4</t>
+          <t>-937541902.2</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-1313205268.9</t>
+          <t>-1735683114.9</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-100281183.86</t>
+          <t>104199746.18</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28.84</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>484.681</t>
+          <t>538.389</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2757,17 +2757,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2777,27 +2777,27 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2812,67 +2812,67 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>538</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25.66</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>25.0325</t>
+          <t>25.085</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>24.707</t>
+          <t>24.733</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>51.60</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>88.88888888888874</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>90.7407407407407</t>
+          <t>96.29629629629625</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-95.72</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>92604.2</t>
+          <t>5899063.2</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2163336.3</t>
+          <t>4174699.4</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-95</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>73474.09</t>
+          <t>931057.44</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -3014,12 +3014,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>27.69</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3064,32 +3064,32 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-31.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -3099,67 +3099,67 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>54</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>32.32000000000001</t>
+          <t>32.16</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>32.63500000000001</t>
+          <t>32.5375</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>31.382</t>
+          <t>31.426</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-42.00</t>
+          <t>-74.07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>26.66666666666657</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>67.71241830065357</t>
+          <t>42.22222222222219</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>156.89</t>
+          <t>76.34</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3169,22 +3169,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>1627.4</t>
+          <t>1027.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>633.5</t>
+          <t>582.4</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>177.09</t>
+          <t>-51.43</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>35.53</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>39143.289</t>
+          <t>23852.714</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>32.96</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -3361,17 +3361,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>78</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -3381,67 +3381,67 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>175</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>29698</t>
+          <t>23853</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>24.095</t>
+          <t>24.0375</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>24.544</t>
+          <t>24.474</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-29.67</t>
+          <t>-23.96</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.12121212121209</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1.14942528735632</t>
+          <t>4.04040404040401</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-175194490.4</t>
+          <t>-246258971.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-84948252.87</t>
+          <t>-6370039.69</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>31.16</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>175187</t>
+          <t>175943</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2152.934</t>
+          <t>1934.647</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -748,17 +748,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>251.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -773,97 +773,97 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>40</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-16.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>46</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>245.0</t>
+          <t>242.8</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>237.025</t>
+          <t>238.275</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>230.16</t>
+          <t>230.97</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21.73913043478261</t>
+          <t>52.17391304347826</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>17.26063197909242</t>
+          <t>25.3623188405797</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>33.87</t>
+          <t>-82.19</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -873,22 +873,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>390099758.6</t>
+          <t>44355154.6</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>291398461.4</t>
+          <t>248983170.4</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-82</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>45406697.15</t>
+          <t>58505055.77</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>46.21</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>64.08</t>
+          <t>64.46</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>77477</t>
+          <t>79700</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1020,62 +1020,62 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2380.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>35.71</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>804.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1597.0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>23.96</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-3.08</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>778.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>97</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-15.0</t>
+          <t>-21.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1085,72 +1085,72 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>70</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>13.03</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>785.6</t>
+          <t>790.4</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>715.15</t>
+          <t>725.95</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>637.78</t>
+          <t>642.26</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>51.16</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>48.60</t>
+          <t>49.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>4.918032786885246</t>
+          <t>47.54098360655738</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>37.63325465811933</t>
+          <t>25.38107563991945</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-235.94</t>
+          <t>-114.83</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-1047620.4</t>
+          <t>-68397.4</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>770655.2</t>
+          <t>461092.6</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-235</t>
+          <t>-114</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-389627.46</t>
+          <t>-190128.77</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>22.11</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>62285</t>
+          <t>64367</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1292,12 +1292,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>強勢股;建議關注股;多頭排列股</t>
+          <t>弱勢突破股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1307,137 +1307,137 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-2.06</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>195.0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-3.78</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>17.2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-9.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>110</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>16.395</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>15.453</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19.99999999999988</t>
+          <t>8.57142857142849</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>29.30555555555548</t>
+          <t>16.19047619047607</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-373.67</t>
+          <t>-613.23</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1447,22 +1447,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-7505.8</t>
+          <t>-6744.4</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2742.6</t>
+          <t>1314.1</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-373</t>
+          <t>-613</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2038.46</t>
+          <t>-1639.14</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>89.35</t>
+          <t>92.96</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1579,12 +1579,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>建議關注股;多頭排列股</t>
+          <t>建議關注股</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1933.464</t>
+          <t>3765.623</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1609,17 +1609,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1649,82 +1649,82 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>3766</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>41.97</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>42.0125</t>
+          <t>42.055</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.637</t>
+          <t>41.665</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.24</t>
+          <t>-36.70</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>31.57894736842066</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>28.07017543859632</t>
+          <t>19.29824561403495</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-2555.28</t>
+          <t>-334.57</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1734,22 +1734,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-99658667.0</t>
+          <t>-94920762.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4058950.3</t>
+          <t>-21842438.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2555</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-14065755.48</t>
+          <t>-23128155.68</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>87067</t>
+          <t>86549</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4190.214</t>
+          <t>3950.598</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1896,17 +1896,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>11.10</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>277.5</t>
+          <t>280.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1926,92 +1926,92 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>279.05</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>281.05</t>
+          <t>281.0</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-283.92</t>
+          <t>-116.89</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>44.11764705882353</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>20.94017094017095</t>
+          <t>41.66666666666668</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>235.37</t>
+          <t>-77.76</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2021,22 +2021,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>109013797.8</t>
+          <t>25632972.6</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-80529566.9</t>
+          <t>115252021.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-235</t>
+          <t>-77</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-8267791.0</t>
+          <t>67980864.27</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.14</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>185894</t>
+          <t>187904</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2168,137 +2168,137 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1130.751</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10.85</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2047.513</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2.16</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.99</t>
+          <t>11.0175</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>10.5868</t>
+          <t>10.6018</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-39.04</t>
+          <t>-45.05</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>24.00000000000006</t>
+          <t>41.66666666666669</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>21.74327956989248</t>
+          <t>28.34050179211472</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>72.26</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2308,22 +2308,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-14333875.6</t>
+          <t>-9853443.2</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-51667018.0</t>
+          <t>-31116030.4</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-72</t>
+          <t>-68</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-693352.77</t>
+          <t>-68149.77</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>154.07</t>
+          <t>154.72</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2440,12 +2440,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10329.127</t>
+          <t>8871.425</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2495,97 +2495,97 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>103</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>124.9</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>129.675</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>120.01</t>
+          <t>120.36</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-50.18</t>
+          <t>-55.23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14.28571428571428</t>
+          <t>18.18181818181818</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>10.87027914614121</t>
+          <t>13.12136139722346</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>45.98</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2595,22 +2595,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-937541902.2</t>
+          <t>-320869634.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-1735683114.9</t>
+          <t>-1471085024.2</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>-78</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>104199746.18</t>
+          <t>64139162.07</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>538.389</t>
+          <t>669.521</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2757,17 +2757,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2782,22 +2782,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2807,72 +2807,72 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>670</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>25.085</t>
+          <t>25.1325</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>24.733</t>
+          <t>24.753</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>25.46</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>49.99999999999978</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>96.29629629629625</t>
+          <t>79.62962962962952</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>-103.78</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>5899063.2</t>
+          <t>-128050.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4174699.4</t>
+          <t>3388609.1</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-103</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>931057.44</t>
+          <t>-822735.22</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.33</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>27.69</t>
+          <t>11.79</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3069,97 +3069,97 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-31.0</t>
+          <t>-67.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>32.5375</t>
+          <t>32.4525</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>31.426</t>
+          <t>31.477</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-74.07</t>
+          <t>-97.95</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.78947368421055</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>42.22222222222219</t>
+          <t>14.15204678362571</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>76.34</t>
+          <t>222.44</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3169,22 +3169,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>1027.0</t>
+          <t>1326.2</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>582.4</t>
+          <t>411.3</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-51.43</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>35.53</t>
+          <t>35.41</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23852.714</t>
+          <t>38543.601</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>85</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -3371,72 +3371,72 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>294</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>23853</t>
+          <t>38544</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.21</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>24.0375</t>
+          <t>23.9875</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>24.474</t>
+          <t>24.401</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-23.96</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12.12121212121209</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-246258971.0</t>
+          <t>-243600120.4</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-6370039.69</t>
+          <t>-59318653.32</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>175943</t>
+          <t>174432</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1934.647</t>
+          <t>1494.856</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -748,17 +748,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>251.0</t>
+          <t>253.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -773,97 +773,97 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>242.8</t>
+          <t>245.6</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>238.275</t>
+          <t>239.75</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>230.97</t>
+          <t>231.68</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>52.17391304347826</t>
+          <t>63.04347826086957</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>25.3623188405797</t>
+          <t>45.65217391304348</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-82.19</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -873,22 +873,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44355154.6</t>
+          <t>328880390.4</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>248983170.4</t>
+          <t>342531767.7</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-82</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>58505055.77</t>
+          <t>58490637.6</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>48.01</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>64.46</t>
+          <t>65.16</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>79700</t>
+          <t>80493</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1005,12 +1005,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>強勢股;建議關注股;多頭排列股</t>
+          <t>弱勢突破股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2380.0</t>
+          <t>1332.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1035,17 +1035,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>792.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>79</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.0</t>
+          <t>-18.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1085,72 +1085,72 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>58</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>790.4</t>
+          <t>793.8</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>725.95</t>
+          <t>736.55</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>642.26</t>
+          <t>646.52</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>49.00</t>
+          <t>48.94</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>47.54098360655738</t>
+          <t>27.86885245901639</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>25.38107563991945</t>
+          <t>26.77595628415299</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-114.83</t>
+          <t>207.13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-68397.4</t>
+          <t>116922.8</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>461092.6</t>
+          <t>-109140.4</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-114</t>
+          <t>-207</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-190128.77</t>
+          <t>-267597.39</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.51</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>64367</t>
+          <t>63406</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1292,12 +1292,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>弱勢突破股;建議關注股;多頭排列股</t>
+          <t>建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1307,12 +1307,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1322,122 +1322,122 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>16.95</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>7.67</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>17.14</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>16.6925</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>15.503</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>-11.87</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>0.67</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-2.06</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-12.0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>價漲量縮</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-2.58</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>6.85</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>16.54</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>15.48</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>-5.10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>8.57142857142849</t>
+          <t>6.060606060605936</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>16.19047619047607</t>
+          <t>11.54401154401143</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-613.23</t>
+          <t>-140.31</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1447,32 +1447,32 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-6744.4</t>
+          <t>-10240.6</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>1314.1</t>
+          <t>-4261.4</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-613</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1639.14</t>
+          <t>-1320.89</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3765.623</t>
+          <t>4659.879</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1609,17 +1609,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1634,97 +1634,97 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4660</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>41.87</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>42.05249999999999</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>41.677</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>-63.19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>3766</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>41.97</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>42.055</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>41.665</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>-36.70</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>19.29824561403495</t>
+          <t>10.52631578947357</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-334.57</t>
+          <t>-202.34</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1734,22 +1734,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-94920762.0</t>
+          <t>-92213180.2</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-21842438.0</t>
+          <t>-30499672.5</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-23128155.68</t>
+          <t>-31621182.13</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>15.26</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>86549</t>
+          <t>85928</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3950.598</t>
+          <t>3374.738</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1896,17 +1896,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11.10</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>280.5</t>
+          <t>284.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1921,97 +1921,97 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>77</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>277.2</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>279.05</t>
+          <t>279.85</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>281.0</t>
+          <t>280.99</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-116.89</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>41.66666666666668</t>
+          <t>73.03921568627452</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-77.76</t>
+          <t>2429.37</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2021,22 +2021,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>25632972.6</t>
+          <t>599023333.4</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>115252021.0</t>
+          <t>23682663.7</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-77</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>67980864.27</t>
+          <t>109036192.46</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>17.14</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>187904</t>
+          <t>190583</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1130.751</t>
+          <t>2804.18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2183,17 +2183,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2213,17 +2213,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -2233,72 +2233,72 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>-1.20</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>10.92</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>11.0525</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>10.6188</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>-43.22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>0.09</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>-1.61</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>3.92</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>10.84</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>11.0175</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>10.6018</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>-45.05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>41.66666666666669</t>
+          <t>66.66666666666676</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>28.34050179211472</t>
+          <t>44.11111111111115</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>118.30</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2308,22 +2308,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-9853443.2</t>
+          <t>2957655.2</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-31116030.4</t>
+          <t>-16165660.4</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-68</t>
+          <t>-118</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-68149.77</t>
+          <t>3614034.74</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>154.72</t>
+          <t>159.04</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2440,12 +2440,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>弱勢突破股</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2455,137 +2455,137 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>28824.994</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>22.47</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>8871.425</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>6.91</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>37</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>28825</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>129.95</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>120.36</t>
+          <t>120.81</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-55.23</t>
+          <t>-44.68</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18.18181818181818</t>
+          <t>72.72727272727273</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>13.12136139722346</t>
+          <t>35.06493506493506</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>246.70</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2595,22 +2595,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-320869634.0</t>
+          <t>885895314.6</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-1471085024.2</t>
+          <t>-603900102.9</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-78</t>
+          <t>-246</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>64139162.07</t>
+          <t>400004236.27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>292647</t>
+          <t>306694</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>669.521</t>
+          <t>1124.196</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2757,17 +2757,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2782,72 +2782,72 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>25.1325</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>24.753</t>
+          <t>24.776</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>25.46</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2857,22 +2857,22 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>49.99999999999978</t>
+          <t>49.99999999999956</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>79.62962962962952</t>
+          <t>66.66666666666644</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-103.78</t>
+          <t>48.70</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-128050.0</t>
+          <t>7916937.6</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3388609.1</t>
+          <t>5324056.5</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-103</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-822735.22</t>
+          <t>1421378.9</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3029,32 +3029,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>11.79</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3069,97 +3069,97 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>43</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-67.0</t>
+          <t>-13.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>31.96</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>32.4525</t>
+          <t>32.4125</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>31.477</t>
+          <t>31.531</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-97.95</t>
+          <t>-102.31</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15.78947368421055</t>
+          <t>42.10526315789473</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>14.15204678362571</t>
+          <t>19.29824561403509</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>222.44</t>
+          <t>32.45</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3169,22 +3169,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>1326.2</t>
+          <t>629.8</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>411.3</t>
+          <t>475.5</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-48.31</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>35.41</t>
+          <t>35.61</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38543.601</t>
+          <t>20760.816</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>17.48</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>70</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -3371,67 +3371,67 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>-15.0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>168</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>38544</t>
+          <t>20761</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>23.21</t>
+          <t>23.14</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>23.9875</t>
+          <t>23.895</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>24.401</t>
+          <t>24.331</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-20.77</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.00</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -3456,22 +3456,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-243600120.4</t>
+          <t>-480121963.4</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-424901460.9</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-59318653.32</t>
+          <t>-64035825.65</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>22.43</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>174432</t>
+          <t>173677</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE11"/>
+  <dimension ref="A1:BE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -723,7 +723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1494.856</t>
+          <t>5454.373</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -748,17 +748,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>40.14</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>253.5</t>
+          <t>264.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -773,122 +773,122 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>65</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>103</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>245.6</t>
+          <t>250.4</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>239.75</t>
+          <t>241.75</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>231.68</t>
+          <t>232.69</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>63.04347826086957</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>45.65217391304348</t>
+          <t>71.73913043478261</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>328880390.4</t>
+          <t>499305257.4</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>342531767.7</t>
+          <t>450957711.8</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>58490637.6</t>
+          <t>135950127.85</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>48.01</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>65.16</t>
+          <t>50.81</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>80493</t>
+          <t>83827</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1005,12 +1005,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>弱勢突破股;建議關注股;多頭排列股</t>
+          <t>建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1332.0</t>
+          <t>1925.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1035,17 +1035,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>792.0</t>
+          <t>777.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1060,97 +1060,97 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>84</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-18.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>793.8</t>
+          <t>785.8</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>736.55</t>
+          <t>746.65</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>646.52</t>
+          <t>650.76</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>45.38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>48.94</t>
+          <t>48.23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>27.86885245901639</t>
+          <t>4.761904761904762</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>26.77595628415299</t>
+          <t>26.72391360915949</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>207.13</t>
+          <t>-53.66</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1160,32 +1160,32 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>116922.8</t>
+          <t>-789721.8</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-109140.4</t>
+          <t>-513926.2</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-207</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-267597.39</t>
+          <t>-348684.94</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>49.01</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>63406</t>
+          <t>62205</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1307,12 +1307,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1372,72 +1372,72 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>142</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>17.14</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>16.6925</t>
+          <t>16.8575</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>15.503</t>
+          <t>15.536</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>6.060606060605936</t>
+          <t>21.2121212121211</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>11.54401154401143</t>
+          <t>11.94805194805183</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-140.31</t>
+          <t>62.39</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1447,22 +1447,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-10240.6</t>
+          <t>-1906.8</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-4261.4</t>
+          <t>-5069.3</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>-62</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1320.89</t>
+          <t>-737.56</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4659.879</t>
+          <t>3166.044</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1609,17 +1609,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>7.60</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1634,22 +1634,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1659,72 +1659,72 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>42.05249999999999</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.677</t>
+          <t>41.705</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-63.19</t>
+          <t>-64.53</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33333333333314</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>10.52631578947357</t>
+          <t>11.11111111111106</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-202.34</t>
+          <t>-58.98</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1734,22 +1734,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-92213180.2</t>
+          <t>-49272242.4</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-30499672.5</t>
+          <t>-30993131.6</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-31621182.13</t>
+          <t>-12287514.19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>16.63</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>85928</t>
+          <t>86756</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3374.738</t>
+          <t>2592.393</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1896,17 +1896,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>284.5</t>
+          <t>281.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1921,22 +1921,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1946,72 +1946,72 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>55</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>277.2</t>
+          <t>278.9</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>279.85</t>
+          <t>280.15</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>280.99</t>
+          <t>281.01</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>16.39</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.86206896551724</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>73.03921568627452</t>
+          <t>83.62068965517243</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2429.37</t>
+          <t>297.31</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2021,22 +2021,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>599023333.4</t>
+          <t>293464816.4</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>23682663.7</t>
+          <t>73862478.9</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>109036192.46</t>
+          <t>8320462.88</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>190583</t>
+          <t>188239</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2168,32 +2168,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2199.604</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2804.18</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -2218,14 +2218,14 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>價-量-</t>
@@ -2233,47 +2233,47 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>11.0525</t>
+          <t>11.0975</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>10.6188</t>
+          <t>10.6398</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-43.22</t>
+          <t>-36.60</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2283,22 +2283,22 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>66.66666666666676</t>
+          <t>83.33333333333339</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>44.11111111111115</t>
+          <t>63.88888888888894</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>118.30</t>
+          <t>127.57</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2308,22 +2308,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2957655.2</t>
+          <t>937092.4</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-16165660.4</t>
+          <t>-3399536.7</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-118</t>
+          <t>-127</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3614034.74</t>
+          <t>5600230.06</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>159.04</t>
+          <t>158.81</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2440,12 +2440,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28824.994</t>
+          <t>10836.889</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -2505,87 +2505,87 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>275</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>28825</t>
+          <t>10837</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>129.95</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>120.81</t>
+          <t>121.27</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-44.68</t>
+          <t>-38.33</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>72.72727272727273</t>
+          <t>63.63636363636363</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>35.06493506493506</t>
+          <t>51.51515151515152</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>246.70</t>
+          <t>150.15</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2595,22 +2595,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>885895314.6</t>
+          <t>158406069.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-603900102.9</t>
+          <t>-315880593.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-246</t>
+          <t>-150</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>400004236.27</t>
+          <t>236652278.7</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>22.61</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>306694</t>
+          <t>304353</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2727,12 +2727,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>強勢股;建議關注股;多頭排列股</t>
+          <t>弱勢突破股;建議關注股;多頭排列股</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1124.196</t>
+          <t>1463.697</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2757,17 +2757,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2807,72 +2807,72 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-6.70</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>24.776</t>
+          <t>24.759</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>-51.61</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>49.99999999999956</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>66.66666666666644</t>
+          <t>33.33333333333312</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>48.70</t>
+          <t>-480.85</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>7916937.6</t>
+          <t>-4283037.6</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5324056.5</t>
+          <t>1124606.8</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-480</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1421378.9</t>
+          <t>-1803147.92</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>居家生活平</t>
+          <t>居家生活右下</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3069,97 +3069,97 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>50</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>32.4125</t>
+          <t>32.36499999999999</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>31.531</t>
+          <t>31.584</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-102.31</t>
+          <t>-124.33</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>42.10526315789473</t>
+          <t>28.94736842105264</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>19.29824561403509</t>
+          <t>28.94736842105264</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>-239.67</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3169,22 +3169,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>629.8</t>
+          <t>-687.6</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>475.5</t>
+          <t>492.3</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-239</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-48.31</t>
+          <t>-198.5</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>35.61</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3295,293 +3295,6 @@
       <c r="BE10" t="inlineStr">
         <is>
           <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>20760.816</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>17.48</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>-15.0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>20761</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>-3.16</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>-1.79</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>23.14</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>23.895</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>24.331</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>-20.77</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>4.04040404040401</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>-13.00</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>-480121963.4</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>-424901460.9</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-64035825.65</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>33.91465883488689</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-6.193883484790765</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>5.87318368368304</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>4.57</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>22.33</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>15.12%</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>3.15%</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>30.93</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>173677</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>台泥-水泥工業-上市</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>水泥工業右下</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>28.5</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE10"/>
+  <dimension ref="A1:BF11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,115 +601,120 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>volume_threshold</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>Volume_Price_Change_sum</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>highlight_date</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
@@ -718,12 +723,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>強勢股;建議關注股;多頭排列股</t>
+          <t>強勢股;反彈型股</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -733,12 +738,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5454.373</t>
+          <t>2210.719</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -748,12 +753,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>16.27</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -773,82 +778,82 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>67</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>60</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>250.4</t>
+          <t>255.3</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>241.75</t>
+          <t>243.25</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>232.69</t>
+          <t>233.76</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>33.92</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -858,145 +863,150 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>71.73913043478261</t>
+          <t>87.68115942028986</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>499305257.4</t>
+          <t>448730265.8</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>450957711.8</t>
+          <t>423483390.2</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>135950127.85</t>
+          <t>55968279.66289203</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
+          <t>35865401.87</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
           <t>采鈺</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>半導體業</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
           <t>-0.644811051273512</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>-20.18542484584181</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>-6.47127141471608</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>4.75</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>6.99</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>22.79%</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>12.35%</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>50.81</t>
-        </is>
-      </c>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>50.98</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
           <t>83827</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>影像感測器67.42%、微光學元件30.36%、其他2.22% (2024年)</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>采鈺-半導體業-上市</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>半導體業平</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>55.59</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>** 半導體 - 生產製程及檢測設備</t>
         </is>
@@ -1005,12 +1015,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>建議關注股;多頭排列股</t>
+          <t>弱勢突破股</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1020,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1925.0</t>
+          <t>1134.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1035,17 +1045,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>777.0</t>
+          <t>781.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1060,97 +1070,97 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>65</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>-19.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>15.30</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>785.8</t>
+          <t>786.4</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>746.65</t>
+          <t>755.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>650.76</t>
+          <t>655.1</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-9.54</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>42.61</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>48.23</t>
+          <t>47.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>4.761904761904762</t>
+          <t>14.28571428571428</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>26.72391360915949</t>
+          <t>15.63882383554513</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-53.66</t>
+          <t>73.98</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1160,27 +1170,27 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-789721.8</t>
+          <t>-207126.8</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-513926.2</t>
+          <t>-795933.8</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-73</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-348684.94</t>
+          <t>-138261.1070419265</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-216714.48</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1190,100 +1200,105 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
           <t>譜瑞-KY</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>半導體業</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AP3" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
           <t>-5.062816287608069</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>-3.412094994647266</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>5.211217380242647</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
           <t>52.71</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>22.08</t>
-        </is>
-      </c>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>22.19</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>43.11%</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>17.22%</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>49.01</t>
-        </is>
-      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>62205</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
+          <t>62525</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
           <t>高速訊號傳輸介面晶片44.78%、DisplayPort系列(DP)38.99%、Source Drivers12.74%、TrueTouch系列3.49% (2024年)</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>譜瑞-KY-半導體業-上櫃</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>半導體業平</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>252.85</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>** 半導體 - 平面顯示器驅動IC</t>
         </is>
@@ -1292,12 +1307,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>建議關注股;多頭排列股</t>
+          <t>弱勢突破股</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1307,12 +1322,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1322,17 +1337,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1357,7 +1372,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1377,67 +1392,67 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>201</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>16.8575</t>
+          <t>17.0125</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>15.536</t>
+          <t>15.571</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-17.65</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>21.2121212121211</t>
+          <t>15.15151515151517</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>11.94805194805183</t>
+          <t>14.14141414141406</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>62.39</t>
+          <t>65.64</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1447,27 +1462,27 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-1906.8</t>
+          <t>-1650.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-5069.3</t>
+          <t>-4801.4</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-62</t>
+          <t>-65</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-737.56</t>
+          <t>-714.4372455105871</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-756.37</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1477,100 +1492,105 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
           <t>李洲</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AP4" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
           <t>200.283758971791</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>125.7025761124122</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>20.94933089328606</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
           <t>0.60</t>
         </is>
       </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>15.96%</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>-47.47%</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>95.5</t>
-        </is>
-      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>94.73</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
+          <t>1421</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
           <t>LED 光電產品93.51%、磊晶片6.32%、其他0.17% (2024年)</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>李洲-光電業-上櫃</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>12.69</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>** LED照明產業 - 封裝/模組、燈具/應用</t>
         </is>
@@ -1579,12 +1599,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>弱勢突破股</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1594,12 +1614,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3166.044</t>
+          <t>2775.103</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1609,17 +1629,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7.60</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1639,92 +1659,92 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>39</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.09</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.705</t>
+          <t>41.744</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-64.53</t>
+          <t>-73.08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>33.33333333333314</t>
+          <t>39.99999999999962</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>11.11111111111106</t>
+          <t>24.44444444444427</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-58.98</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1734,27 +1754,27 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-49272242.4</t>
+          <t>-50901769.4</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-30993131.6</t>
+          <t>-54992938.5</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-12287514.19</t>
+          <t>-13643769.74968577</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-17132315.55</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1764,100 +1784,105 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
           <t>興富發</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>建材營造</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AP5" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
           <t>-63.40863348097227</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>-44.53237722684639</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>-58.46140979330202</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
+          <t>5.98</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
           <t>2.28</t>
         </is>
       </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>15.26</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>20.37%</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>7.22%</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>16.63</t>
-        </is>
-      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>86756</t>
+          <t>16.59</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
+          <t>86549</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
           <t>建設業務99.44%、百貨0.38%、營造0.18% (2024年)</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>興富發-建材營造-上市</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>建材營造平</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>24.27</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>** 建材營造 - 建設業</t>
         </is>
@@ -1866,12 +1891,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>多頭排列股</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1881,12 +1906,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2592.393</t>
+          <t>2805.62</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1896,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>281.0</t>
+          <t>277.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1921,24 +1946,24 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>-3.0</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>價-量-</t>
@@ -1946,32 +1971,32 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>81</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>278.9</t>
+          <t>280.1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1981,37 +2006,37 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>281.01</t>
+          <t>280.95</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>75.86206896551724</t>
+          <t>48.27586206896552</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>83.62068965517243</t>
+          <t>74.71264367816092</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>297.31</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2021,27 +2046,27 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>293464816.4</t>
+          <t>340041811.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>73862478.9</t>
+          <t>165640647.3</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>8320462.88</t>
+          <t>-11032192.81376723</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-66023374.85</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2051,100 +2076,105 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
           <t>技嘉</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AP6" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
           <t>8.811722960289302</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>45.46314217201299</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>32.12491672435991</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>3.62</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
           <t>152.65</t>
         </is>
       </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>17.17</t>
-        </is>
-      </c>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>16.92</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>9.42%</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>5.18%</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>29.12</t>
-        </is>
-      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>188239</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
+          <t>185559</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
           <t>網路通訊產品64.27%、電腦配件31.22%、其他4.51% (2024年)</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>技嘉-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>77.62</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、主機板、機殼、電源供應器、散熱片、風扇馬達、散熱模組、顯示卡、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
@@ -2153,12 +2183,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>弱勢突破股</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2168,12 +2198,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2199.604</t>
+          <t>2036.456</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2183,17 +2213,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2208,24 +2238,24 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>價-量-</t>
@@ -2233,27 +2263,27 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -2263,42 +2293,42 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>11.0975</t>
+          <t>11.13</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>10.6398</t>
+          <t>10.659</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-36.60</t>
+          <t>-41.99</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>83.33333333333339</t>
+          <t>60.00000000000014</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>63.88888888888894</t>
+          <t>70.00000000000007</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>127.57</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2308,27 +2338,27 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>937092.4</t>
+          <t>-350630.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-3399536.7</t>
+          <t>-1248708.1</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-127</t>
+          <t>-71</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>5600230.06</t>
+          <t>-844300.4051654871</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3344451.88</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2338,100 +2368,105 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
           <t>錸德</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AP7" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
           <t>7.266079007508978</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>29.43204577292231</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>8.178446379053689</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
           <t>3.29</t>
         </is>
       </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>14.57%</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>0.16%</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>158.81</t>
-        </is>
-      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
+          <t>7561</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
           <t>光學產品84.42%、其他15.58% (2024年)</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>錸德-光電業-上市</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>光電業平</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>7.63</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 光碟片</t>
         </is>
@@ -2440,12 +2475,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>弱勢突破股</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2455,12 +2490,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10836.889</t>
+          <t>23152.125</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2470,12 +2505,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2500,92 +2535,92 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>10837</t>
+          <t>23152</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.925</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>121.27</t>
+          <t>121.73</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-38.33</t>
+          <t>-33.10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>63.63636363636363</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>51.51515151515152</t>
+          <t>74.62121212121212</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>150.15</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2595,27 +2630,27 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>158406069.0</t>
+          <t>-103407672.8</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-315880593.0</t>
+          <t>-941987380.6</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-150</t>
+          <t>-89</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>236652278.7</t>
+          <t>-12081327.92350463</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6266600.51</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2625,100 +2660,105 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
           <t>光寶科</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AP8" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
           <t>1.409424233691332</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>7.352888368225501</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>20.99056536095143</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AT8" t="inlineStr">
         <is>
           <t>3.67</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AU8" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="AU8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>17.81</t>
         </is>
       </c>
-      <c r="AV8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>22.61</t>
         </is>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>22.12%</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>9.22%</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>29.12</t>
-        </is>
-      </c>
       <c r="AZ8" t="inlineStr">
         <is>
+          <t>28.93</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
           <t>304353</t>
         </is>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>資訊及消費性電子43.00%、雲端及物聯網37.00%、光電通訊20.00% (2024年)</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>光寶科-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右上</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>35.46</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>** 汽車 - 銷售、進出口業務、車燈、其他** 電腦及週邊設備 - 機殼、電源供應器、伺服器、其他電腦及週邊設備、安全監控系統** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 其他 - 其他電子產品及電子服務產業** 雲端運算 - 電力設備、冷卻設備、雲端應用服務、系統整合、顧問諮詢、設備安裝服務、IaaS、PaaS、SaaS** 體驗科技 - 環境感知、深度感測、視覺、手勢/動作** LED照明產業 - 封裝/模組、燈具/應用** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 智慧電網 - 配電管理設施** 醫療器材 - 醫療耗材、生物檢測</t>
         </is>
@@ -2727,12 +2767,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>弱勢突破股;建議關注股;多頭排列股</t>
+          <t>弱勢突破股</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2742,137 +2782,137 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>-1.7</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>846.852</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1463.697</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>7.18</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-0.84</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-6.39</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>24.73</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>25.0975</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>24.737</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>-147.30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>1464</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>-6.70</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>25.24</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>25.16</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>24.759</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>-51.61</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>33.33333333333312</t>
+          <t>16.66666666666652</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-480.85</t>
+          <t>-103.29</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2882,130 +2922,135 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-4283037.6</t>
+          <t>-5715292.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>1124606.8</t>
+          <t>-2811343.9</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-480</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1803147.92</t>
+          <t>-251984.24075151</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>-2893391.29</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
           <t>橋椿</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>居家生活</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="AP9" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
           <t>7.751419501579042</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>-10.38604692305599</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>-22.74807474555465</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
+          <t>7.78</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
           <t>7.59</t>
         </is>
       </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
-      </c>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>18.67</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
           <t>8.32%</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>-1.03%</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>14.9</t>
-        </is>
-      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
+          <t>4630</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
           <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>橋椿-居家生活-上市</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>35.8</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>** 其他 - 其他</t>
         </is>
@@ -3014,12 +3059,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>弱勢突破股</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3029,12 +3074,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3044,17 +3089,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>50.26</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3074,22 +3119,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>79</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -3099,202 +3144,499 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>98</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>-1.94</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>31.7</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>32.3275</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>31.643</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>-127.94</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>44.73684210526299</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>38.59649122807011</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>-82.20</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>893.2</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>-82</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>-14.13600617256148</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>59.9</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>宏佳騰</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.5502992040917953</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-62.96013378851607</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>-7.737807792515493</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>6.79</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>32.7</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>20.81%</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>-4.48%</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>35.64</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>2389</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>ATV/ UTV64.10%、摩托車14.76%、電動車輛13.19%、零組件及其他7.95% (2024年)</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>宏佳騰-電機機械-上櫃</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>電機機械右下</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>多頭排列股</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>41530.248</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>34.97</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>22.45</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>41530</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>-2.09</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>31.69</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>32.36499999999999</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>31.584</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>-124.33</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>28.94736842105264</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>28.94736842105264</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>-239.67</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>-3.39</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>-1.94</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>22.93</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>23.735</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>24.205</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>-24.70</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>-46.11</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>-687.6</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>492.3</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-239</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-198.5</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>宏佳騰</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-0.5502992040917953</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-62.96013378851607</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-7.737807792515493</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>6.79</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>32.4</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>20.81%</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>-4.48%</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>35.92</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2366</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>ATV/ UTV64.10%、摩托車14.76%、電動車輛13.19%、零組件及其他7.95% (2024年)</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>宏佳騰-電機機械-上櫃</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>電機機械右下</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>-475051133.8</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>-325122812.1</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>-53429463.92338758</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>-106940990.65</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>水泥工業</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>33.91465883488689</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-6.193883484790765</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>5.87318368368304</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>21.8</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>15.12%</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>3.15%</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>30.73</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>169524</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>台泥-水泥工業-上市</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>水泥工業右下</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>28.5</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,122 +738,122 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4046.309</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>29.78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>267.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2210.719</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>16.27</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>264.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>95</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>255.3</t>
+          <t>259.9</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>243.25</t>
+          <t>244.975</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>233.76</t>
+          <t>234.85</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>33.92</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>87.68115942028986</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>17.90</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -878,27 +878,27 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>448730265.8</t>
+          <t>560207621.8</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>423483390.2</t>
+          <t>475153690.2</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>55968279.66289203</t>
+          <t>61210447.2101293</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>35865401.87</t>
+          <t>90042368.72</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -963,27 +963,27 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>50.57</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>22.79%</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>12.35%</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>22.79%</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>12.35%</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>50.98</t>
-        </is>
-      </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>83827</t>
+          <t>84780</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1134.0</t>
+          <t>2015.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>781.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>76</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1085,82 +1085,82 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-19.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>90</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>15.30</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>786.4</t>
+          <t>781.4</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>755.3</t>
+          <t>760.85</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>655.1</t>
+          <t>658.96</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-9.54</t>
+          <t>-16.60</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>42.61</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>47.10</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14.28571428571428</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>15.63882383554513</t>
+          <t>6.34920634920633</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>73.98</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1170,27 +1170,27 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-207126.8</t>
+          <t>-261279.4</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-795933.8</t>
+          <t>-654449.9</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-73</t>
+          <t>-60</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-138261.1070419265</t>
+          <t>-163157.8815007637</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-216714.48</t>
+          <t>-300090.14</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>62525</t>
+          <t>60284</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1362,97 +1362,97 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-2.89</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>9.78</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>16.94</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>17.125</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>15.599</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>-27.78</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>9.26</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>17.09</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>17.0125</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>15.571</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>-17.65</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15.15151515151517</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>14.14141414141406</t>
+          <t>12.12121212121208</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>65.64</t>
+          <t>66.66</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1462,27 +1462,27 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-1650.0</t>
+          <t>-1501.6</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-4801.4</t>
+          <t>-4503.7</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-65</t>
+          <t>-66</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-714.4372455105871</t>
+          <t>-710.2202888706809</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-756.37</t>
+          <t>-687.03</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>94.73</t>
+          <t>90.99</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2775.103</t>
+          <t>3339.962</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1654,22 +1654,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1679,72 +1679,72 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>48</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>42.09</t>
+          <t>42.05499999999999</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.744</t>
+          <t>41.788</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-73.08</t>
+          <t>-44.47</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>39.99999999999962</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>24.44444444444427</t>
+          <t>57.7777777777776</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>43.69</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-50901769.4</t>
+          <t>-39056110.8</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-54992938.5</t>
+          <t>-69357388.9</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-43</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-13643769.74968577</t>
+          <t>-11669529.00260795</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-17132315.55</t>
+          <t>-811204.89</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>15.26</t>
+          <t>15.42</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>16.59</t>
+          <t>16.47</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>86549</t>
+          <t>87481</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2805.62</t>
+          <t>4840.387</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>277.0</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1946,97 +1946,97 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>280.1</t>
+          <t>277.9</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>280.15</t>
+          <t>279.8</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>280.95</t>
+          <t>280.74</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-106.82</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>48.27586206896552</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>74.71264367816092</t>
+          <t>41.37931034482759</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>-614.60</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>340041811.0</t>
+          <t>-151382358.8</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>165640647.3</t>
+          <t>-21184280.5</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>614</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-11032192.81376723</t>
+          <t>-33280991.17979264</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-66023374.85</t>
+          <t>-155649382.19</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>28.26</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>185559</t>
+          <t>178525</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2036.456</t>
+          <t>2348.156</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2213,17 +2213,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2243,67 +2243,67 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>11.13</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>10.659</t>
+          <t>10.6804</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-41.99</t>
+          <t>-40.38</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2313,22 +2313,22 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>60.00000000000014</t>
+          <t>80.00000000000007</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>70.00000000000007</t>
+          <t>74.44444444444451</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>461.69</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2338,27 +2338,27 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-350630.0</t>
+          <t>9230078.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-1248708.1</t>
+          <t>-2551898.8</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-71</t>
+          <t>-461</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-844300.4051654871</t>
+          <t>98471.2927463468</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3344451.88</t>
+          <t>5283715.63</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>158.74</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2490,137 +2490,137 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>13897.98</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>10.83</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.96</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>23152.125</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>18.05</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-3.85</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>187</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>23152</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>128.4</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>130.925</t>
+          <t>131.15</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>121.73</t>
+          <t>122.13</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-33.10</t>
+          <t>-41.31</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>74.62121212121212</t>
+          <t>62.87878787878788</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>13.47</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2630,27 +2630,27 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-103407672.8</t>
+          <t>-714980596.4</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-941987380.6</t>
+          <t>-826261249.3</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-89</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-12081327.92350463</t>
+          <t>-22422371.68914159</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6266600.51</t>
+          <t>-79298112.4</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>21.91</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>28.26</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>304353</t>
+          <t>294988</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>846.852</t>
+          <t>594.633</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2797,17 +2797,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2822,97 +2822,97 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>-5.0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-6.99</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>-3.75</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>24.03</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>24.965</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>24.708</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>-503.36</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>847</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>-6.39</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>-1.46</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>24.73</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>25.0975</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>24.737</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>-147.30</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>16.66666666666652</t>
-        </is>
-      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-103.29</t>
+          <t>-323.25</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2922,27 +2922,27 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-5715292.0</t>
+          <t>-11183761.4</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>-2811343.9</t>
+          <t>-2642349.1</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>323</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-251984.24075151</t>
+          <t>-692794.8803996872</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2893391.29</t>
+          <t>-3117253.4</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>50.26</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3114,72 +3114,72 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>76</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.86</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>32.3275</t>
+          <t>32.2775</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>31.643</t>
+          <t>31.708</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-127.94</t>
+          <t>-138.58</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>44.73684210526299</t>
+          <t>42.10526315789473</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-82.20</t>
+          <t>-35.79</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3214,27 +3214,27 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>485.6</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>893.2</t>
+          <t>756.3</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-82</t>
+          <t>-35</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-14.13600617256148</t>
+          <t>-12.62457796381608</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>35.64</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>41530.248</t>
+          <t>19170.872</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3381,17 +3381,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -3421,67 +3421,67 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>41530</t>
+          <t>19171</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
+          <t>-1.72</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>-3.83</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>-2.09</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>-3.39</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>23.735</t>
+          <t>23.645</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>24.205</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-24.70</t>
+          <t>-25.48</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-46.11</t>
+          <t>-46.33</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-475051133.8</t>
+          <t>-671416820.4</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-325122812.1</t>
+          <t>-458837895.7</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-53429463.92338758</t>
+          <t>-58682255.68481097</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-106940990.65</t>
+          <t>-87572610.37</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>30.58</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>169524</t>
+          <t>168769</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4046.309</t>
+          <t>3826.383</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,17 +753,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>28.16</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>267.0</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -778,82 +778,82 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>74</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>92</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>259.9</t>
+          <t>263.7</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>244.975</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>234.85</t>
+          <t>235.79</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>35.38</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -868,37 +868,37 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>17.90</t>
+          <t>87.60</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>560207621.8</t>
+          <t>671033604.2</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>475153690.2</t>
+          <t>357694379.4</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>61210447.2101293</t>
+          <t>70537829.09613542</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>90042368.72</t>
+          <t>121838429.47</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>50.57</t>
+          <t>51.14</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.68</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>84780</t>
+          <t>85733</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2015.0</t>
+          <t>871.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>749.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1070,82 +1070,82 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>60</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>-16.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>871</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>781.4</t>
+          <t>770.4</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>760.85</t>
+          <t>764.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>658.96</t>
+          <t>662.32</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-16.60</t>
+          <t>-22.59</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>33.14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>45.23</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>6.34920634920633</t>
+          <t>4.761904761904742</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>-83.72</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1170,27 +1170,27 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-261279.4</t>
+          <t>-771726.8</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-654449.9</t>
+          <t>-420062.1</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-60</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-163157.8815007637</t>
+          <t>-182024.3654123883</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-300090.14</t>
+          <t>-285790.03</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>60284</t>
+          <t>59963</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>半導體業平</t>
+          <t>半導體業右下</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1362,22 +1362,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1387,57 +1387,57 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>109</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>16.94</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>17.125</t>
+          <t>17.2175</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>15.599</t>
+          <t>15.615</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-27.78</t>
+          <t>-38.39</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>12.12121212121208</t>
+          <t>5.050505050505046</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>66.66</t>
+          <t>64.10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1462,27 +1462,27 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-1501.6</t>
+          <t>-1475.6</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-4503.7</t>
+          <t>-4110.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-66</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-710.2202888706809</t>
+          <t>-686.3188462321152</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-687.03</t>
+          <t>-554.86</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>90.99</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3339.962</t>
+          <t>1903.963</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1654,17 +1654,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1679,52 +1679,52 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>41</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>42.05499999999999</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.788</t>
+          <t>41.81399999999999</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-44.47</t>
+          <t>-17.27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1739,12 +1739,12 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>57.7777777777776</t>
+          <t>79.99999999999989</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>119.86</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-39056110.8</t>
+          <t>8575025.4</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-69357388.9</t>
+          <t>-43172868.3</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-43</t>
+          <t>-119</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-11669529.00260795</t>
+          <t>-8930183.753651159</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-811204.89</t>
+          <t>6136215.12</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>15.42</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>16.47</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>87481</t>
+          <t>87584</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4840.387</t>
+          <t>3230.777</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>263.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1951,77 +1951,77 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>112</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>277.9</t>
+          <t>274.5</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>279.8</t>
+          <t>279.075</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>280.74</t>
+          <t>280.33</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-106.82</t>
+          <t>-127.17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>41.37931034482759</t>
+          <t>16.09195402298851</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-614.60</t>
+          <t>-109.92</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-151382358.8</t>
+          <t>-542463036.2</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-21184280.5</t>
+          <t>-258415031.8</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-33280991.17979264</t>
+          <t>-55996703.71376923</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-155649382.19</t>
+          <t>-180933122.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>28.26</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>178525</t>
+          <t>176515</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2348.156</t>
+          <t>2386.6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2213,17 +2213,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2238,97 +2238,97 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2387</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>-1.09</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>-1.59</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>11.1475</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>10.6954</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>-49.14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>2348</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>-1.61</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>10.97</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>11.15</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>10.6804</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>-40.38</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>80.00000000000007</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>74.44444444444451</t>
+          <t>46.66666666666672</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>461.69</t>
+          <t>478.47</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2338,27 +2338,27 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>9230078.0</t>
+          <t>6446689.8</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-2551898.8</t>
+          <t>-1703376.7</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-461</t>
+          <t>-478</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>98471.2927463468</t>
+          <t>487578.8580331727</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5283715.63</t>
+          <t>2627670.47</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>158.74</t>
+          <t>160.6</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13897.98</t>
+          <t>12192.391</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2535,47 +2535,47 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>144</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -2585,42 +2585,42 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>131.15</t>
+          <t>130.725</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>122.13</t>
+          <t>122.45</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-41.31</t>
+          <t>-51.90</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>14.28571428571428</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>62.87878787878788</t>
+          <t>46.42857142857142</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>-42.60</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2630,27 +2630,27 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-714980596.4</t>
+          <t>-797122621.2</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-826261249.3</t>
+          <t>-558996127.6</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-22422371.68914159</t>
+          <t>-35971756.40411512</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-79298112.4</t>
+          <t>-110493372.34</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>21.91</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>28.26</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>294988</t>
+          <t>292647</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>594.633</t>
+          <t>546.178</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2797,17 +2797,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2822,82 +2822,82 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>-5.0</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>546</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.965</t>
+          <t>24.825</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>24.708</t>
+          <t>24.661</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-503.36</t>
+          <t>-1147.79</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-323.25</t>
+          <t>-97.51</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2922,27 +2922,27 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-11183761.4</t>
+          <t>-10161677.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>-2642349.1</t>
+          <t>-5144863.5</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-692794.8803996872</t>
+          <t>-1062040.658237963</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3117253.4</t>
+          <t>-3092892.44</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>47.18</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3114,77 +3114,77 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>98</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>92</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>31.86</t>
+          <t>32.16</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>32.2775</t>
+          <t>32.26000000000001</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>31.708</t>
+          <t>31.783</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-138.58</t>
+          <t>-19.24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -3194,17 +3194,17 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>42.10526315789473</t>
+          <t>94.73684210526308</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>38.59649122807011</t>
+          <t>60.52631578947361</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-35.79</t>
+          <t>-16.57</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3214,27 +3214,27 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>485.6</t>
+          <t>949.2</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>756.3</t>
+          <t>1137.7</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-35</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-12.62457796381608</t>
+          <t>17.54766906806073</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>33.67</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19170.872</t>
+          <t>26563.11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3381,17 +3381,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>22.37</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3406,97 +3406,97 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>26563</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>-4.20</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>22.54</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>23.5275</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>24.077</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>-26.72</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>19171</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-1.72</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>-3.83</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>22.74</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>23.645</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>24.15</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>-25.48</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-46.33</t>
+          <t>-43.01</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -3506,27 +3506,27 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-671416820.4</t>
+          <t>-611324601.2</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-458837895.7</t>
+          <t>-427462360.8</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-58682255.68481097</t>
+          <t>-62541343.74743845</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-87572610.37</t>
+          <t>-83766328.09</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>30.58</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>168769</t>
+          <t>166881</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3826.383</t>
+          <t>2422.699</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,12 +753,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>28.16</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -783,77 +783,77 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>46</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>263.7</t>
+          <t>267.0</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>249.05</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>235.79</t>
+          <t>236.72</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>35.38</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -868,37 +868,37 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>87.60</t>
+          <t>17.19</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>671033604.2</t>
+          <t>465464109.6</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>357694379.4</t>
+          <t>397172250.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>70537829.09613542</t>
+          <t>61944434.55548447</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>121838429.47</t>
+          <t>14680764.58</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>49.68</t>
+          <t>51.51</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>85733</t>
+          <t>85767</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>871.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>11.55</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>749.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1075,92 +1075,92 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>54</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-16.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>770</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>770.4</t>
+          <t>763.2</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>764.8</t>
+          <t>769.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>662.32</t>
+          <t>665.78</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-22.59</t>
+          <t>-26.03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>33.14</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.72727272727273</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>4.761904761904742</t>
+          <t>4.242424242424224</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-83.72</t>
+          <t>-171.87</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1170,27 +1170,27 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-771726.8</t>
+          <t>-442276.6</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-420062.1</t>
+          <t>-162676.9</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-182024.3654123883</t>
+          <t>-181027.46633118</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-285790.03</t>
+          <t>-175544.52</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>49.02</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>59963</t>
+          <t>60524</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>半導體業右下</t>
+          <t>半導體業平</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1387,22 +1387,22 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>94</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1412,32 +1412,32 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>16.61</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>17.2175</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>15.615</t>
+          <t>15.627</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-38.39</t>
+          <t>-50.31</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>5.050505050505046</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>64.10</t>
+          <t>76.02</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1462,27 +1462,27 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-1475.6</t>
+          <t>-1395.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-4110.0</t>
+          <t>-5817.8</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>-76</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-686.3188462321152</t>
+          <t>-646.9233480402773</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-554.86</t>
+          <t>-430.25</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>91.83</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1599,12 +1599,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>反彈型股</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1903.963</t>
+          <t>2689.345</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,12 +1629,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1664,12 +1664,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1679,52 +1679,52 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>42.075</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.81399999999999</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.27</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1739,12 +1739,12 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>79.99999999999989</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>119.86</t>
+          <t>173.27</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>8575025.4</t>
+          <t>24723421.6</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-43172868.3</t>
+          <t>-33744879.3</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-119</t>
+          <t>-173</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8930183.753651159</t>
+          <t>-8123628.400131791</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6136215.12</t>
+          <t>-3687573.96</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3230.777</t>
+          <t>1331.18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>263.5</t>
+          <t>264.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1946,22 +1946,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1971,72 +1971,72 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>38</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>274.5</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>279.075</t>
+          <t>278.375</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>280.33</t>
+          <t>279.92</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-127.17</t>
+          <t>-109.53</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.380952380952381</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>16.09195402298851</t>
+          <t>0.7936507936508032</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-109.92</t>
+          <t>-1953.01</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-542463036.2</t>
+          <t>-663677374.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-258415031.8</t>
+          <t>-32327020.3</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-55996703.71376923</t>
+          <t>-63309171.52007706</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-180933122.65</t>
+          <t>-103527744.45</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>176515</t>
+          <t>176850</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2386.6</t>
+          <t>1076.525</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2238,22 +2238,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -2263,57 +2263,57 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>11.1475</t>
+          <t>11.1425</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>10.6954</t>
+          <t>10.7084</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-49.14</t>
+          <t>-56.95</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>46.66666666666672</t>
+          <t>26.66666666666667</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>478.47</t>
+          <t>-579.15</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2338,27 +2338,27 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6446689.8</t>
+          <t>-2086666.8</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-1703376.7</t>
+          <t>435494.2</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-478</t>
+          <t>-579</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>487578.8580331727</t>
+          <t>687850.974570753</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2627670.47</t>
+          <t>1789347.62</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>160.6</t>
+          <t>160.03</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12192.391</t>
+          <t>4836.067</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2545,67 +2545,67 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-14.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>78</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>128.4</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>130.725</t>
+          <t>130.325</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>122.45</t>
+          <t>122.76</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-51.90</t>
+          <t>-61.59</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>46.42857142857142</t>
+          <t>22.02380952380952</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-42.60</t>
+          <t>-325.69</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2630,27 +2630,27 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-797122621.2</t>
+          <t>-1670940573.8</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-558996127.6</t>
+          <t>-392522629.6</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>325</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-35971756.40411512</t>
+          <t>-39812290.92401819</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-110493372.34</t>
+          <t>-60935230.78</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>546.178</t>
+          <t>422.397</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2797,17 +2797,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2822,22 +2822,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2847,57 +2847,57 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>422</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.825</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>24.661</t>
+          <t>24.615</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-1147.79</t>
+          <t>-301.56</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-97.51</t>
+          <t>-260.23</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2922,27 +2922,27 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-10161677.0</t>
+          <t>-17799039.2</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>-5144863.5</t>
+          <t>-4941050.8</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>260</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1062040.658237963</t>
+          <t>-1328589.684194959</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3092892.44</t>
+          <t>-2794609.33</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>17.74</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>47.18</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3114,27 +3114,27 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>54</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>-44.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -3144,67 +3144,67 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>32.26000000000001</t>
+          <t>32.205</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>31.783</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-19.24</t>
+          <t>-29.72</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>94.73684210526308</t>
+          <t>50.0000000000001</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>60.52631578947361</t>
+          <t>62.28070175438597</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-16.57</t>
+          <t>13.62</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3214,27 +3214,27 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>949.2</t>
+          <t>828.4</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>1137.7</t>
+          <t>729.1</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>17.54766906806073</t>
+          <t>23.3437780485388</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>55.22</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>33.67</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>34.91</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26563.11</t>
+          <t>16378.731</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3381,17 +3381,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3406,97 +3406,97 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>52</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-21.0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>134</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>26563</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>23.5275</t>
+          <t>23.4275</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>24.077</t>
+          <t>24.01</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-26.72</t>
+          <t>-21.38</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.83333333333335</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.94444444444443</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-43.01</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -3506,27 +3506,27 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-611324601.2</t>
+          <t>-442354832.8</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-427462360.8</t>
+          <t>-461238398.1</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-62541343.74743845</t>
+          <t>-54044952.47368902</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-83766328.09</t>
+          <t>-7314800.47</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>166881</t>
+          <t>168769</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,122 +738,122 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8522.348</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>62.72</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-7.93</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>271.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2422.699</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>17.83</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>270.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>152</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>267.0</t>
+          <t>268.4</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>249.05</t>
+          <t>250.7</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>236.72</t>
+          <t>237.54</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>27.52</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>17.19</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -878,27 +878,27 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>465464109.6</t>
+          <t>660308254.2</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>397172250.0</t>
+          <t>579806755.8</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>61944434.55548447</t>
+          <t>78320728.26175937</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>14680764.58</t>
+          <t>168390343.65</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>51.14</t>
+          <t>51.33</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>51.51</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>85767</t>
+          <t>86085</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>2510.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11.55</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>784.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1070,97 +1070,97 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>62</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>70</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>763.2</t>
+          <t>764.6</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>769.2</t>
+          <t>774.95</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>665.78</t>
+          <t>669.74</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-26.03</t>
+          <t>-23.69</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12.72727272727273</t>
+          <t>63.63636363636363</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>4.242424242424224</t>
+          <t>25.45454545454544</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-171.87</t>
+          <t>195.69</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1170,27 +1170,27 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-442276.6</t>
+          <t>255564.8</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-162676.9</t>
+          <t>-267078.5</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>-195</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-181027.46633118</t>
+          <t>-151544.2875834089</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-175544.52</t>
+          <t>10613.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>48.52</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>60524</t>
+          <t>62765</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1362,127 +1362,127 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-4.31</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>9.81</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>16.44</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>15.645</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>-55.76</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>26.08695652173922</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>8.695652173913066</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>6.98</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-1658.0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>-1782.4</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-3.37</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>-3.60</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>10.26</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>16.61</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>17.23</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>15.627</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>-50.31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>76.02</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-1395.0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>-5817.8</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-76</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-646.9233480402773</t>
+          <t>-567.9486702911817</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-430.25</t>
+          <t>-133.59</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>92.99</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1599,12 +1599,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>反彈型股</t>
+          <t>強勢股;反彈型股</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1614,122 +1614,122 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>7.79</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>32270.156</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>77.48</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6.80</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2689.345</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>6.46</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>88</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>369</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>32270</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>42.84999999999999</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>42.075</t>
+          <t>42.2575</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>41.902</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>153.77</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1744,37 +1744,37 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>173.27</t>
+          <t>141.10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>24723421.6</t>
+          <t>289049604.2</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-33744879.3</t>
+          <t>119888680.9</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-173</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8123628.400131791</t>
+          <t>9600451.329603653</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3687573.96</t>
+          <t>107082889.84</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>15.44</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>87584</t>
+          <t>94417</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1331.18</t>
+          <t>1639.114</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>264.0</t>
+          <t>265.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1946,97 +1946,97 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-9.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>267.2</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>278.375</t>
+          <t>277.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>279.92</t>
+          <t>279.54</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-109.53</t>
+          <t>-86.01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2.380952380952381</t>
+          <t>7.142857142857142</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.7936507936508032</t>
+          <t>3.174603174603184</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-1953.01</t>
+          <t>-530.17</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-663677374.0</t>
+          <t>-429907645.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-32327020.3</t>
+          <t>-68221414.3</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>530</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-63309171.52007706</t>
+          <t>-59779347.52564854</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-103527744.45</t>
+          <t>-40365315.56</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>28.01</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>176850</t>
+          <t>177520</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2198,64 +2198,64 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2775.512</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11.15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1076.525</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10.85</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>價-量-</t>
@@ -2263,32 +2263,32 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -2298,37 +2298,37 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>10.7084</t>
+          <t>10.7254</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-56.95</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>26.66666666666667</t>
+          <t>33.33333333333331</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-579.15</t>
+          <t>-1217.25</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2338,27 +2338,27 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-2086666.8</t>
+          <t>-794812.2</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>435494.2</t>
+          <t>71140.1</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-579</t>
+          <t>-1217</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>687850.974570753</t>
+          <t>1249913.771410787</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1789347.62</t>
+          <t>4341259.15</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>160.03</t>
+          <t>162.74</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2490,137 +2490,137 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>12344.708</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>9.62</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.59</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>4836.067</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>3.77</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-14.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>350</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>127.2</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>130.325</t>
+          <t>129.725</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>122.76</t>
+          <t>123.05</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-61.59</t>
+          <t>-68.46</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14.28571428571428</t>
+          <t>8.333333333333332</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>22.02380952380952</t>
+          <t>12.3015873015873</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-325.69</t>
+          <t>-134.53</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2630,27 +2630,27 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-1670940573.8</t>
+          <t>-1075811790.2</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-392522629.6</t>
+          <t>-458702860.6</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-39812290.92401819</t>
+          <t>-12506327.4667552</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-60935230.78</t>
+          <t>137676471.55</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.83</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>28.01</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>292647</t>
+          <t>293818</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2767,12 +2767,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>多頭排列股</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>422.397</t>
+          <t>458.173</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2797,17 +2797,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2832,87 +2832,87 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>458</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.535</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>24.615</t>
+          <t>24.572</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-301.56</t>
+          <t>-167.40</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.194805194805174</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.731601731601725</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-260.23</t>
+          <t>-34.74</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2922,27 +2922,27 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-17799039.2</t>
+          <t>-8842879.8</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>-4941050.8</t>
+          <t>-6562958.7</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1328589.684194959</t>
+          <t>-1286229.354659035</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2794609.33</t>
+          <t>-1053247.54</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>17.74</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>11.79</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3114,97 +3114,97 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>65</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-44.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>32.205</t>
+          <t>32.125</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>31.868</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-29.72</t>
+          <t>-138.05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>50.0000000000001</t>
+          <t>13.88888888888888</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>62.28070175438597</t>
+          <t>52.87524366471735</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>535.19</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3214,27 +3214,27 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>828.4</t>
+          <t>1003.6</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>729.1</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>535</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>23.3437780485388</t>
+          <t>10.10257570162339</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>55.22</t>
+          <t>-62.72</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.76</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>18286.009</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>15.40</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>16378.731</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>13.79</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3406,97 +3406,97 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-21.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>163</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>18286</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>23.4275</t>
+          <t>23.345</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>24.01</t>
+          <t>23.947</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-21.38</t>
+          <t>-12.34</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20.83333333333335</t>
+          <t>45.83333333333313</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>6.94444444444443</t>
+          <t>22.22222222222214</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>32.90</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -3506,27 +3506,27 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-442354832.8</t>
+          <t>-235544735.8</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-461238398.1</t>
+          <t>-351041635.9</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-32</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-54044952.47368902</t>
+          <t>-38069176.32307376</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7314800.47</t>
+          <t>49797592.51</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>168769</t>
+          <t>171034</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF11"/>
+  <dimension ref="A1:BF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -723,7 +723,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>強勢股;反彈型股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -733,17 +733,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8522.348</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,17 +753,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -773,102 +773,102 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>61</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>268.4</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>250.7</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>237.54</t>
+          <t>15.645</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>27.52</t>
+          <t>-55.76</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>26.08695652173922</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>8.695652173913066</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -878,144 +878,144 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>660308254.2</t>
+          <t>-1658.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>579806755.8</t>
+          <t>-1782.4</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>78320728.26175937</t>
+          <t>-567.9486702911817</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>168390343.65</t>
+          <t>-133.59</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>李洲</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.644811051273512</t>
+          <t>200.283758971791</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-20.18542484584181</t>
+          <t>125.7025761124122</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-6.47127141471608</t>
+          <t>20.94933089328606</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>51.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>22.79%</t>
+          <t>15.96%</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12.35%</t>
+          <t>-47.47%</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>95.44</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>86085</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>影像感測器67.42%、微光學元件30.36%、其他2.22% (2024年)</t>
+          <t>LED 光電產品93.51%、磊晶片6.32%、其他0.17% (2024年)</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>采鈺-半導體業-上市</t>
+          <t>李洲-光電業-上櫃</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>半導體業平</t>
+          <t>光電業右下</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>** 半導體 - 生產製程及檢測設備</t>
+          <t>** LED照明產業 - 封裝/模組、燈具/應用</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>強勢股;【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2510.0</t>
+          <t>32270.156</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>37.67</t>
+          <t>77.48</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>784.0</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1065,27 +1065,27 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>88</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1095,102 +1095,102 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>24972</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>764.6</t>
+          <t>42.84999999999999</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>774.95</t>
+          <t>42.2575</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>669.74</t>
+          <t>41.902</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-23.69</t>
+          <t>153.77</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>63.63636363636363</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>25.45454545454544</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>195.69</t>
+          <t>141.10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>255564.8</t>
+          <t>289049604.2</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-267078.5</t>
+          <t>119888680.9</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-195</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-151544.2875834089</t>
+          <t>9600451.329603653</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10613.2</t>
+          <t>107082889.84</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1205,109 +1205,109 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.062816287608069</t>
+          <t>-63.40863348097227</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-3.412094994647266</t>
+          <t>-44.53237722684639</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>5.211217380242647</t>
+          <t>-58.46140979330202</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>43.11%</t>
+          <t>20.37%</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>17.22%</t>
+          <t>7.22%</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>48.52</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>62765</t>
+          <t>93589</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>高速訊號傳輸介面晶片44.78%、DisplayPort系列(DP)38.99%、Source Drivers12.74%、TrueTouch系列3.49% (2024年)</t>
+          <t>建設業務99.44%、百貨0.38%、營造0.18% (2024年)</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>譜瑞-KY-半導體業-上櫃</t>
+          <t>興富發-建材營造-上市</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>半導體業平</t>
+          <t>建材營造平</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>252.85</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>** 半導體 - 平面顯示器驅動IC</t>
+          <t>** 建材營造 - 建設業</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>458.173</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1357,29 +1357,29 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>價漲量-</t>
@@ -1387,72 +1387,72 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>290</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>24.535</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>15.645</t>
+          <t>24.572</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-55.76</t>
+          <t>-167.40</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>26.08695652173922</t>
+          <t>5.194805194805174</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>8.695652173913066</t>
+          <t>1.731601731601725</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>-34.74</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1462,27 +1462,27 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-1658.0</t>
+          <t>-8842879.8</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-1782.4</t>
+          <t>-6562958.7</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-567.9486702911817</t>
+          <t>-1286229.354659035</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-133.59</t>
+          <t>-1053247.54</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1497,109 +1497,109 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>李洲</t>
+          <t>橋椿</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>200.283758971791</t>
+          <t>7.751419501579042</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>125.7025761124122</t>
+          <t>-10.38604692305599</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>20.94933089328606</t>
+          <t>-22.74807474555465</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>15.96%</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>-47.47%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>92.99</t>
+          <t>14.84</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>LED 光電產品93.51%、磊晶片6.32%、其他0.17% (2024年)</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>李洲-光電業-上櫃</t>
+          <t>橋椿-居家生活-上市</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>光電業右下</t>
+          <t>居家生活右下</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>** LED照明產業 - 封裝/模組、燈具/應用</t>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>強勢股;反彈型股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1609,17 +1609,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32270.156</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>77.48</t>
+          <t>11.79</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1649,132 +1649,132 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>65</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>32270</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.84999999999999</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>42.2575</t>
+          <t>32.125</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>41.902</t>
+          <t>31.868</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>153.77</t>
+          <t>-138.05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>13.88888888888888</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.87524366471735</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>141.10</t>
+          <t>535.19</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>289049604.2</t>
+          <t>1003.6</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>119888680.9</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>535</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>9600451.329603653</t>
+          <t>10.10257570162339</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>107082889.84</t>
+          <t>-62.72</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1789,109 +1789,109 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>宏佳騰</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-63.40863348097227</t>
+          <t>-0.5502992040917953</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-44.53237722684639</t>
+          <t>-62.96013378851607</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-58.46140979330202</t>
+          <t>-7.737807792515493</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>16.64</t>
+          <t>31.79</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>20.37%</t>
+          <t>20.81%</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7.22%</t>
+          <t>-4.48%</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>94417</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>建設業務99.44%、百貨0.38%、營造0.18% (2024年)</t>
+          <t>ATV/ UTV64.10%、摩托車14.76%、電動車輛13.19%、零組件及其他7.95% (2024年)</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>興富發-建材營造-上市</t>
+          <t>宏佳騰-電機機械-上櫃</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>建材營造平</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>** 建材營造 - 建設業</t>
+          <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>多頭排列股</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1639.114</t>
+          <t>18286.009</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>15.40</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>265.0</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1946,97 +1946,97 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>51</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-9.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>116</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>267.2</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>277.4</t>
+          <t>23.345</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>279.54</t>
+          <t>23.947</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-86.01</t>
+          <t>-12.34</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>7.142857142857142</t>
+          <t>45.83333333333313</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>3.174603174603184</t>
+          <t>22.22222222222214</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-530.17</t>
+          <t>32.90</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-429907645.0</t>
+          <t>-235544735.8</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-68221414.3</t>
+          <t>-351041635.9</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>-32</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-59779347.52564854</t>
+          <t>-38069176.32307376</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-40365315.56</t>
+          <t>49797592.51</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>水泥工業</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2096,1545 +2096,85 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>8.811722960289302</t>
+          <t>33.91465883488689</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>45.46314217201299</t>
+          <t>-6.193883484790765</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>32.12491672435991</t>
+          <t>5.87318368368304</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>152.65</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>9.42%</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5.18%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>177520</t>
+          <t>171034</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>網路通訊產品64.27%、電腦配件31.22%、其他4.51% (2024年)</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>技嘉-電腦及週邊設備業-上市</t>
+          <t>台泥-水泥工業-上市</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>水泥工業右下</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>77.62</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
-        <is>
-          <t>** 電腦及週邊設備 - 顯示器模組、主機板、機殼、電源供應器、散熱片、風扇馬達、散熱模組、顯示卡、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>弱勢突破股</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2349</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2.74</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2775.512</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2.92</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>11.15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>2776</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>-1.73</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>3.89</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>10.95</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>11.1425</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>10.7254</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>-37.42</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>33.33333333333331</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>-1217.25</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-794812.2</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>71140.1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>-1217</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>1249913.771410787</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>4341259.15</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>錸德</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>7.266079007508978</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>29.43204577292231</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>8.178446379053689</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>14.57%</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>162.74</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>7735</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>光學產品84.42%、其他15.58% (2024年)</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>錸德-光電業-上市</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>光電業平</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>7.63</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>** 電腦及週邊設備 - 光碟片</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>弱勢突破股</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>12344.708</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>9.62</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>125.5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>-0.63</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>-2.64</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>5.42</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>126.3</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>129.725</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>123.05</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>-68.46</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>8.333333333333332</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>12.3015873015873</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>-134.53</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-1075811790.2</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>-458702860.6</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-12506327.4667552</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>137676471.55</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>光寶科</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>1.409424233691332</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>7.352888368225501</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>20.99056536095143</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>17.81</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>21.83</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>22.12%</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>9.22%</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>28.04</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>293818</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>資訊及消費性電子43.00%、雲端及物聯網37.00%、光電通訊20.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>光寶科-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右上</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>35.46</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>** 汽車 - 銷售、進出口業務、車燈、其他** 電腦及週邊設備 - 機殼、電源供應器、伺服器、其他電腦及週邊設備、安全監控系統** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 其他 - 其他電子產品及電子服務產業** 雲端運算 - 電力設備、冷卻設備、雲端應用服務、系統整合、顧問諮詢、設備安裝服務、IaaS、PaaS、SaaS** 體驗科技 - 環境感知、深度感測、視覺、手勢/動作** LED照明產業 - 封裝/模組、燈具/應用** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 智慧電網 - 配電管理設施** 醫療器材 - 醫療耗材、生物檢測</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>多頭排列股</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>458.173</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>458</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>-0.67</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>-8.91</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>24.535</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>24.572</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>-167.40</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>5.194805194805174</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1.731601731601725</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>-34.74</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>-8842879.8</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>-6562958.7</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-1286229.354659035</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>-1053247.54</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>橋椿</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>居家生活</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>7.751419501579042</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-10.38604692305599</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>-22.74807474555465</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>8.11</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>7.59</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>17.9</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>8.32%</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>-1.03%</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>14.81</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>4440</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>橋椿-居家生活-上市</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>居家生活右下</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>35.8</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>** 其他 - 其他</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>弱勢突破股</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>-2.02</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>11.79</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>31.45</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>32.12</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>32.125</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>31.868</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>-138.05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13.88888888888888</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>52.87524366471735</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>535.19</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>1003.6</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>158.0</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>10.10257570162339</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>-62.72</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>宏佳騰</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.5502992040917953</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-62.96013378851607</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>-7.737807792515493</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>6.79</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>32.09</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>20.81%</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>-4.48%</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>35.02</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>ATV/ UTV64.10%、摩托車14.76%、電動車輛13.19%、零組件及其他7.95% (2024年)</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>宏佳騰-電機機械-上櫃</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>電機機械右下</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>多頭排列股</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>18286.009</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>15.40</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>18286</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>-4.13</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>-2.51</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>22.38</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>23.345</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>23.947</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>-12.34</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>45.83333333333313</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>22.22222222222214</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>32.90</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>-235544735.8</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>-351041635.9</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-32</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-38069176.32307376</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>49797592.51</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>33.91465883488689</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-6.193883484790765</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>5.87318368368304</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>4.57</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>21.99</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>15.12%</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>3.15%</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>30.77</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>171034</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>台泥-水泥工業-上市</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>水泥工業右下</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>28.5</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
         <is>
           <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,17 +753,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -773,12 +773,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -788,87 +788,87 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>84</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.1825</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>15.645</t>
+          <t>15.691</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-55.76</t>
+          <t>-66.64</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>26.08695652173922</t>
+          <t>34.78260869565209</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>8.695652173913066</t>
+          <t>23.18840579710139</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>62.00</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -878,27 +878,27 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-1658.0</t>
+          <t>-352.2</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-1782.4</t>
+          <t>-926.9</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-62</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-567.9486702911817</t>
+          <t>-396.5716672439427</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-133.59</t>
+          <t>134.08</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>95.44</t>
+          <t>97.91</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1015,12 +1015,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>強勢股;【b】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>32270.156</t>
+          <t>8593.384</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>77.48</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1065,132 +1065,132 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>147</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>24972</t>
+          <t>8593</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>42.84999999999999</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>42.2575</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>41.902</t>
+          <t>42.038</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>153.77</t>
+          <t>100.42</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>65.85365853658541</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.36585365853664</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>141.10</t>
+          <t>32.83</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>289049604.2</t>
+          <t>-19751447.8</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>119888680.9</t>
+          <t>-29403779.3</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>-32</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>9600451.329603653</t>
+          <t>-772024.3545959266</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>107082889.84</t>
+          <t>-39147796.76</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>93589</t>
+          <t>91519</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>458.173</t>
+          <t>349.608</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1357,22 +1357,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1382,77 +1382,77 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>350</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>24.535</t>
+          <t>24.2625</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>24.572</t>
+          <t>24.488</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-167.40</t>
+          <t>-75.72</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>5.194805194805174</t>
+          <t>9.589041095890453</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1.731601731601725</t>
+          <t>8.124295795528694</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-34.74</t>
+          <t>63.48</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1462,27 +1462,27 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-8842879.8</t>
+          <t>-2498311.6</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-6562958.7</t>
+          <t>-6841036.5</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-63</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1286229.354659035</t>
+          <t>-1005680.364309413</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1053247.54</t>
+          <t>-477757.27</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11.79</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1649,102 +1649,102 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>31.67</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>31.9375</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>31.9</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>-746.75</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>-0.02</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>32.12</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>32.125</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>31.868</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>-138.05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13.88888888888888</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>52.87524366471735</t>
+          <t>4.629629629629628</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>535.19</t>
+          <t>-39.94</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>1003.6</t>
+          <t>208.4</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>347.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>-39</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>10.10257570162339</t>
+          <t>-32.76346137254044</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-62.72</t>
+          <t>-161.91</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31.79</t>
+          <t>31.28</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>35.28</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2284</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18286.009</t>
+          <t>35223.119</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>15.40</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1946,97 +1946,97 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>55</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>281</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>35223</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>23.345</t>
+          <t>23.145</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>23.947</t>
+          <t>23.812</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-12.34</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>45.83333333333313</t>
+          <t>22.22222222222218</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>22.22222222222214</t>
+          <t>41.01851851851833</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>32.90</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-235544735.8</t>
+          <t>-176022782.8</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-351041635.9</t>
+          <t>-423719801.6</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-38069176.32307376</t>
+          <t>-24333435.15314436</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>49797592.51</t>
+          <t>-11524450.56</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.52</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>171034</t>
+          <t>168391</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,17 +753,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -808,67 +808,67 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>97</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>17.1825</t>
+          <t>17.1075</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>15.691</t>
+          <t>15.717</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-66.64</t>
+          <t>-72.67</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>34.78260869565209</t>
+          <t>21.73913043478263</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>23.18840579710139</t>
+          <t>21.73913043478252</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>62.00</t>
+          <t>64.58</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -878,27 +878,27 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-352.2</t>
+          <t>-317.6</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-926.9</t>
+          <t>-896.6</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-62</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-396.5716672439427</t>
+          <t>-326.4013757522321</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>134.08</t>
+          <t>59.54</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>97.91</t>
+          <t>99.24</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8593.384</t>
+          <t>5843.232</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,122 +1045,122 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>43.7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>-8.0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>-64.0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>價跌量縮</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>5843</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>-1.13</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>44.2</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>8593</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>43.92</t>
-        </is>
-      </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>42.5975</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>42.038</t>
+          <t>42.07299999999999</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>100.42</t>
+          <t>66.17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>65.85365853658541</t>
+          <t>50.00000000000009</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>85.36585365853664</t>
+          <t>68.69918699187</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>-121.84</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1170,27 +1170,27 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-19751447.8</t>
+          <t>-87116332.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-29403779.3</t>
+          <t>-39270653.3</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-772024.3545959266</t>
+          <t>-7946964.876669273</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-39147796.76</t>
+          <t>-47409137.75</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>15.95</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>91519</t>
+          <t>90483</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,62 +1322,62 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>-1.33</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>371.3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-2.27</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>22.05</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>349.608</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>371</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1417,42 +1417,42 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>24.2625</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>24.488</t>
+          <t>24.441</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-75.72</t>
+          <t>-57.96</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>9.589041095890453</t>
+          <t>3.225806451612947</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>8.124295795528694</t>
+          <t>7.467962881131284</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>63.48</t>
+          <t>70.75</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1462,27 +1462,27 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-2498311.6</t>
+          <t>-1740431.4</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-6841036.5</t>
+          <t>-5951054.2</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-63</t>
+          <t>-70</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1005680.364309413</t>
+          <t>-969946.9476498023</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-477757.27</t>
+          <t>-773413.16</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.76</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1599,12 +1599,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1634,12 +1634,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1654,22 +1654,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1689,47 +1689,47 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>31.67</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>31.9375</t>
+          <t>31.835</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.917</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-746.75</t>
+          <t>-276.32</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1739,12 +1739,12 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>4.629629629629628</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-39.94</t>
+          <t>-322.62</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>208.4</t>
+          <t>-500.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>347.0</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-39</t>
+          <t>-322</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-32.76346137254044</t>
+          <t>-56.94318464011589</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-161.91</t>
+          <t>-189.93</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>35.28</t>
+          <t>35.27</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35223.119</t>
+          <t>36296.148</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1946,22 +1946,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>70</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1971,72 +1971,72 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>192</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>35223</t>
+          <t>36296</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>22.47</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>23.0275</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>23.737</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>-1.69</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>-0.49</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>-3.18</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>-2.80</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>22.41</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>23.145</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>23.812</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>-4.63</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22.22222222222218</t>
+          <t>42.85714285714249</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>41.01851851851833</t>
+          <t>40.02645502645478</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>140.81</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-176022782.8</t>
+          <t>103611485.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-423719801.6</t>
+          <t>-253856558.1</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>-140</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-24333435.15314436</t>
+          <t>-9090052.420794342</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11524450.56</t>
+          <t>74748552.61</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>30.72</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>168391</t>
+          <t>169146</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -486,157 +486,157 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>highlight_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>漲跌BYN天</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>增縮BYN天</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>漲跌BYN天Diff</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>增縮BYN天Diff</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>盤後量</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>成交量</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>MA5_%</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>均價_%</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>均價long_%</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>MA_short</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>MA_long</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>MA_longlong</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_%</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MACD</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MACD-SL</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>%K</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>%D</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>VPC_MA_%</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>VPC_break</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Volume_MA_short</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Volume_MA_long</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Volume_Oscillator</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>volume_threshold</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Volume_Price_Change_sum</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>highlight_enddate</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Type0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Type1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Type2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Full_Summary</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>盤後量</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>成交量</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>MA5_%</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>均價_%</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>均價long_%</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>MA_short</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>MA_long</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>MA_longlong</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_%</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>MACD</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>MACD-SL</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>%K</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>%D</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>VPC_MA_%</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>VPC_break</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Volume_MA_short</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Volume_MA_long</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Volume_Oscillator</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>volume_threshold</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Volume_Price_Change_sum</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>highlight_date</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>highlight_enddate</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Type0</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Type1</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Type2</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>Full_Summary</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
@@ -783,152 +783,152 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>-2.0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>-4.95</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>8.85</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>16.26</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>17.1075</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>15.717</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>-72.67</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>21.73913043478263</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>21.73913043478252</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>64.58</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>-317.6</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>-896.6</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>-326.4013757522321</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>59.54</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>李洲</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>-4.95</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>16.26</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>17.1075</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>15.717</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>-72.67</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>21.73913043478263</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>21.73913043478252</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>64.58</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-317.6</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>-896.6</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-64</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-326.4013757522321</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>59.54</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>李洲</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1070,157 +1070,157 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>-8.0</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>-64.0</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>5843</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>-1.13</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>44.2</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>42.5975</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>42.07299999999999</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>66.17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>50.00000000000009</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>68.69918699187</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>-121.84</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>-87116332.0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>-39270653.3</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>-7946964.876669273</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>-47409137.75</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>興富發</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>價跌量縮</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>5843</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>-1.13</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>3.76</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>44.2</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>42.5975</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>42.07299999999999</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>66.17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>50.00000000000009</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>68.69918699187</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>-121.84</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-87116332.0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>-39270653.3</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-7946964.876669273</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>-47409137.75</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>興富發</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1367,152 +1367,152 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-0.63</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-8.08</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>22.19</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>24.14</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>24.441</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>-57.96</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>-0.77</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>3.225806451612947</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>7.467962881131284</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>70.75</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-1740431.4</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>-5951054.2</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-70</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-969946.9476498023</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>-773413.16</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>橋椿</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>居家生活</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-0.63</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>-8.08</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>22.19</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>24.14</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>24.441</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>-57.96</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>-0.77</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>3.225806451612947</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>7.467962881131284</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>70.75</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-1740431.4</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>-5951054.2</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-70</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-969946.9476498023</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>-773413.16</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>橋椿</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>居家生活</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1654,157 +1654,157 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>-3.0</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-2.02</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>-2.06</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>31.18</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>31.835</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>31.917</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>-276.32</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>-322.62</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>-500.0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>224.6</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>-322</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>-56.94318464011589</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>-189.93</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>宏佳騰</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-2.02</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>-2.06</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>31.18</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>31.835</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>31.917</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>-276.32</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>-322.62</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-500.0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>224.6</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-322</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-56.94318464011589</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>-189.93</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>宏佳騰</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1946,157 +1946,157 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15.0</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>36296</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>22.47</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>23.0275</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>23.737</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>-1.69</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>42.85714285714249</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>40.02645502645478</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>140.81</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>103611485.0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>-253856558.1</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>-140</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>-9090052.420794342</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>74748552.61</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>水泥工業</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>價-量增</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>36296</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>-2.42</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>-2.99</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>22.47</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>23.0275</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>23.737</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>-1.69</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>-0.50</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>42.85714285714249</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>40.02645502645478</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>140.81</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>103611485.0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>-253856558.1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>-140</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-9090052.420794342</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>74748552.61</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,17 +753,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -803,72 +803,72 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>99</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.27</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>17.1075</t>
+          <t>16.9975</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>15.717</t>
+          <t>15.738</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-72.67</t>
+          <t>-86.24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21.73913043478263</t>
+          <t>4.761904761904826</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>21.73913043478252</t>
+          <t>20.42788129744651</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>64.58</t>
+          <t>61.42</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -878,27 +878,27 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-317.6</t>
+          <t>-333.4</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-896.6</t>
+          <t>-864.2</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>-61</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-326.4013757522321</t>
+          <t>-275.3876218512067</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>59.54</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>99.24</t>
+          <t>100.53</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5843.232</t>
+          <t>3735.505</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1075,92 +1075,92 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>43</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-64.0</t>
+          <t>-51.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>65</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>42.5975</t>
+          <t>42.685</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>42.07299999999999</t>
+          <t>42.102</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>66.17</t>
+          <t>42.19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>50.00000000000009</t>
+          <t>44.73684210526318</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>68.69918699187</t>
+          <t>53.53016688061624</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-121.84</t>
+          <t>-168.49</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1170,27 +1170,27 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-87116332.0</t>
+          <t>-96915099.6</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-39270653.3</t>
+          <t>-36095839.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7946964.876669273</t>
+          <t>-13640221.35236016</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-47409137.75</t>
+          <t>-44953131.97</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>90483</t>
+          <t>90069</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>371.3</t>
+          <t>426.944</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1372,87 +1372,87 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>427</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-8.08</t>
+          <t>-7.42</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.0125</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>24.441</t>
+          <t>24.392</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-57.96</t>
+          <t>-42.68</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>3.225806451612947</t>
+          <t>17.39130434782605</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>7.467962881131284</t>
+          <t>10.06871729844315</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>70.75</t>
+          <t>125.58</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1462,27 +1462,27 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-1740431.4</t>
+          <t>2018517.2</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-5951054.2</t>
+          <t>-7890261.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-70</t>
+          <t>-125</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-969946.9476498023</t>
+          <t>-764067.1361078493</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-773413.16</t>
+          <t>368271.83</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>14.76</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,122 +1629,122 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30.45</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-1.30</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>-2.84</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>30.85</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>31.7525</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>31.936</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>-170.95</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30.55</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-2.02</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>-2.06</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>31.18</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>31.835</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>31.917</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>-276.32</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-322.62</t>
+          <t>-393.10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-500.0</t>
+          <t>-492.4</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-322</t>
+          <t>-393</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-56.94318464011589</t>
+          <t>-77.63581323393944</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-189.93</t>
+          <t>-191.45</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>35.27</t>
+          <t>35.21</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1891,12 +1891,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36296.148</t>
+          <t>45743.034</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1951,92 +1951,92 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>280</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>36296</t>
+          <t>45743</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>23.0275</t>
+          <t>22.9375</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>23.737</t>
+          <t>23.691</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>42.85714285714249</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>40.02645502645478</t>
+          <t>55.02645502645487</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>140.81</t>
+          <t>332.41</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>103611485.0</t>
+          <t>237755088.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-253856558.1</t>
+          <t>-102299872.4</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-140</t>
+          <t>-332</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-9090052.420794342</t>
+          <t>15447634.64920013</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>74748552.61</t>
+          <t>150404913.53</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>31.09</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>169146</t>
+          <t>173300</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,219 +753,219 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>-5.0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-3.73</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>-4.41</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>6.96</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>16.1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>16.8425</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>15.747</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>-132.39</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>8.833678398895811</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>26.72</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>-958.8</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>-1308.4</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-26</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>-242.6987135670361</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>-62.91</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>李洲</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>200.283758971791</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>125.7025761124122</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>20.94933089328606</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>-4.28</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>16.27</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>16.9975</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>15.738</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>-86.24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>4.761904761904826</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>20.42788129744651</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>61.42</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-333.4</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>-864.2</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-61</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-275.3876218512067</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>5.19</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>李洲</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>200.283758971791</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>125.7025761124122</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>20.94933089328606</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX2" t="inlineStr">
         <is>
           <t>15.96%</t>
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>100.53</t>
+          <t>96.95</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1015,12 +1015,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>強勢股;【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3735.505</t>
+          <t>4744.148</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1070,97 +1070,97 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>34</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-51.0</t>
+          <t>-9.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>103</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>44.17</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>42.685</t>
+          <t>42.7825</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>42.102</t>
+          <t>42.13799999999999</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>36.68</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>44.73684210526318</t>
+          <t>59.70149253731341</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>53.53016688061624</t>
+          <t>51.47944488085891</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-168.49</t>
+          <t>-1114.83</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1170,32 +1170,32 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-96915099.6</t>
+          <t>-346014804.6</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-36095839.0</t>
+          <t>-28482600.2</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-13640221.35236016</t>
+          <t>-13740652.5825901</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-44953131.97</t>
+          <t>-14293024.35</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>16.15</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>16.59</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>90069</t>
+          <t>91622</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>426.944</t>
+          <t>747.801</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1367,129 +1367,129 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-2.12</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-7.22</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-1.96</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>22.12</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>23.8425</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>24.319</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>-36.59</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-0.60</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>6.872370266479663</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>45.92</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-3276942.6</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>-6059911.2</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-45</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-765666.0774658791</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>-774460.25</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>-7.42</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>-1.56</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>22.23</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>24.0125</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>24.392</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>-42.68</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17.39130434782605</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>10.06871729844315</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>125.58</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>2018517.2</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>-7890261.0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-125</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-764067.1361078493</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>368271.83</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AL4" t="inlineStr">
         <is>
           <t>橋椿</t>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>14.54</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>22.56</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>36</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1674,77 +1674,77 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-2.10</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>-3.50</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>30.54</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>31.6475</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>31.949</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>-132.38</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-1.30</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>-2.84</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>-0.57</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>31.7525</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>31.936</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>-170.95</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-393.10</t>
+          <t>-411.26</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-492.4</t>
+          <t>-611.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>196.3</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-393</t>
+          <t>-411</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-77.63581323393944</t>
+          <t>-105.9716364685952</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-191.45</t>
+          <t>-261.82</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>35.21</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>45743.034</t>
+          <t>32677.659</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>27.52</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1951,67 +1951,67 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>392</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>45743</t>
+          <t>32678</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>22.9375</t>
+          <t>22.8625</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>23.691</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2021,22 +2021,22 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>23.52941176470586</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>55.02645502645487</t>
+          <t>55.46218487394943</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>332.41</t>
+          <t>107.11</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>237755088.0</t>
+          <t>8089596.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-102299872.4</t>
+          <t>-113727569.9</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-332</t>
+          <t>-107</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>15447634.64920013</t>
+          <t>23315581.063899</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>150404913.53</t>
+          <t>66589286.34</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2091,12 +2091,12 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>30.66</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>173300</t>
+          <t>168391</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,17 +753,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -783,92 +783,92 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>109</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>16.02</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>16.8425</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>15.747</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-132.39</t>
+          <t>-186.79</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.31578947368423</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>8.833678398895811</t>
+          <t>10.35923141186301</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.89</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -878,27 +878,27 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-958.8</t>
+          <t>-417.8</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-1308.4</t>
+          <t>-786.7</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-26</t>
+          <t>-46</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-242.6987135670361</t>
+          <t>-179.2305106921023</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-62.91</t>
+          <t>169.84</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>96.95</t>
+          <t>96.18</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1020,67 +1020,67 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6461.443</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15.51</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4744.148</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>11.39</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>44.25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1090,77 +1090,77 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>44.17</t>
+          <t>44.14</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>42.7825</t>
+          <t>42.9175</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>42.13799999999999</t>
+          <t>42.20399999999999</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>59.70149253731341</t>
+          <t>83.33333333333323</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>51.47944488085891</t>
+          <t>62.59055599196996</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-1114.83</t>
+          <t>-592.67</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1170,32 +1170,32 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-346014804.6</t>
+          <t>-60294058.6</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-28482600.2</t>
+          <t>12238143.4</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>-592</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-13740652.5825901</t>
+          <t>-9523406.274694644</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-14293024.35</t>
+          <t>13671448.42</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>16.59</t>
+          <t>16.76</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>91622</t>
+          <t>93279</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>747.801</t>
+          <t>254.763</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1377,67 +1377,67 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>255</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>23.8425</t>
+          <t>23.6375</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>24.319</t>
+          <t>24.244</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-36.59</t>
+          <t>-30.42</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>6.872370266479663</t>
+          <t>5.797101449275348</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>-22.10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1462,27 +1462,27 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-3276942.6</t>
+          <t>-5675391.6</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-6059911.2</t>
+          <t>-4648327.5</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-765666.0774658791</t>
+          <t>-762831.154959932</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-774460.25</t>
+          <t>-747239.08</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.42</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22.56</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1659,92 +1659,92 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>31.6475</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>31.949</t>
+          <t>31.954</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-132.38</t>
+          <t>-94.39</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.2903225806452</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.763440860215068</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-411.26</t>
+          <t>-380.79</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-611.0</t>
+          <t>-508.2</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>196.3</t>
+          <t>-105.7</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-411</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-105.9716364685952</t>
+          <t>-119.4659344402243</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-261.82</t>
+          <t>-193.68</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.77</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2255</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>32677.659</t>
+          <t>27808.628</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27.52</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1956,87 +1956,87 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>89</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>153</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>32678</t>
+          <t>27809</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>22.8625</t>
+          <t>22.795</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.577</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23.52941176470586</t>
+          <t>29.41176470588243</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>55.46218487394943</t>
+          <t>50.98039215686274</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>107.11</t>
+          <t>350.96</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>8089596.0</t>
+          <t>189879694.4</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-113727569.9</t>
+          <t>42105430.9</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-107</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>23315581.063899</t>
+          <t>36358320.00461075</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>66589286.34</t>
+          <t>108093384.18</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>30.66</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>168391</t>
+          <t>168769</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,17 +753,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -783,189 +783,189 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>-3.75</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>15.64</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>16.25</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>15.876</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>-120.94</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>24.99999999999989</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>20.61403508771931</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>55.49</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>-119.6</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>-268.7</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-55</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>36.0869674472825</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>201.68</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-1.69</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>-4.19</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>6.02</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>16.02</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>16.72</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>15.77</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>-186.79</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>26.31578947368423</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>10.35923141186301</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>46.89</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-417.8</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>-786.7</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-46</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-179.2305106921023</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>169.84</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>李洲</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>200.283758971791</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>125.7025761124122</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>20.94933089328606</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>李洲</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>200.283758971791</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>125.7025761124122</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>20.94933089328606</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX2" t="inlineStr">
         <is>
           <t>15.96%</t>
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>96.18</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6461.443</t>
+          <t>12877.84</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1075,92 +1075,92 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>82</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>430</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>44.14</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>42.9175</t>
+          <t>43.8475</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>42.20399999999999</t>
+          <t>42.691</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>83.33333333333323</t>
+          <t>33.84615384615389</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>62.59055599196996</t>
+          <t>72.30769230769236</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-592.67</t>
+          <t>422.08</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1170,32 +1170,32 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-60294058.6</t>
+          <t>97734692.4</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>12238143.4</t>
+          <t>18720316.9</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-592</t>
+          <t>422</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-9523406.274694644</t>
+          <t>14870653.74983079</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>13671448.42</t>
+          <t>-26327394.27</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>93279</t>
+          <t>92347</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1307,12 +1307,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>254.763</t>
+          <t>288.205</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1387,72 +1387,72 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>288</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>23.6375</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>24.244</t>
+          <t>24.011</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-30.42</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.99999999999986</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>5.797101449275348</t>
+          <t>81.66666666666653</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-22.10</t>
+          <t>1486.00</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1462,27 +1462,27 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-5675391.6</t>
+          <t>6494349.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-4648327.5</t>
+          <t>409478.7</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-762831.154959932</t>
+          <t>459973.8872785709</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-747239.08</t>
+          <t>1169336.39</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1674,77 +1674,77 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>31.075</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>31.954</t>
+          <t>31.977</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-94.39</t>
+          <t>-15.95</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11.2903225806452</t>
+          <t>78.57142857142836</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3.763440860215068</t>
+          <t>59.96825396825406</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-380.79</t>
+          <t>43.84</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-508.2</t>
+          <t>-198.4</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-105.7</t>
+          <t>-353.3</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>-43</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-119.4659344402243</t>
+          <t>-123.4977374745873</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-193.68</t>
+          <t>-87.27</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>34.83</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27808.628</t>
+          <t>189463.031</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1951,129 +1951,129 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3,753</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>189463</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>-3.57</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>22.47</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>22.57</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>23.405</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>26.75</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>-0.40</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>33.33333333333331</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>47.10</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>527976497.2</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>358928095.8</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>65831284.96745466</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>316755827.5</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>-7.0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>27809</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>-1.47</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>-3.32</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>22.795</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>23.577</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>7.04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>29.41176470588243</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>50.98039215686274</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>350.96</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>189879694.4</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>42105430.9</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>36358320.00461075</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>108093384.18</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AL6" t="inlineStr">
         <is>
           <t>台泥</t>
@@ -2091,12 +2091,12 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>168769</t>
+          <t>176320</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,32 +738,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>-1.28</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>-0.64</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>49.0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -803,72 +803,72 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>15.64</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>16.165</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>15.876</t>
+          <t>15.896</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-120.94</t>
+          <t>-87.39</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>24.99999999999989</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>20.61403508771931</t>
+          <t>18.859649122807</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>55.49</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -878,27 +878,27 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-119.6</t>
+          <t>-76.4</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-268.7</t>
+          <t>-467.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-55</t>
+          <t>-83</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>36.0869674472825</t>
+          <t>53.82277738671571</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>201.68</t>
+          <t>151.37</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -933,22 +933,22 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>200.283758971791</t>
+          <t>-71.1988141560126</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>125.7025761124122</t>
+          <t>-14.64030752333882</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>20.94933089328606</t>
+          <t>16.61009005389843</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>96.89</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12877.84</t>
+          <t>7560.802</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1065,102 +1065,102 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>-7.0</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>45.84</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>43.8475</t>
+          <t>43.995</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>42.691</t>
+          <t>42.75900000000001</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>33.84615384615389</t>
+          <t>46.15384615384615</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>72.30769230769236</t>
+          <t>54.35897435897442</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>422.08</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1170,32 +1170,32 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>97734692.4</t>
+          <t>126916064.6</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>18720316.9</t>
+          <t>90937536.8</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>14870653.74983079</t>
+          <t>13153967.80095718</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-26327394.27</t>
+          <t>3712195.08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1215,72 +1215,72 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-63.40863348097227</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-44.53237722684639</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-58.46140979330202</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>20.37%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7.22%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>92347</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>建設業務99.44%、百貨0.38%、營造0.18% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>** 建材營造 - 建設業</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>288.205</t>
+          <t>419.765</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,122 +1337,122 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>22.15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-1.48</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-5.75</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>22.25</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>-2.55</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>-5.17</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>22.19</t>
-        </is>
-      </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>22.585</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>24.011</t>
+          <t>23.962</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>10.13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>64.99999999999986</t>
+          <t>54.99999999999972</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>81.66666666666653</t>
+          <t>73.33333333333319</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1486.00</t>
+          <t>969.32</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1462,27 +1462,27 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>6494349.0</t>
+          <t>2731669.8</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>409478.7</t>
+          <t>255459.5</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>969</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>459973.8872785709</t>
+          <t>417144.2989833557</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1169336.39</t>
+          <t>181581.56</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1517,62 +1517,62 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>7.751419501579042</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-10.38604692305599</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-22.74807474555465</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>8.32%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>** 其他 - 其他</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1659,67 +1659,67 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-9.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>31.075</t>
+          <t>31.0225</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>31.977</t>
+          <t>31.951</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-15.95</t>
+          <t>-12.72</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1729,22 +1729,22 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>78.57142857142836</t>
+          <t>35.71428571428557</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>59.96825396825406</t>
+          <t>69.20634920634922</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>43.84</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-198.4</t>
+          <t>-354.6</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-353.3</t>
+          <t>-367.4</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-43</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-123.4977374745873</t>
+          <t>-121.5773106188375</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-87.27</t>
+          <t>-111.01</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1809,27 +1809,27 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.5502992040917953</t>
+          <t>24.95650476538034</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-62.96013378851607</t>
+          <t>-56.09617185216992</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-7.737807792515493</t>
+          <t>-18.19449110167005</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>34.83</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>189463.031</t>
+          <t>144904.986</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>76.48</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1946,82 +1946,82 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>187</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3,753</t>
+          <t>798</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>189463</t>
+          <t>144905</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>7.33</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22.635</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>23.405</t>
+          <t>23.429</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>67.71</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>33.33333333333331</t>
+          <t>66.66666666666664</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>47.10</t>
+          <t>66.72</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>527976497.2</t>
+          <t>1307640966.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>358928095.8</t>
+          <t>784354898.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>65831284.96745466</t>
+          <t>130386358.6486848</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>316755827.5</t>
+          <t>485439263.9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -2101,27 +2101,27 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>33.91465883488689</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-6.193883484790765</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>5.87318368368304</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>23.88</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>176320</t>
+          <t>185759</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,17 +753,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -783,189 +783,189 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-1.48</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>-3.12</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>15.58</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>16.0825</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>15.917</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>-70.44</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>8.333333333333288</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>9.21</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>-376.6</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>-414.8</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>57.60284512108156</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>78.39</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>-3.31</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>15.63</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>16.165</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>15.896</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>-87.39</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>18.859649122807</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>83.64</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-76.4</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>-467.0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-83</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>53.82277738671571</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>151.37</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>李洲</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-71.1988141560126</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-14.64030752333882</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>16.61009005389843</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>李洲</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-71.1988141560126</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-14.64030752333882</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>16.61009005389843</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX2" t="inlineStr">
         <is>
           <t>15.96%</t>
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>96.89</t>
+          <t>95.82</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1015,12 +1015,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>強勢股;【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7560.802</t>
+          <t>7991.596</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>24.76</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1080,67 +1080,67 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>88</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>45.47000000000001</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>43.995</t>
+          <t>44.145</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>42.75900000000001</t>
+          <t>42.825</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1150,17 +1150,17 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>46.15384615384615</t>
+          <t>21.99999999999989</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>54.35897435897442</t>
+          <t>33.99999999999999</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>39.56</t>
+          <t>-213.05</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1170,27 +1170,27 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>126916064.6</t>
+          <t>-91250930.2</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>90937536.8</t>
+          <t>80720517.2</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-213</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>13153967.80095718</t>
+          <t>6862222.974028464</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3712195.08</t>
+          <t>-27742373.57</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1225,62 +1225,62 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>135.7791560902942</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.442111486802782</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-47.58774907778343</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.37%</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.22%</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92761</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建設業務99.44%、百貨0.38%、營造0.18% (2024年)</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 建材營造 - 建設業</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>419.765</t>
+          <t>438.867</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1357,139 +1357,139 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-0.54</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-0.67</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-6.25</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>22.27</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>22.42</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>23.915</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>12.10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>54.99999999999972</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>58.33333333333309</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>-445.40</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-397082.8</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>114963.4</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-445</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>270197.0558460394</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>-538012.78</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>-1.48</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>-5.75</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>22.25</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>22.585</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>23.962</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>10.13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>54.99999999999972</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>73.33333333333319</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>969.32</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>2731669.8</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>255459.5</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>417144.2989833557</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>181581.56</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AL4" t="inlineStr">
         <is>
           <t>橋椿</t>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1517,62 +1517,62 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.312824007547442</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.60101708031618</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.72990160044902</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1659,129 +1659,129 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>-2.41</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>-3.02</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>30.19</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>30.935</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>31.897</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>-14.82</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>38.09523809523798</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>-15.53</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>-450.0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>-389.5</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>-122.9826925582316</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>-130.71</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-9.0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>-2.52</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>-2.91</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>30.24</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>31.0225</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>31.951</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>-12.72</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>35.71428571428557</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>69.20634920634922</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-354.6</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>-367.4</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-121.5773106188375</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>-111.01</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AL5" t="inlineStr">
         <is>
           <t>宏佳騰</t>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1896,147 +1896,147 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-3.53</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>66096.545</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>34.89</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>23.75</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>2025-09-22</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>5.33</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>144904.986</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>76.48</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>6.09</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>211</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>456</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>144905</t>
+          <t>66097</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>23.22</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>22.635</t>
+          <t>22.6675</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>23.429</t>
+          <t>23.437</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>67.71</t>
+          <t>88.05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>64.5833333333333</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>66.66666666666664</t>
+          <t>88.19444444444441</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>66.72</t>
+          <t>92.84</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>1307640966.0</t>
+          <t>1053655319.6</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>784354898.0</t>
+          <t>546374235.6</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>130386358.6486848</t>
+          <t>143116268.3794239</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>485439263.9</t>
+          <t>213130771.9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2091,12 +2091,12 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>185759</t>
+          <t>179341</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF11"/>
+  <dimension ref="A1:BF8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3358.0</t>
+          <t>3564.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,17 +753,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>240.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -783,92 +783,92 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1,164</t>
+          <t>53</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>237.8</t>
+          <t>238.5</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>243.375</t>
+          <t>242.5</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>240.07</t>
+          <t>240.56</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-205.69</t>
+          <t>-104.70</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>78.57142857142857</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>33.33333333333331</t>
+          <t>26.19047619047616</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-43.34</t>
+          <t>26.80</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -878,27 +878,27 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-452611.8</t>
+          <t>-122410.6</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-315763.4</t>
+          <t>-167236.6</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-136848</t>
+          <t>44826</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-40486.71929666829</t>
+          <t>-31763.12804725144</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-93396.16</t>
+          <t>16216.62</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>90.11</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>264037</t>
+          <t>276692</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3429.468</t>
+          <t>2051.123</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>378.0</t>
+          <t>395.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1075,92 +1075,92 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>79</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-25.0</t>
+          <t>-62.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>53</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>394.4</t>
+          <t>398.5</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>377.925</t>
+          <t>378.625</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>365.22</t>
+          <t>366.08</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>35.58</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>31.20567375886525</t>
+          <t>54.34782608695652</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>66.90307328605202</t>
+          <t>51.68568198170419</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>100.22</t>
+          <t>70.14</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1170,32 +1170,32 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>659757655.2</t>
+          <t>733761847.8</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>329512941.1</t>
+          <t>431259644.3</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>330244714</t>
+          <t>302502203</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>73128812.8069333</t>
+          <t>64231556.47992393</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-39323674.67</t>
+          <t>15296646.68</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>55.63</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>30364</t>
+          <t>31730</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1307,27 +1307,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>強勢股;【b】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3429.468</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>378.0</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1362,97 +1362,97 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>35</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>394.4</t>
+          <t>15.22</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>377.925</t>
+          <t>15.735</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>365.22</t>
+          <t>15.974</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>-38.14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>31.20567375886525</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>66.90307328605202</t>
+          <t>12.12121212121205</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>100.22</t>
+          <t>-67.59</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1462,164 +1462,164 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>659757655.2</t>
+          <t>-395.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>329512941.1</t>
+          <t>-235.7</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>330244714</t>
+          <t>-159</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>73128812.8069333</t>
+          <t>78.60023459172174</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-39323674.67</t>
+          <t>66.92</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>李洲</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.9020166977669146</t>
+          <t>-71.1988141560126</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2.801034214035957</t>
+          <t>-14.64030752333882</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>20.6824397798794</t>
+          <t>16.61009005389843</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>33.05%</t>
+          <t>15.96%</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>16.15%</t>
+          <t>-47.47%</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>30364</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>商品銷售97.03%、勞務2.86%、其他0.11% (2024年)</t>
+          <t>LED 光電產品93.51%、磊晶片6.32%、其他0.17% (2024年)</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>辛耘-半導體業-上市</t>
+          <t>李洲-光電業-上櫃</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>半導體業右上</t>
+          <t>光電業右下</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>62.83</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>** 半導體 - 生產製程及檢測設備、生產製程及檢測設備** 平面顯示器 - 生產製程及檢測設備** LED照明產業 - 生產製程、檢測設備及原物料** 太陽能產業 - 太陽能發電設備/系統及系統工程</t>
+          <t>** LED照明產業 - 封裝/模組、燈具/應用</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>強勢股;【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3429.468</t>
+          <t>19845.734</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>61.50</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>378.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1654,17 +1654,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>130</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1674,77 +1674,77 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-25.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>330</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>19846</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>394.4</t>
+          <t>42.46</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>377.925</t>
+          <t>44.1475</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>365.22</t>
+          <t>42.837</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>-133.81</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>31.20567375886525</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>66.90307328605202</t>
+          <t>0.6006006006005856</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>100.22</t>
+          <t>-174.53</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1754,42 +1754,42 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>659757655.2</t>
+          <t>-467514793.6</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>329512941.1</t>
+          <t>-170299364.5</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>330244714</t>
+          <t>-297215429</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>73128812.8069333</t>
+          <t>-37011427.89599285</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-39323674.67</t>
+          <t>-97541743.7</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -1799,119 +1799,119 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.9020166977669146</t>
+          <t>135.7791560902942</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.801034214035957</t>
+          <t>8.442111486802782</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>20.6824397798794</t>
+          <t>-47.58774907778343</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>33.05%</t>
+          <t>20.37%</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>16.15%</t>
+          <t>7.22%</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>30364</t>
+          <t>87467</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>商品銷售97.03%、勞務2.86%、其他0.11% (2024年)</t>
+          <t>建設業務99.44%、百貨0.38%、營造0.18% (2024年)</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>辛耘-半導體業-上市</t>
+          <t>興富發-建材營造-上市</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>半導體業右上</t>
+          <t>建材營造右下</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>62.83</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>** 半導體 - 生產製程及檢測設備、生產製程及檢測設備** 平面顯示器 - 生產製程及檢測設備** LED照明產業 - 生產製程、檢測設備及原物料** 太陽能產業 - 太陽能發電設備/系統及系統工程</t>
+          <t>** 建材營造 - 建設業</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>強勢股;【b】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3429.468</t>
+          <t>506.95</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>378.0</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1946,97 +1946,97 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>507</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>394.4</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>377.925</t>
+          <t>22.1125</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>365.22</t>
+          <t>23.742</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>31.20567375886525</t>
+          <t>35.71428571428557</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>66.90307328605202</t>
+          <t>34.12698412698408</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>100.22</t>
+          <t>-272.14</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,42 +2046,42 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>659757655.2</t>
+          <t>-1263589.2</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>329512941.1</t>
+          <t>734040.3</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>330244714</t>
+          <t>-1997629</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>73128812.8069333</t>
+          <t>100688.5512850276</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-39323674.67</t>
+          <t>563670.96</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>橋椿</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2091,92 +2091,92 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.9020166977669146</t>
+          <t>-4.312824007547442</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.801034214035957</t>
+          <t>-22.60101708031618</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>20.6824397798794</t>
+          <t>-22.72990160044902</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>33.05%</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>16.15%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>14.54</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>30364</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>商品銷售97.03%、勞務2.86%、其他0.11% (2024年)</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>辛耘-半導體業-上市</t>
+          <t>橋椿-居家生活-上市</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>半導體業右上</t>
+          <t>居家生活右下</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>62.83</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>** 半導體 - 生產製程及檢測設備、生產製程及檢測設備** 平面顯示器 - 生產製程及檢測設備** LED照明產業 - 生產製程、檢測設備及原物料** 太陽能產業 - 太陽能發電設備/系統及系統工程</t>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
@@ -2188,22 +2188,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2213,17 +2213,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>28.72</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2243,137 +2243,137 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>-1.83</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>-3.21</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>-3.84</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>29.44</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>30.4175</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>31.631</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>-20.82</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>-0.64</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>-0.53</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>-40.11</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>-829.6</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>-592.1</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>-237</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-134.6042436352146</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>-213.47</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>-1.50</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>-3.04</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>-0.96</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>15.33</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>15.81</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>15.963</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>-39.51</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>12.12121212121205</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>-54.95</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-411.4</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>-265.5</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>-145</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>80.72337889221228</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>92.88</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>李洲</t>
+          <t>宏佳騰</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -2383,119 +2383,119 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-71.1988141560126</t>
+          <t>24.95650476538034</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-14.64030752333882</t>
+          <t>-56.09617185216992</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>16.61009005389843</t>
+          <t>-18.19449110167005</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>15.96%</t>
+          <t>20.81%</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-47.47%</t>
+          <t>-4.48%</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>90.11</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>LED 光電產品93.51%、磊晶片6.32%、其他0.17% (2024年)</t>
+          <t>ATV/ UTV64.10%、摩托車14.76%、電動車輛13.19%、零組件及其他7.95% (2024年)</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>李洲-光電業-上櫃</t>
+          <t>宏佳騰-電機機械-上櫃</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>光電業右下</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>** LED照明產業 - 封裝/模組、燈具/應用</t>
+          <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4364.562</t>
+          <t>39101.788</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13.53</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2530,97 +2530,97 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>61</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>174</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>39102</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>43.41</t>
+          <t>23.79</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>44.2475</t>
+          <t>22.8975</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>42.872</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-77.37</t>
+          <t>388.32</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>1.8018018018017</t>
+          <t>74.99999999999997</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2.926181995949403</t>
+          <t>71.52777777777773</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-237.38</t>
+          <t>-132.36</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2630,42 +2630,42 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-240015796.0</t>
+          <t>-182108664.2</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-71140551.8</t>
+          <t>562766150.9</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-168875244</t>
+          <t>-744874815</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-26005915.93116681</t>
+          <t>106355887.3432737</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-58234550.63</t>
+          <t>65291866.56</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>水泥工業</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -2675,966 +2675,90 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>135.7791560902942</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>8.442111486802782</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-47.58774907778343</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>20.37%</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.22%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>89748</t>
+          <t>181228</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>建設業務99.44%、百貨0.38%、營造0.18% (2024年)</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>興富發-建材營造-上市</t>
+          <t>台泥-水泥工業-上市</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>建材營造平</t>
+          <t>水泥工業右下</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
-        <is>
-          <t>** 建材營造 - 建設業</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>-2.01</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>404.878</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>4.29</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-2.51</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>-1.08</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>-7.00</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>22.14</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>22.1225</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>23.787</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>15.53</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>-0.50</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>-0.59</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>40.55555555555546</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>-1045.65</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>-5360605.6</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>566871.7</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-5927477</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>16509.93085205917</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>-533003.02</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>橋椿</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>居家生活</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-4.312824007547442</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-22.60101708031618</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>-22.72990160044902</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>7.59</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>8.32%</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>-1.03%</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>4380</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>橋椿-居家生活-上市</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>居家生活右下</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>35.8</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>** 其他 - 其他</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>13.33</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-1.02</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>29.25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>-1.48</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>-2.89</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>-3.58</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>29.69</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>30.5725</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>31.707</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>-17.74</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>-0.59</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>-0.50</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>7.84313725490192</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>-52.48</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>-636.6</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>-417.5</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-219</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-120.2641390689735</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>-150.62</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>宏佳騰</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>24.95650476538034</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-56.09617185216992</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>-18.19449110167005</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>6.79</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>29.85</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>20.81%</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>-4.48%</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>33.9</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>2180</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>ATV/ UTV64.10%、摩托車14.76%、電動車輛13.19%、零組件及其他7.95% (2024年)</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>宏佳騰-電機機械-上櫃</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>電機機械右下</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>-0.63</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>26848.861</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>14.17</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>-21.0</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>26849</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>4.80</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>-2.75</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>23.91</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>22.815</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>23.459</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>203.52</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>66.66666666666666</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>63.88888888888884</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>-23.97</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>323779604.0</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>425878050.6</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-102098446</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>113822072.9396568</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>20204629.16</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-9.760342271298851</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-6.072228435914363</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>4.189538872550337</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>4.57</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>23.11</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>15.12%</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>3.15%</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>31.06</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>179718</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>台泥-水泥工業-上市</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>水泥工業右下</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>28.5</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
         <is>
           <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,222 +738,222 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3749.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>14.56</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-2.12</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>235.5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3749</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>-2.06</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>236.9</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>241.875</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>241.11</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>-78.09</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>-2.50</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>-1.40</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>42.85714285714285</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>40.47619047619045</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>-60.91</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>-554845.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>-344809.9</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-210035</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>-32754.06159599144</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>-38204.2</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>元太</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-14.37152843188938</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>8.331352654369573</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>33.64857459462222</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
           <t>4.67</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>3564.0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>13.84</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>240.5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>3564</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>-1.65</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>238.5</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>242.5</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>240.56</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>-104.70</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>-2.31</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-1.13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>78.57142857142857</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>26.19047619047616</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>26.80</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-122410.6</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>-167236.6</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>44826</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-31763.12804725144</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>16216.62</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>元太</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-14.37152843188938</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>8.331352654369573</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>33.64857459462222</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>4.77</t>
-        </is>
-      </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>276692</t>
+          <t>270940</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2051.123</t>
+          <t>2111.655</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.94</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>395.0</t>
+          <t>385.5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1075,92 +1075,92 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>46</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-62.0</t>
+          <t>-33.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>398.5</t>
+          <t>398.0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>378.625</t>
+          <t>379.225</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>366.08</t>
+          <t>367.03</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>35.58</t>
+          <t>19.78</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>54.34782608695652</t>
+          <t>32.23140495867769</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>51.68568198170419</t>
+          <t>39.26163493483316</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>70.14</t>
+          <t>-68.30</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1170,32 +1170,32 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>733761847.8</t>
+          <t>117549612.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>431259644.3</t>
+          <t>370783972.3</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>302502203</t>
+          <t>-253234360</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>64231556.47992393</t>
+          <t>43911971.38493001</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>15296646.68</t>
+          <t>-67845746.64</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>55.63</t>
+          <t>55.09</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>31730</t>
+          <t>30966</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1387,169 +1387,169 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-2.01</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>15.14</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>15.67</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>15.991</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>-33.64</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>15.66</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-274.6</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>-325.6</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>74.52359131762572</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-1.77</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>-3.27</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>-1.50</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>15.22</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>15.735</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>15.974</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>-38.14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>12.12121212121205</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>-67.59</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-395.0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>-235.7</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-159</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>78.60023459172174</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>66.92</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>李洲</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-71.1988141560126</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-14.64030752333882</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>16.61009005389843</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>李洲</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-71.1988141560126</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-14.64030752333882</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>16.61009005389843</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX4" t="inlineStr">
         <is>
           <t>15.96%</t>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19845.734</t>
+          <t>7975.868</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>61.50</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1664,72 +1664,72 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>-31.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>19846</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.46</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>44.1475</t>
+          <t>44.0325</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>42.837</t>
+          <t>42.795</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-133.81</t>
+          <t>-240.74</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-174.53</t>
+          <t>-66.88</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-467514793.6</t>
+          <t>-459739351.4</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-170299364.5</t>
+          <t>-275495140.8</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-297215429</t>
+          <t>-184244210</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-37011427.89599285</t>
+          <t>-44668100.01405367</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-97541743.7</t>
+          <t>-86779796.66</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>15.97</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>87467</t>
+          <t>86923</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>506.95</t>
+          <t>280.115</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,122 +1921,122 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>-6.71</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>22.15</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>-6.86</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>22.14</t>
-        </is>
-      </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>22.1125</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>23.742</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>35.71428571428557</t>
+          <t>42.85714285714278</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>34.12698412698408</t>
+          <t>26.19047619047612</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-272.14</t>
+          <t>152.27</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-1263589.2</t>
+          <t>1916326.6</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>734040.3</t>
+          <t>759621.9</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1997629</t>
+          <t>1156704</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>100688.5512850276</t>
+          <t>231307.5170610862</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>563670.96</t>
+          <t>949711.83</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2091,12 +2091,12 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2213,17 +2213,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>57</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>-15.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -2268,52 +2268,52 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>30</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.21</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>30.4175</t>
+          <t>30.1975</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>31.631</t>
+          <t>31.548</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-20.82</t>
+          <t>-23.49</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-40.11</t>
+          <t>-31.16</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2338,27 +2338,27 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-829.6</t>
+          <t>-857.4</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-592.1</t>
+          <t>-653.7</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-237</t>
+          <t>-203</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-134.6042436352146</t>
+          <t>-144.055169304196</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-213.47</t>
+          <t>-196.04</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.86</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>39101.788</t>
+          <t>42802.396</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2535,92 +2535,92 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>57</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>296</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>39102</t>
+          <t>42802</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>23.79</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>22.8975</t>
+          <t>22.9825</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.471</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>388.32</t>
+          <t>2179.24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>74.99999999999997</t>
+          <t>66.66666666666666</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>71.52777777777773</t>
+          <t>69.44444444444441</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-132.36</t>
+          <t>-115.02</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2630,32 +2630,32 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-182108664.2</t>
+          <t>-73601458.2</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>562766150.9</t>
+          <t>490026930.7</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-744874815</t>
+          <t>-563628388</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>106355887.3432737</t>
+          <t>81896215.91117072</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>65291866.56</t>
+          <t>-52631976.97</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.11</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>181228</t>
+          <t>179718</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF8"/>
+  <dimension ref="A1:BH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,230 +491,240 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>cond_entry</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LevelArea</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>漲跌BYN天</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>增縮BYN天</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>漲跌BYN天Diff</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>增縮BYN天Diff</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>VPC_MA_%</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>VPC_break</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change_sum</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
@@ -723,12 +733,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -738,12 +748,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3749.0</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,17 +763,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>7.82</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>235.5</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -783,230 +793,240 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-2.63</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>234.1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>240.425</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>241.84</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>-56.28</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>28.57142857142854</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>-12.70</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>746914.2</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>855603.9</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>-108689</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>-55787.30990307487</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>-49063.96</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>3749</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-0.59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>-2.06</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>236.9</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>241.875</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>241.11</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>-78.09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>-2.50</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-1.40</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>42.85714285714285</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>40.47619047619045</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>-60.91</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-554845.0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>-344809.9</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-210035</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-32754.06159599144</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>-38204.2</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>元太</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>-14.37152843188938</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>8.331352654369573</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>33.64857459462222</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>4.67</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
           <t>9.24</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>25.32</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>25.05</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>60.29%</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>39.55%</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>90.31</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>270940</t>
-        </is>
-      </c>
       <c r="BB2" t="inlineStr">
         <is>
+          <t>91.1</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>268132</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
           <t>消費性電子產品59.99%、物聯網應用40.01% (2024年)</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>元太-光電業-上櫃</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>光電業平</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>50.4</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 面板、電子書</t>
         </is>
@@ -1015,27 +1035,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>強勢股;【b】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2111.655</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1045,17 +1065,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12.94</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>385.5</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1070,556 +1090,576 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>False</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-33.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>226</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>398.0</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>379.225</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>367.03</t>
+          <t>42.98999999999999</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>19.78</t>
+          <t>42.465</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>42.51900000000001</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>136.49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>32.23140495867769</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>39.26163493483316</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-68.30</t>
+          <t>97.43589743589759</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
+          <t>89.74358974358988</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>117549612.0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>370783972.3</t>
-        </is>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-253234360</t>
+          <t>13766.6</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>43911971.38493001</t>
+          <t>13321.0</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-67845746.64</t>
+          <t>445</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>-273.9859545497775</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>磐儀</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.9020166977669146</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2.801034214035957</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>20.6824397798794</t>
+          <t>2.777924820167158</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>43.952087915709</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>39.99348075729182</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>33.05%</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16.15%</t>
+          <t>128.53</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>55.09</t>
+          <t>44.83%</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>30966</t>
+          <t>10.25%</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>商品銷售97.03%、勞務2.86%、其他0.11% (2024年)</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>辛耘-半導體業-上市</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>半導體業右上</t>
+          <t>系統產品49.64%、單板電腦35.36%、其他15.01% (2024年)</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>62.83</t>
+          <t>磐儀-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>** 半導體 - 生產製程及檢測設備、生產製程及檢測設備** 平面顯示器 - 生產製程及檢測設備** LED照明產業 - 生產製程、檢測設備及原物料** 太陽能產業 - 太陽能發電設備/系統及系統工程</t>
+          <t>電腦及週邊設備業平</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>21.68</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 工業電腦</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>945.994</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5.80</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>381.5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>31.0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>14.95</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>946</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>15.991</t>
+          <t>383.7</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-33.64</t>
+          <t>379.475</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>368.47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>13.46153846153846</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
+          <t>22.11803348166986</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-47.67</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-274.6</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>-325.6</t>
-        </is>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>795335615.6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>74.52359131762572</t>
+          <t>1519701377.7</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>-724365762</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>112540625.5580736</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>李洲</t>
+          <t>-10087664.79</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-71.1988141560126</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-14.64030752333882</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>16.61009005389843</t>
+          <t>-0.9020166977669146</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>2.801034214035957</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>20.6824397798794</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>6.07</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>1.18</t>
         </is>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>15.96%</t>
+          <t>36.27</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>-47.47%</t>
+          <t>31.37</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>33.05%</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>16.15%</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>LED 光電產品93.51%、磊晶片6.32%、其他0.17% (2024年)</t>
+          <t>55.47</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>李洲-光電業-上櫃</t>
+          <t>30645</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>光電業右下</t>
+          <t>商品銷售97.03%、勞務2.86%、其他0.11% (2024年)</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>辛耘-半導體業-上市</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>** LED照明產業 - 封裝/模組、燈具/應用</t>
+          <t>半導體業右上</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>62.83</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>** 半導體 - 生產製程及檢測設備、生產製程及檢測設備** 平面顯示器 - 生產製程及檢測設備** LED照明產業 - 生產製程、檢測設備及原物料** 太陽能產業 - 太陽能發電設備/系統及系統工程</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7975.868</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1629,17 +1669,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1659,259 +1699,269 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>False</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-31.0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>7976</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>26</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>44.0325</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>42.795</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-240.74</t>
+          <t>15.5375</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>16.011</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-25.42</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0.6006006006005856</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>-66.88</t>
-        </is>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>-15.79</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-459739351.4</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>-275495140.8</t>
-        </is>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-184244210</t>
+          <t>528.4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-44668100.01405367</t>
+          <t>627.5</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-86779796.66</t>
+          <t>-99</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
+          <t>-615.0622701031616</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>-402.18</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>興富發</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>李洲</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>135.7791560902942</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>8.442111486802782</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-47.58774907778343</t>
+          <t>-71.1988141560126</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>-14.64030752333882</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>16.61009005389843</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>20.37%</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7.22%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>15.96%</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>86923</t>
+          <t>-47.47%</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>建設業務99.44%、百貨0.38%、營造0.18% (2024年)</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>興富發-建材營造-上市</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>建材營造右下</t>
+          <t>LED 光電產品93.51%、磊晶片6.32%、其他0.17% (2024年)</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>李洲-光電業-上櫃</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>** 建材營造 - 建設業</t>
+          <t>光電業右下</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>12.69</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>** LED照明產業 - 封裝/模組、燈具/應用</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>280.115</t>
+          <t>5805.541</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1921,17 +1971,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>17.99</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1946,264 +1996,274 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>-43.0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>5806</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>-1.52</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>-7.80</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>40.21</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>43.6125</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>-1048.20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>-19.76</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>353202181.4</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>440189699.1</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>-86987517</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>20671647.59371134</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>-14641195.11</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>-6.71</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>22.12</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>23.71</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>19.43</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-0.54</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>42.85714285714278</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>26.19047619047612</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>152.27</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>1916326.6</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>759621.9</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>1156704</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>231307.5170610862</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>949711.83</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>橋椿</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>居家生活</t>
-        </is>
-      </c>
       <c r="AN6" t="inlineStr">
         <is>
+          <t>興富發</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.312824007547442</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-22.60101708031618</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-22.72990160044902</t>
+          <t>135.7791560902942</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>8.442111486802782</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>-47.58774907778343</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>8.32%</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>20.37%</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>7.22%</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>橋椿-居家生活-上市</t>
+          <t>86054</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>居家生活右下</t>
+          <t>建設業務99.44%、百貨0.38%、營造0.18% (2024年)</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>興富發-建材營造-上市</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>** 其他 - 其他</t>
+          <t>建材營造右下</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>24.27</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>** 建材營造 - 建設業</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>481.546</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2213,17 +2273,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2238,527 +2298,849 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>False</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-15.0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>482</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>29.21</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>30.1975</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>31.548</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-23.49</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>23.584</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>8.74</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>-31.16</t>
-        </is>
-      </c>
       <c r="AE7" t="inlineStr">
         <is>
+          <t>14.28571428571426</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>13.62</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-857.4</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>-653.7</t>
-        </is>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-203</t>
+          <t>9574398.2</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-144.055169304196</t>
+          <t>8426755.0</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-196.04</t>
+          <t>1147643</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-583861.7802077744</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>宏佳騰</t>
+          <t>-197071.98</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>橋椿</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>24.95650476538034</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-56.09617185216992</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-18.19449110167005</t>
+          <t>-4.312824007547442</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>-22.60101708031618</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>-22.72990160044902</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>8.41</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>20.81%</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-4.48%</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>33.86</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>ATV/ UTV64.10%、摩托車14.76%、電動車輛13.19%、零組件及其他7.95% (2024年)</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>宏佳騰-電機機械-上櫃</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>橋椿-居家生活-上市</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
+          <t>居家生活右下</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>35.8</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1599</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>-27.0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-3.55</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-4.82</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>28.83</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>29.89</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>31.405</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>-17.58</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>12.90322580645159</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>4.301075268817197</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>-3.40</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>762.4</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>789.2</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>-26</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>-45.63852493312474</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>-57.45</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>宏佳騰</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>24.95650476538034</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-56.09617185216992</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>-18.19449110167005</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>6.79</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>29.39</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>20.81%</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-4.48%</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>33.96</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>2146</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>ATV/ UTV64.10%、摩托車14.76%、電動車輛13.19%、零組件及其他7.95% (2024年)</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>宏佳騰-電機機械-上櫃</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>電機機械右下</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>【d】</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>1101</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>42802.396</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>23168.217</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>22.59</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.52</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>12.23</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-1.69</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>2025-09-22</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>42802</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>3.56</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>-2.08</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>22.9825</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>23.471</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2179.24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>66.66666666666666</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>69.44444444444441</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>-115.02</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-73601458.2</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>490026930.7</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>-563628388</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>81896215.91117072</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>-52631976.97</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>-8.0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>23168</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>23.81</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>23.105</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>23.446</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>202.93</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>21.73913043478257</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>40.13526570048302</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>-51.55</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>734773234.2</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>1516674888.2</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>-781901654</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>64817260.67398548</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>-61455149.21</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
         <is>
           <t>台泥</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>水泥工業</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>-9.760342271298851</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AT9" t="inlineStr">
         <is>
           <t>-6.072228435914363</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AU9" t="inlineStr">
         <is>
           <t>4.189538872550337</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
         <is>
           <t>4.57</t>
         </is>
       </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>23.11</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>23.01</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>15.12%</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>3.15%</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>30.96</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>179718</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>30.78</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>178963</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
         <is>
           <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>台泥-水泥工業-上市</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>水泥工業右下</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>28.5</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2014.0</t>
+          <t>2915.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -763,17 +763,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>237.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -803,92 +803,92 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>122</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>234.1</t>
+          <t>235.7</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>240.425</t>
+          <t>239.8</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>241.84</t>
+          <t>242.31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-56.28</t>
+          <t>-32.50</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>57.14285714285714</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>28.57142857142854</t>
+          <t>33.33333333333331</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-13.61</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -898,27 +898,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>746914.2</t>
+          <t>730407.2</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>855603.9</t>
+          <t>845507.9</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-108689</t>
+          <t>-115100</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-55787.30990307487</t>
+          <t>-54736.42455781888</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>-49063.96</t>
+          <t>-48956.56</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -998,12 +998,12 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>268132</t>
+          <t>273311</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
@@ -1035,12 +1035,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1130,102 +1130,102 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>426</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>42.98999999999999</t>
+          <t>43.51000000000001</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>42.465</t>
+          <t>42.58499999999999</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>42.51900000000001</t>
+          <t>42.58200000000001</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>136.49</t>
+          <t>129.91</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>97.43589743589759</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>89.74358974358988</t>
+          <t>94.87179487179493</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>-5.81</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>13766.6</t>
+          <t>13597.6</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>13321.0</t>
+          <t>14436.1</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>-838</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-273.9859545497775</t>
+          <t>-160.8851972749212</t>
         </is>
       </c>
       <c r="AL3" t="in